--- a/Slots/H045_超級鑽石/文件/101015_Help.xlsx
+++ b/Slots/H045_超級鑽石/文件/101015_Help.xlsx
@@ -523,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I123"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1701,7 +1701,7 @@
     <row r="70">
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>BUY FEATURE</t>
+          <t>EXTRA BET</t>
         </is>
       </c>
     </row>
@@ -1738,14 +1738,14 @@
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>購買特色</t>
+          <t>額外投注</t>
         </is>
       </c>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>BUY FEATURE</t>
+          <t>EXTRA BET</t>
         </is>
       </c>
       <c r="H72" s="7" t="n"/>
@@ -1762,14 +1762,14 @@
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>▪ 點擊「購買特色」按鈕，將開啟「購買特色」選單。</t>
+          <t>▪ 額外投注的扣款為 {2} × 您所選的基礎投注。</t>
         </is>
       </c>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>▪ BY TAPPING ON THE BUY FEATURE BUTTON, YOU WILL OPEN THE BUY FEATURE MENU.</t>
+          <t>▪ EXTRA BET COSTS {2} × THE BASE BET YOU SELECT.</t>
         </is>
       </c>
       <c r="H73" s="7" t="n"/>
@@ -1778,14 +1778,14 @@
     <row r="74">
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>▪ 您可以按「+」或「-」按鈕調整投注額與數量。</t>
+          <t>▪ 所有獎金仍依您所選的基礎投注計算。</t>
         </is>
       </c>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>▪ YOU CAN INCREASE OR DECREASE YOUR BET AND QUANTITY BY PRESSING THE "+" OR "-" BUTTONS.</t>
+          <t>▪ ALL WINS ARE STILL CALCULATED ON THE BASE BET YOU SELECT.</t>
         </is>
       </c>
       <c r="H74" s="7" t="n"/>
@@ -1794,94 +1794,91 @@
     <row r="75">
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>▪ 以所選投注額的 {50} 倍購買，直接觸發免費遊戲特色。</t>
+          <t>▪ 免費遊戲的觸發機率提升為一般投注的 {5} 倍。</t>
         </is>
       </c>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>▪ THE FREE GAME FEATURE CAN BE TRIGGERED DIRECTLY BY BUYING IT FOR {50}X THE SELECTED BET.</t>
+          <t>▪ THE CHANCE TO TRIGGER THE FREE GAME FEATURE IS {5} TIMES THAT OF THE NORMAL BET.</t>
         </is>
       </c>
       <c r="H75" s="7" t="n"/>
       <c r="I75" s="8" t="n"/>
     </row>
-    <row r="76">
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>▪ 最多可一次購買 {99} 次。</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="n"/>
-      <c r="F76" s="8" t="n"/>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>▪ THE MAXIMUM SELECTED QUANTITY IS {99}.</t>
-        </is>
-      </c>
-      <c r="H76" s="7" t="n"/>
-      <c r="I76" s="8" t="n"/>
-    </row>
     <row r="77">
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>▪ 總價 = 價格 × 數量，顯示在「購買特色」選單中。</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="n"/>
-      <c r="F77" s="8" t="n"/>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>▪ TOTAL PRICE = PRICE × QUANTITY, WHICH IS DISPLAYED IN THE BUY FEATURE MENU.</t>
-        </is>
-      </c>
-      <c r="H77" s="7" t="n"/>
-      <c r="I77" s="8" t="n"/>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>BUY FEATURE</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>▪ 按下「旋轉」按鈕／「購買並開始遊戲」按鈕後，「購買特色」選單中顯示的價格將從玩家的餘額中扣除。</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="n"/>
-      <c r="F78" s="8" t="n"/>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>▪ AFTER PRESSING THE SPIN BUTTON / BUY BUTTON, THE PRICE DISPLAYED IN THE BUY FEATURE MENU IS DEDUCTED FROM THE PLAYER'S BALANCE.</t>
-        </is>
-      </c>
-      <c r="H78" s="7" t="n"/>
-      <c r="I78" s="8" t="n"/>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>繁中</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
     </row>
     <row r="79">
+      <c r="B79" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>主要標題</t>
+        </is>
+      </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>▪ 第一局之後，玩家需按「旋轉」按鈕逐次進行，或點選「自動旋轉」按鈕自動進行剩餘的「購買特色」；剩餘數量為 {0} 時自動旋轉停止。</t>
+          <t>購買特色</t>
         </is>
       </c>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="8" t="n"/>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>▪ AFTER THE FIRST GAME, THE PLAYER PRESSES THE SPIN BUTTON TO PLAY EACH REMAINING BUY FEATURE, OR TAPS THE AUTO SPIN BUTTON TO PLAY THEM AUTOMATICALLY. AUTO SPIN STOPS WHEN THE REMAINING QUANTITY IS {0}.</t>
+          <t>BUY FEATURE</t>
         </is>
       </c>
       <c r="H79" s="7" t="n"/>
       <c r="I79" s="8" t="n"/>
     </row>
     <row r="80">
+      <c r="B80" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>▪ 如果網路中斷／瀏覽器關閉，剩餘的「購買特色」數量將被取消。</t>
+          <t>▪ 點擊「購買特色」按鈕，將開啟「購買特色」選單。</t>
         </is>
       </c>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="8" t="n"/>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>▪ IN CASE OF NETWORK DISCONNECTION / BROWSER CLOSE, THE REMAINING BUY FEATURE QUANTITY WILL BE CANCELLED.</t>
+          <t>▪ BY TAPPING ON THE BUY FEATURE BUTTON, YOU WILL OPEN THE BUY FEATURE MENU.</t>
         </is>
       </c>
       <c r="H80" s="7" t="n"/>
@@ -1890,14 +1887,14 @@
     <row r="81">
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>▪ 在最後一個「購買特色」完成之前，無法調整投注，也無法取消剩餘的「購買特色」。</t>
+          <t>▪ 您可以按「+」或「-」按鈕調整投注額與數量。</t>
         </is>
       </c>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>▪ THE BET CANNOT BE ADJUSTED AND THE REMAINING BUY FEATURE CANNOT BE CANCELLED BEFORE THE LAST BUY FEATURE IS COMPLETED.</t>
+          <t>▪ YOU CAN INCREASE OR DECREASE YOUR BET AND QUANTITY BY PRESSING THE "+" OR "-" BUTTONS.</t>
         </is>
       </c>
       <c r="H81" s="7" t="n"/>
@@ -1906,91 +1903,94 @@
     <row r="82">
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>▪ 所有「購買特色」完成後，投注將切換回購買前的投注。</t>
+          <t>▪ 以所選投注額的 {50} 倍購買，直接觸發免費遊戲特色。</t>
         </is>
       </c>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>▪ AFTER ALL BUY FEATURE ROUNDS ARE COMPLETED, THE BET WILL SWITCH BACK TO THE BET BEFORE THE PURCHASE.</t>
+          <t>▪ THE FREE GAME FEATURE CAN BE TRIGGERED DIRECTLY BY BUYING IT FOR {50}X THE SELECTED BET.</t>
         </is>
       </c>
       <c r="H82" s="7" t="n"/>
       <c r="I82" s="8" t="n"/>
     </row>
+    <row r="83">
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>▪ 最多可一次購買 {99} 次。</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="n"/>
+      <c r="F83" s="8" t="n"/>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>▪ THE MAXIMUM SELECTED QUANTITY IS {99}.</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="n"/>
+      <c r="I83" s="8" t="n"/>
+    </row>
     <row r="84">
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>OP JACKPOT</t>
-        </is>
-      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>▪ 總價 = 價格 × 數量，顯示在「購買特色」選單中。</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="n"/>
+      <c r="F84" s="8" t="n"/>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>▪ TOTAL PRICE = PRICE × QUANTITY, WHICH IS DISPLAYED IN THE BUY FEATURE MENU.</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="n"/>
+      <c r="I84" s="8" t="n"/>
     </row>
     <row r="85">
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>繁中</t>
-        </is>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>▪ 按下「旋轉」按鈕／「購買並開始遊戲」按鈕後，「購買特色」選單中顯示的價格將從玩家的餘額中扣除。</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="n"/>
+      <c r="F85" s="8" t="n"/>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>▪ AFTER PRESSING THE SPIN BUTTON / BUY BUTTON, THE PRICE DISPLAYED IN THE BUY FEATURE MENU IS DEDUCTED FROM THE PLAYER'S BALANCE.</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="n"/>
+      <c r="I85" s="8" t="n"/>
     </row>
     <row r="86">
-      <c r="B86" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>OP JACKPOT</t>
+          <t>▪ 第一局之後，玩家需按「旋轉」按鈕逐次進行，或點選「自動旋轉」按鈕自動進行剩餘的「購買特色」；剩餘數量為 {0} 時自動旋轉停止。</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>OP JACKPOT</t>
+          <t>▪ AFTER THE FIRST GAME, THE PLAYER PRESSES THE SPIN BUTTON TO PLAY EACH REMAINING BUY FEATURE, OR TAPS THE AUTO SPIN BUTTON TO PLAY THEM AUTOMATICALLY. AUTO SPIN STOPS WHEN THE REMAINING QUANTITY IS {0}.</t>
         </is>
       </c>
       <c r="H86" s="7" t="n"/>
       <c r="I86" s="8" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>規則說明</t>
-        </is>
-      </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>▪ 在遊戲中，OP JACKPOT 特色由盤面上的 [C1] 隨機觸發。</t>
+          <t>▪ 如果網路中斷／瀏覽器關閉，剩餘的「購買特色」數量將被取消。</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>▪ OP JACKPOT FEATURE IS TRIGGERED RANDOMLY BY {1} OR MORE [C1] ON THE REELS.</t>
+          <t>▪ IN CASE OF NETWORK DISCONNECTION / BROWSER CLOSE, THE REMAINING BUY FEATURE QUANTITY WILL BE CANCELLED.</t>
         </is>
       </c>
       <c r="H87" s="7" t="n"/>
@@ -1999,14 +1999,14 @@
     <row r="88">
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>▪ OP JACKPOT 特色會在畫面中出現 {12} 個 [幣]，其中包括 [GRAND]、[MAJOR]、[MINOR] 及 [MINI]。</t>
+          <t>▪ 在最後一個「購買特色」完成之前，無法調整投注，也無法取消剩餘的「購買特色」。</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
       <c r="F88" s="8" t="n"/>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>▪ DURING OP JACKPOT FEATURE, THERE ARE {12} [COIN] WHICH CONSIST OF [GRAND], [MAJOR], [MINOR] AND [MINI].</t>
+          <t>▪ THE BET CANNOT BE ADJUSTED AND THE REMAINING BUY FEATURE CANNOT BE CANCELLED BEFORE THE LAST BUY FEATURE IS COMPLETED.</t>
         </is>
       </c>
       <c r="H88" s="7" t="n"/>
@@ -2015,94 +2015,91 @@
     <row r="89">
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>▪ 選擇 {1} 個 [幣] 以揭示 [GRAND]、[MAJOR]、[MINOR] 或 [MINI]。</t>
+          <t>▪ 所有「購買特色」完成後，投注將切換回購買前的投注。</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="8" t="n"/>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>▪ SELECT A [COIN] TO REVEAL [GRAND], [MAJOR], [MINOR], OR [MINI].</t>
+          <t>▪ AFTER ALL BUY FEATURE ROUNDS ARE COMPLETED, THE BET WILL SWITCH BACK TO THE BET BEFORE THE PURCHASE.</t>
         </is>
       </c>
       <c r="H89" s="7" t="n"/>
       <c r="I89" s="8" t="n"/>
     </row>
-    <row r="90">
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>▪ 當玩家獲得 {3} 個相同的 OP JACKPOT 特色符號，即可獲得該 OP JACKPOT 並結算總獎金。</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="n"/>
-      <c r="F90" s="8" t="n"/>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>▪ IF PLAYER GETS {3} SAME JACKPOT SYMBOLS WILL WIN THE JACKPOT AND CALCULATE TOTAL WINNINGS.</t>
-        </is>
-      </c>
-      <c r="H90" s="7" t="n"/>
-      <c r="I90" s="8" t="n"/>
-    </row>
     <row r="91">
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>▪ [GRAND] 為連機累進彩金。單場遊戲中，投注選項選擇 {2.00} 以上即可解鎖 [GRAND]。</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="n"/>
-      <c r="F91" s="8" t="n"/>
-      <c r="G91" s="6" t="inlineStr">
-        <is>
-          <t>▪ [GRAND] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [GRAND].</t>
-        </is>
-      </c>
-      <c r="H91" s="7" t="n"/>
-      <c r="I91" s="8" t="n"/>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>OP JACKPOT</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>▪ [MAJOR] 為連機累進彩金。單場遊戲中，投注選項選擇 {2.00} 以上即可解鎖 [MAJOR]。</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="n"/>
-      <c r="F92" s="8" t="n"/>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>▪ [MAJOR] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [MAJOR].</t>
-        </is>
-      </c>
-      <c r="H92" s="7" t="n"/>
-      <c r="I92" s="8" t="n"/>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>繁中</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
     </row>
     <row r="93">
+      <c r="B93" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>主要標題</t>
+        </is>
+      </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>▪ [MINOR] 為紅利彩金，依照投注選項改變。</t>
+          <t>OP JACKPOT</t>
         </is>
       </c>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="8" t="n"/>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>▪ [MINOR] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
+          <t>OP JACKPOT</t>
         </is>
       </c>
       <c r="H93" s="7" t="n"/>
       <c r="I93" s="8" t="n"/>
     </row>
     <row r="94">
+      <c r="B94" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>▪ [MINI] 為紅利彩金，依照投注選項改變。</t>
+          <t>▪ 在遊戲中，OP JACKPOT 特色由盤面上的 [C1] 隨機觸發。</t>
         </is>
       </c>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="8" t="n"/>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>▪ [MINI] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
+          <t>▪ OP JACKPOT FEATURE IS TRIGGERED RANDOMLY BY {1} OR MORE [C1] ON THE REELS.</t>
         </is>
       </c>
       <c r="H94" s="7" t="n"/>
@@ -2111,62 +2108,46 @@
     <row r="95">
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>▪ 玩家投注越高，觸發 OP JACKPOT 特色的機會越高。</t>
+          <t>▪ OP JACKPOT 特色會在畫面中出現 {12} 個 [幣]，其中包括 [GRAND]、[MAJOR]、[MINOR] 及 [MINI]。</t>
         </is>
       </c>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>▪ THE HIGHER BET, THE HIGHER CHANCES TO TRIGGER OP JACKPOT FEATURE.</t>
+          <t>▪ DURING OP JACKPOT FEATURE, THERE ARE {12} [COIN] WHICH CONSIST OF [GRAND], [MAJOR], [MINOR] AND [MINI].</t>
         </is>
       </c>
       <c r="H95" s="7" t="n"/>
       <c r="I95" s="8" t="n"/>
     </row>
     <row r="96">
-      <c r="B96" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>OP JACKPOT</t>
+          <t>▪ 選擇 {1} 個 [幣] 以揭示 [GRAND]、[MAJOR]、[MINOR] 或 [MINI]。</t>
         </is>
       </c>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>OP JACKPOT</t>
+          <t>▪ SELECT A [COIN] TO REVEAL [GRAND], [MAJOR], [MINOR], OR [MINI].</t>
         </is>
       </c>
       <c r="H96" s="7" t="n"/>
       <c r="I96" s="8" t="n"/>
     </row>
     <row r="97">
-      <c r="B97" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>規則說明</t>
-        </is>
-      </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>在游戏中，OP JACKPOT 特色由特色转轮上 [C1] 随机触发。</t>
+          <t>▪ 當玩家獲得 {3} 個相同的 OP JACKPOT 特色符號，即可獲得該 OP JACKPOT 並結算總獎金。</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="8" t="n"/>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>OP JACKPOT FEATURE IS TRIGGERED RANDOMLY BY {1} OR MORE [C1] ON THE REELS.</t>
+          <t>▪ IF PLAYER GETS {3} SAME JACKPOT SYMBOLS WILL WIN THE JACKPOT AND CALCULATE TOTAL WINNINGS.</t>
         </is>
       </c>
       <c r="H97" s="7" t="n"/>
@@ -2175,14 +2156,14 @@
     <row r="98">
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>OP JACKPOT 特色会在画面中出现 {12} 个 [幣]，其中包括 [GRAND]、[MAJOR]、[MINOR] 及 [MINI]。</t>
+          <t>▪ [GRAND] 為連機累進彩金。單場遊戲中，投注選項選擇 {2.00} 以上即可解鎖 [GRAND]。</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>DURING OP JACKPOT FEATURE, THERE ARE {12} [COIN] WHICH CONSIST OF [GRAND], [MAJOR], [MINOR] AND [MINI].</t>
+          <t>▪ [GRAND] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [GRAND].</t>
         </is>
       </c>
       <c r="H98" s="7" t="n"/>
@@ -2191,14 +2172,14 @@
     <row r="99">
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>选择 {1} 个 [幣] 以揭示 [GRAND]、[MAJOR]、[MINOR] 或 [MINI]。</t>
+          <t>▪ [MAJOR] 為連機累進彩金。單場遊戲中，投注選項選擇 {2.00} 以上即可解鎖 [MAJOR]。</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>SELECT A [COIN] TO REVEAL [GRAND], [MAJOR], [MINOR], OR [MINI].</t>
+          <t>▪ [MAJOR] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [MAJOR].</t>
         </is>
       </c>
       <c r="H99" s="7" t="n"/>
@@ -2207,14 +2188,14 @@
     <row r="100">
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>当玩家获得 {3} 个相同的 OP JACKPOT 特色符号即可获得该 OP JACKPOT 并结算总奖金。</t>
+          <t>▪ [MINOR] 為紅利彩金，依照投注選項改變。</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="8" t="n"/>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>IF PLAYER GETS {3} SAME JACKPOT SYMBOLS WILL WIN THE JACKPOT AND CALCULATE TOTAL WINNINGS.</t>
+          <t>▪ [MINOR] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
         </is>
       </c>
       <c r="H100" s="7" t="n"/>
@@ -2223,14 +2204,14 @@
     <row r="101">
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>[GRAND] 为连机累进彩金。单场游戏中，投注选项选择 {2.00} 以上即可解锁 [GRAND]。</t>
+          <t>▪ [MINI] 為紅利彩金，依照投注選項改變。</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="8" t="n"/>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>[GRAND] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [GRAND].</t>
+          <t>▪ [MINI] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
         </is>
       </c>
       <c r="H101" s="7" t="n"/>
@@ -2239,46 +2220,62 @@
     <row r="102">
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>[MAJOR] 为连机累进彩金。单场游戏中，投注选项选择 {2.00} 以上即可解锁 [MAJOR]。</t>
+          <t>▪ 玩家投注越高，觸發 OP JACKPOT 特色的機會越高。</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="8" t="n"/>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>[MAJOR] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [MAJOR].</t>
+          <t>▪ THE HIGHER BET, THE HIGHER CHANCES TO TRIGGER OP JACKPOT FEATURE.</t>
         </is>
       </c>
       <c r="H102" s="7" t="n"/>
       <c r="I102" s="8" t="n"/>
     </row>
     <row r="103">
+      <c r="B103" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>主要標題</t>
+        </is>
+      </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>[MINOR] 为红利彩金，依照投注选项改变。</t>
+          <t>OP JACKPOT</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
       <c r="F103" s="8" t="n"/>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>[MINOR] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
+          <t>OP JACKPOT</t>
         </is>
       </c>
       <c r="H103" s="7" t="n"/>
       <c r="I103" s="8" t="n"/>
     </row>
     <row r="104">
+      <c r="B104" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>[MINI] 为红利彩金，依照投注选项改变。</t>
+          <t>在游戏中，OP JACKPOT 特色由特色转轮上 [C1] 随机触发。</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="8" t="n"/>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>[MINI] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
+          <t>OP JACKPOT FEATURE IS TRIGGERED RANDOMLY BY {1} OR MORE [C1] ON THE REELS.</t>
         </is>
       </c>
       <c r="H104" s="7" t="n"/>
@@ -2287,91 +2284,94 @@
     <row r="105">
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>玩家投注越高触发 OP JACKPOT 特色的机会越高。</t>
+          <t>OP JACKPOT 特色会在画面中出现 {12} 个 [幣]，其中包括 [GRAND]、[MAJOR]、[MINOR] 及 [MINI]。</t>
         </is>
       </c>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="8" t="n"/>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>THE HIGHER BET, THE HIGHER CHANCES TO TRIGGER OP JACKPOT FEATURE.</t>
+          <t>DURING OP JACKPOT FEATURE, THERE ARE {12} [COIN] WHICH CONSIST OF [GRAND], [MAJOR], [MINOR] AND [MINI].</t>
         </is>
       </c>
       <c r="H105" s="7" t="n"/>
       <c r="I105" s="8" t="n"/>
     </row>
+    <row r="106">
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>选择 {1} 个 [幣] 以揭示 [GRAND]、[MAJOR]、[MINOR] 或 [MINI]。</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="n"/>
+      <c r="F106" s="8" t="n"/>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>SELECT A [COIN] TO REVEAL [GRAND], [MAJOR], [MINOR], OR [MINI].</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="n"/>
+      <c r="I106" s="8" t="n"/>
+    </row>
     <row r="107">
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>LINES / WAYS</t>
-        </is>
-      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>当玩家获得 {3} 个相同的 OP JACKPOT 特色符号即可获得该 OP JACKPOT 并结算总奖金。</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="n"/>
+      <c r="F107" s="8" t="n"/>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>IF PLAYER GETS {3} SAME JACKPOT SYMBOLS WILL WIN THE JACKPOT AND CALCULATE TOTAL WINNINGS.</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="n"/>
+      <c r="I107" s="8" t="n"/>
     </row>
     <row r="108">
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>繁中</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>[GRAND] 为连机累进彩金。单场游戏中，投注选项选择 {2.00} 以上即可解锁 [GRAND]。</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="n"/>
+      <c r="F108" s="8" t="n"/>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>[GRAND] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [GRAND].</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="n"/>
+      <c r="I108" s="8" t="n"/>
     </row>
     <row r="109">
-      <c r="B109" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>最多路數</t>
+          <t>[MAJOR] 为连机累进彩金。单场游戏中，投注选项选择 {2.00} 以上即可解锁 [MAJOR]。</t>
         </is>
       </c>
       <c r="E109" s="7" t="n"/>
       <c r="F109" s="8" t="n"/>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>MAXIMUM WAYS</t>
+          <t>[MAJOR] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [MAJOR].</t>
         </is>
       </c>
       <c r="H109" s="7" t="n"/>
       <c r="I109" s="8" t="n"/>
     </row>
     <row r="110">
-      <c r="B110" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>規則說明</t>
-        </is>
-      </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>▪ 所有符號必須由最左至右連續出現，方可獲獎。</t>
+          <t>[MINOR] 为红利彩金，依照投注选项改变。</t>
         </is>
       </c>
       <c r="E110" s="7" t="n"/>
       <c r="F110" s="8" t="n"/>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>▪ ALL WINS ARE FROM LEFTMOST TO RIGHT ONLY.</t>
+          <t>[MINOR] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
         </is>
       </c>
       <c r="H110" s="7" t="n"/>
@@ -2380,14 +2380,14 @@
     <row r="111">
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>▪ 當同一路有多種獲獎組合，僅會賠付最高的獲獎組合。</t>
+          <t>[MINI] 为红利彩金，依照投注选项改变。</t>
         </is>
       </c>
       <c r="E111" s="7" t="n"/>
       <c r="F111" s="8" t="n"/>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>▪ ONLY THE HIGHEST WIN IS PAID WHEN THERE IS MORE THAN ONE WINNING COMBINATION WITH A CERTAIN SYMBOL.</t>
+          <t>[MINI] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
         </is>
       </c>
       <c r="H111" s="7" t="n"/>
@@ -2396,139 +2396,139 @@
     <row r="112">
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>▪ 遊戲設定 = 最多 {1,024} 路。</t>
+          <t>玩家投注越高触发 OP JACKPOT 特色的机会越高。</t>
         </is>
       </c>
       <c r="E112" s="7" t="n"/>
       <c r="F112" s="8" t="n"/>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>▪ GAME SETTING = {1,024} MAXIMUM WAYS.</t>
+          <t>THE HIGHER BET, THE HIGHER CHANCES TO TRIGGER OP JACKPOT FEATURE.</t>
         </is>
       </c>
       <c r="H112" s="7" t="n"/>
       <c r="I112" s="8" t="n"/>
     </row>
-    <row r="113">
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>[走線圖- 1,024 MAX WAYS]</t>
-        </is>
-      </c>
-      <c r="E113" s="7" t="n"/>
-      <c r="F113" s="8" t="n"/>
-      <c r="G113" s="6" t="inlineStr">
-        <is>
-          <t>[走線圖- 1,024 MAX WAYS]</t>
-        </is>
-      </c>
-      <c r="H113" s="7" t="n"/>
-      <c r="I113" s="8" t="n"/>
-    </row>
     <row r="114">
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
-        </is>
-      </c>
-      <c r="E114" s="7" t="n"/>
-      <c r="F114" s="8" t="n"/>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
-        </is>
-      </c>
-      <c r="H114" s="7" t="n"/>
-      <c r="I114" s="8" t="n"/>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>LINES / WAYS</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>[走線圖-NO WIN]</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="n"/>
-      <c r="F115" s="8" t="n"/>
-      <c r="G115" s="6" t="inlineStr">
-        <is>
-          <t>[走線圖-NO WIN]</t>
-        </is>
-      </c>
-      <c r="H115" s="7" t="n"/>
-      <c r="I115" s="8" t="n"/>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>繁中</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>主要標題</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>最多路數</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="n"/>
+      <c r="F116" s="8" t="n"/>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>MAXIMUM WAYS</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="n"/>
+      <c r="I116" s="8" t="n"/>
     </row>
     <row r="117">
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>GAME RULE</t>
-        </is>
-      </c>
+      <c r="B117" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>▪ 所有符號必須由最左至右連續出現，方可獲獎。</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="n"/>
+      <c r="F117" s="8" t="n"/>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>▪ ALL WINS ARE FROM LEFTMOST TO RIGHT ONLY.</t>
+        </is>
+      </c>
+      <c r="H117" s="7" t="n"/>
+      <c r="I117" s="8" t="n"/>
     </row>
     <row r="118">
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D118" s="5" t="inlineStr">
-        <is>
-          <t>繁中</t>
-        </is>
-      </c>
-      <c r="G118" s="5" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>▪ 當同一路有多種獲獎組合，僅會賠付最高的獲獎組合。</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="n"/>
+      <c r="F118" s="8" t="n"/>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>▪ ONLY THE HIGHEST WIN IS PAID WHEN THERE IS MORE THAN ONE WINNING COMBINATION WITH A CERTAIN SYMBOL.</t>
+        </is>
+      </c>
+      <c r="H118" s="7" t="n"/>
+      <c r="I118" s="8" t="n"/>
     </row>
     <row r="119">
-      <c r="B119" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>遊戲規則</t>
+          <t>▪ 遊戲設定 = 最多 {1,024} 路。</t>
         </is>
       </c>
       <c r="E119" s="7" t="n"/>
       <c r="F119" s="8" t="n"/>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>GAME RULES</t>
+          <t>▪ GAME SETTING = {1,024} MAXIMUM WAYS.</t>
         </is>
       </c>
       <c r="H119" s="7" t="n"/>
       <c r="I119" s="8" t="n"/>
     </row>
     <row r="120">
-      <c r="B120" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>規則說明</t>
-        </is>
-      </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>▪ 選擇您想要玩的投注選項。</t>
+          <t>[走線圖- 1,024 MAX WAYS]</t>
         </is>
       </c>
       <c r="E120" s="7" t="n"/>
       <c r="F120" s="8" t="n"/>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>▪ SELECT BET OPTION YOU WISH TO PLAY.</t>
+          <t>[走線圖- 1,024 MAX WAYS]</t>
         </is>
       </c>
       <c r="H120" s="7" t="n"/>
@@ -2537,14 +2537,14 @@
     <row r="121">
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>▪ 所有中獎金額均乘以投注選項，除非是累積獎。</t>
+          <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
         </is>
       </c>
       <c r="E121" s="7" t="n"/>
       <c r="F121" s="8" t="n"/>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>▪ ALL WINS ARE MULTIPLIED BY BET OPTION EXCEPT PROGRESSIVES BONUSES.</t>
+          <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
         </is>
       </c>
       <c r="H121" s="7" t="n"/>
@@ -2553,46 +2553,157 @@
     <row r="122">
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>▪ 遊戲出現故障時，所有賠付與遊戲結果均視為無效。</t>
+          <t>[走線圖-NO WIN]</t>
         </is>
       </c>
       <c r="E122" s="7" t="n"/>
       <c r="F122" s="8" t="n"/>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>▪ MALFUNCTION VOIDS ALL PAYS AND PLAYS.</t>
+          <t>[走線圖-NO WIN]</t>
         </is>
       </c>
       <c r="H122" s="7" t="n"/>
       <c r="I122" s="8" t="n"/>
     </row>
-    <row r="123">
-      <c r="D123" s="6" t="inlineStr">
+    <row r="124">
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>GAME RULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>繁中</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>主要標題</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>遊戲規則</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="n"/>
+      <c r="F126" s="8" t="n"/>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>GAME RULES</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="n"/>
+      <c r="I126" s="8" t="n"/>
+    </row>
+    <row r="127">
+      <c r="B127" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>▪ 選擇您想要玩的投注選項。</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="n"/>
+      <c r="F127" s="8" t="n"/>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>▪ SELECT BET OPTION YOU WISH TO PLAY.</t>
+        </is>
+      </c>
+      <c r="H127" s="7" t="n"/>
+      <c r="I127" s="8" t="n"/>
+    </row>
+    <row r="128">
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>▪ 所有中獎金額均乘以投注選項，除非是累積獎。</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="n"/>
+      <c r="F128" s="8" t="n"/>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>▪ ALL WINS ARE MULTIPLIED BY BET OPTION EXCEPT PROGRESSIVES BONUSES.</t>
+        </is>
+      </c>
+      <c r="H128" s="7" t="n"/>
+      <c r="I128" s="8" t="n"/>
+    </row>
+    <row r="129">
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>▪ 遊戲出現故障時，所有賠付與遊戲結果均視為無效。</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="n"/>
+      <c r="F129" s="8" t="n"/>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>▪ MALFUNCTION VOIDS ALL PAYS AND PLAYS.</t>
+        </is>
+      </c>
+      <c r="H129" s="7" t="n"/>
+      <c r="I129" s="8" t="n"/>
+    </row>
+    <row r="130">
+      <c r="D130" s="6" t="inlineStr">
         <is>
           <t>▪ 若玩家在免費遊戲期間中斷連線，系統將自動完成該局結算，並將中獎金額加入餘額。</t>
         </is>
       </c>
-      <c r="E123" s="7" t="n"/>
-      <c r="F123" s="8" t="n"/>
-      <c r="G123" s="6" t="inlineStr">
+      <c r="E130" s="7" t="n"/>
+      <c r="F130" s="8" t="n"/>
+      <c r="G130" s="6" t="inlineStr">
         <is>
           <t>▪ IF THE PLAYER LOSES CONNECTION DURING THE FREE GAME FEATURE, THE SYSTEM WILL COMPLETE THE RESULT AUTOMATICALLY AND ADD ANY WINNINGS TO THE BALANCE.</t>
         </is>
       </c>
-      <c r="H123" s="7" t="n"/>
-      <c r="I123" s="8" t="n"/>
+      <c r="H130" s="7" t="n"/>
+      <c r="I130" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="156">
+  <mergeCells count="164">
     <mergeCell ref="G38:I38"/>
     <mergeCell ref="G103:I103"/>
     <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D76:F76"/>
     <mergeCell ref="G112:I112"/>
     <mergeCell ref="G13:I13"/>
+    <mergeCell ref="D116:F116"/>
     <mergeCell ref="G62:I62"/>
+    <mergeCell ref="G118:I118"/>
     <mergeCell ref="D66:F66"/>
     <mergeCell ref="G87:I87"/>
+    <mergeCell ref="G127:I127"/>
     <mergeCell ref="D75:F75"/>
     <mergeCell ref="D53:F53"/>
     <mergeCell ref="D47:F47"/>
@@ -2607,17 +2718,18 @@
     <mergeCell ref="G73:I73"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="G88:I88"/>
-    <mergeCell ref="D92:F92"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="D39:F39"/>
+    <mergeCell ref="G129:I129"/>
     <mergeCell ref="G63:I63"/>
     <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G90:I90"/>
     <mergeCell ref="D94:F94"/>
+    <mergeCell ref="D129:F129"/>
     <mergeCell ref="G9:I9"/>
     <mergeCell ref="D119:F119"/>
-    <mergeCell ref="G115:I115"/>
     <mergeCell ref="G36:I36"/>
+    <mergeCell ref="D128:F128"/>
+    <mergeCell ref="G107:I107"/>
     <mergeCell ref="D80:F80"/>
     <mergeCell ref="D96:F96"/>
     <mergeCell ref="D105:F105"/>
@@ -2625,23 +2737,27 @@
     <mergeCell ref="G101:I101"/>
     <mergeCell ref="D120:F120"/>
     <mergeCell ref="G37:I37"/>
-    <mergeCell ref="G78:I78"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="G92:I92"/>
+    <mergeCell ref="D107:F107"/>
     <mergeCell ref="G30:I30"/>
     <mergeCell ref="G14:I14"/>
+    <mergeCell ref="D106:F106"/>
     <mergeCell ref="G80:I80"/>
     <mergeCell ref="D93:F93"/>
     <mergeCell ref="G55:I55"/>
     <mergeCell ref="G64:I64"/>
     <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D130:F130"/>
     <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D117:F117"/>
     <mergeCell ref="D55:F55"/>
     <mergeCell ref="G54:I54"/>
     <mergeCell ref="G119:I119"/>
     <mergeCell ref="G32:I32"/>
     <mergeCell ref="D67:F67"/>
     <mergeCell ref="D110:F110"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="G106:I106"/>
     <mergeCell ref="D54:F54"/>
     <mergeCell ref="D60:F60"/>
     <mergeCell ref="G56:I56"/>
@@ -2657,6 +2773,7 @@
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="D111:F111"/>
+    <mergeCell ref="D108:F108"/>
     <mergeCell ref="D86:F86"/>
     <mergeCell ref="G82:I82"/>
     <mergeCell ref="D95:F95"/>
@@ -2670,13 +2787,12 @@
     <mergeCell ref="G74:I74"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="G68:I68"/>
-    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="G83:I83"/>
     <mergeCell ref="D87:F87"/>
+    <mergeCell ref="G108:I108"/>
     <mergeCell ref="D122:F122"/>
-    <mergeCell ref="G123:I123"/>
     <mergeCell ref="G45:I45"/>
     <mergeCell ref="G110:I110"/>
-    <mergeCell ref="G113:I113"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D121:F121"/>
     <mergeCell ref="G100:I100"/>
@@ -2685,42 +2801,41 @@
     <mergeCell ref="G109:I109"/>
     <mergeCell ref="G47:I47"/>
     <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D113:F113"/>
     <mergeCell ref="G44:I44"/>
+    <mergeCell ref="G84:I84"/>
     <mergeCell ref="G31:I31"/>
     <mergeCell ref="G46:I46"/>
     <mergeCell ref="G102:I102"/>
-    <mergeCell ref="D123:F123"/>
     <mergeCell ref="G40:I40"/>
     <mergeCell ref="G111:I111"/>
     <mergeCell ref="D44:F44"/>
     <mergeCell ref="G12:I12"/>
-    <mergeCell ref="D115:F115"/>
     <mergeCell ref="G72:I72"/>
     <mergeCell ref="G86:I86"/>
     <mergeCell ref="D99:F99"/>
+    <mergeCell ref="D84:F84"/>
     <mergeCell ref="D36:F36"/>
     <mergeCell ref="G97:I97"/>
     <mergeCell ref="D45:F45"/>
     <mergeCell ref="D101:F101"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="D77:F77"/>
     <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G128:I128"/>
     <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D126:F126"/>
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="G49:I49"/>
     <mergeCell ref="G121:I121"/>
     <mergeCell ref="D72:F72"/>
     <mergeCell ref="D103:F103"/>
     <mergeCell ref="D112:F112"/>
-    <mergeCell ref="G114:I114"/>
     <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D118:F118"/>
     <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D114:F114"/>
-    <mergeCell ref="G76:I76"/>
-    <mergeCell ref="G91:I91"/>
+    <mergeCell ref="D127:F127"/>
     <mergeCell ref="D64:F64"/>
     <mergeCell ref="D38:F38"/>
+    <mergeCell ref="G85:I85"/>
     <mergeCell ref="D89:F89"/>
     <mergeCell ref="D98:F98"/>
     <mergeCell ref="G99:I99"/>
@@ -2728,17 +2843,19 @@
     <mergeCell ref="D79:F79"/>
     <mergeCell ref="G75:I75"/>
     <mergeCell ref="D88:F88"/>
+    <mergeCell ref="G130:I130"/>
     <mergeCell ref="D63:F63"/>
-    <mergeCell ref="G77:I77"/>
     <mergeCell ref="G11:I11"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="G117:I117"/>
     <mergeCell ref="G67:I67"/>
     <mergeCell ref="D65:F65"/>
     <mergeCell ref="G61:I61"/>
+    <mergeCell ref="G126:I126"/>
     <mergeCell ref="G39:I39"/>
     <mergeCell ref="G48:I48"/>
+    <mergeCell ref="G116:I116"/>
     <mergeCell ref="D49:F49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Slots/H045_超級鑽石/文件/101015_Help.xlsx
+++ b/Slots/H045_超級鑽石/文件/101015_Help.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,8 +46,17 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -66,8 +75,18 @@
         <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF666666"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -134,11 +153,102 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -158,6 +268,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -523,13 +653,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I130"/>
+  <dimension ref="A1:I120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
     <col width="8.69921875" customWidth="1" min="2" max="2"/>
     <col width="9.8984375" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -546,2156 +681,2254 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>PAYTABLE</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="4" t="inlineStr">
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>繁中</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>英文</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="6" t="n">
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="B7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>主要標題</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>符號賠付值</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>SYMBOL PAYOUT VALUES</t>
         </is>
       </c>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="8" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="6" t="n">
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="11" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="B8" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>規則說明</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>▪ 所有符號必須由最左至右連續出現，方可獲獎。</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>▪ ALL WINS ARE FROM LEFTMOST TO RIGHT ONLY.</t>
         </is>
       </c>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="8" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="6" t="n">
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="B9" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>副標題</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>百搭符號</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>WILD SYMBOL</t>
         </is>
       </c>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="8" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="6" t="n">
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="11" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="B10" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>規則說明</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>▪ [WW][W2] 可替代除 [C1] 以外的所有符號。</t>
         </is>
       </c>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>▪ [WW][W2] SUBSTITUTE FOR ALL SYMBOLS EXCEPT [C1].</t>
         </is>
       </c>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="8" t="n"/>
-    </row>
-    <row r="11">
-      <c r="D11" s="6" t="inlineStr">
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="11" t="n"/>
+    </row>
+    <row r="11" ht="31.5" customHeight="1">
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>▪ [WW][W2] 只會在金框符號被消除後產生。</t>
         </is>
       </c>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>▪ [WW][W2] ARE AWARDED ONLY AFTER A GOLDEN FRAMED SYMBOL IS REMOVED.</t>
         </is>
       </c>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="8" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="6" t="n">
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="11" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="B12" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>副標題</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>免費遊戲獎賞</t>
         </is>
       </c>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>FREE GAME BONUS</t>
         </is>
       </c>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="8" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="6" t="n">
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="47.25" customHeight="1">
+      <c r="B13" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>規則說明</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>▪ 當 {3} 個以上 [C1] 出現在任一位置，即可觸發免費遊戲特色，獲得 {10} 場免費遊戲。</t>
         </is>
       </c>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="15" t="inlineStr">
         <is>
           <t>▪ {3} OR MORE [C1] APPEARING IN ANY POSITION WILL TRIGGER THE FREE GAME FEATURE WITH {10} FREE SPINS.</t>
         </is>
       </c>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="8" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="6" t="n">
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="11" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="B14" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>副標題</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>賠率表</t>
         </is>
       </c>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>PAYTABLE</t>
         </is>
       </c>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="6" t="n">
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="11" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="B15" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>賠率表</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>[M1] 5 - 125</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>[M2] 5 - 100</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>[M3] 5 - 75</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>[M1] 5 - 125</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>[M2] 5 - 100</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="17" t="inlineStr">
         <is>
           <t>[M3] 5 - 75</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="D16" s="6" t="inlineStr">
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>[M1] 4 - 75</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>[M2] 4 - 60</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>[M3] 4 - 45</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>[M1] 4 - 75</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>[M2] 4 - 60</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t>[M3] 4 - 45</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="D17" s="6" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>[M1] 3 - 25</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>[M2] 3 - 20</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>[M3] 3 - 15</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t>[M1] 3 - 25</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>[M2] 3 - 20</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I17" s="17" t="inlineStr">
         <is>
           <t>[M3] 3 - 15</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="D19" s="6" t="inlineStr">
+    <row r="18" ht="7.95" customHeight="1">
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="17" t="n"/>
+      <c r="H18" s="17" t="n"/>
+      <c r="I18" s="17" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>[M4] 5 - 50</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>[A] 5 - 25</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>[K] 5 - 25</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>[M4] 5 - 50</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>[A] 5 - 25</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>[K] 5 - 25</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="D20" s="6" t="inlineStr">
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>[M4] 4 - 30</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>[A] 4 - 15</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>[K] 4 - 15</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>[M4] 4 - 30</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>[A] 4 - 15</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
         <is>
           <t>[K] 4 - 15</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="D21" s="6" t="inlineStr">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>[M4] 3 - 10</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>[A] 3 - 5</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>[K] 3 - 5</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="17" t="inlineStr">
         <is>
           <t>[M4] 3 - 10</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>[A] 3 - 5</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I21" s="17" t="inlineStr">
         <is>
           <t>[K] 3 - 5</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="D23" s="6" t="inlineStr">
+    <row r="22" ht="7.95" customHeight="1">
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="17" t="n"/>
+      <c r="H22" s="17" t="n"/>
+      <c r="I22" s="17" t="n"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>[Q] 5 - 15</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>[J] 5 - 15</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="17" t="inlineStr">
         <is>
           <t>[Q] 5 - 15</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr">
         <is>
           <t>[J] 5 - 15</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="D24" s="6" t="inlineStr">
+      <c r="I23" s="17" t="n"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>[Q] 4 - 10</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>[J] 4 - 10</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="17" t="inlineStr">
         <is>
           <t>[Q] 4 - 10</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>[J] 4 - 10</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="D25" s="6" t="inlineStr">
+      <c r="I24" s="17" t="n"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>[Q] 3 - 5</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>[J] 3 - 5</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="F25" s="17" t="n"/>
+      <c r="G25" s="17" t="inlineStr">
         <is>
           <t>[Q] 3 - 5</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H25" s="17" t="inlineStr">
         <is>
           <t>[J] 3 - 5</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="3" t="inlineStr">
+      <c r="I25" s="17" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>CASCADING FEATURE</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="4" t="inlineStr">
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="10" t="n"/>
+      <c r="I28" s="11" t="n"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>繁中</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="13" t="inlineStr">
         <is>
           <t>英文</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="6" t="n">
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="B30" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>主要標題</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>消除特色</t>
         </is>
       </c>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="15" t="inlineStr">
         <is>
           <t>CASCADING FEATURE</t>
         </is>
       </c>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="6" t="n">
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="47.25" customHeight="1">
+      <c r="B31" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>規則說明</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="15" t="inlineStr">
         <is>
           <t>▪ 遊戲中若達成連線，除金框符號外的中獎符號將被消除，並在原位置補上新的符號。</t>
         </is>
       </c>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="15" t="inlineStr">
         <is>
           <t>▪ ALL SYMBOLS IN WINNING COMBINATIONS, EXCEPT GOLDEN FRAMED SYMBOLS, WILL BE REMOVED AND NEW SYMBOLS WILL FILL THE EMPTY POSITIONS.</t>
         </is>
       </c>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="8" t="n"/>
-    </row>
-    <row r="32">
-      <c r="D32" s="6" t="inlineStr">
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="11" t="n"/>
+    </row>
+    <row r="32" ht="31.5" customHeight="1">
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="15" t="inlineStr">
         <is>
           <t>▪ 消除特色會持續發生，直到沒有新的連線為止。</t>
         </is>
       </c>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="15" t="inlineStr">
         <is>
           <t>▪ THE FEATURE CONTINUES UNTIL THERE ARE NO NEW WINNING COMBINATIONS.</t>
         </is>
       </c>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="8" t="n"/>
-    </row>
-    <row r="34">
-      <c r="B34" s="3" t="inlineStr">
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="11" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>GOLDEN FRAMED FEATURE</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="4" t="inlineStr">
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>繁中</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="13" t="inlineStr">
         <is>
           <t>英文</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="6" t="n">
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="11" t="n"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="B36" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>主要標題</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>金框符號特色</t>
         </is>
       </c>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="11" t="n"/>
+      <c r="G36" s="15" t="inlineStr">
         <is>
           <t>GOLDEN FRAMED FEATURE</t>
         </is>
       </c>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="8" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="6" t="n">
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="11" t="n"/>
+    </row>
+    <row r="37" ht="31.5" customHeight="1">
+      <c r="B37" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>規則說明</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>▪ 金框符號只會出現在第 {2}、{3}、{4} 輪。</t>
         </is>
       </c>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="15" t="inlineStr">
         <is>
           <t>▪ GOLDEN FRAMED SYMBOLS APPEAR ON REELS {2}, {3} AND {4} ONLY.</t>
         </is>
       </c>
-      <c r="H37" s="7" t="n"/>
-      <c r="I37" s="8" t="n"/>
-    </row>
-    <row r="38">
-      <c r="D38" s="6" t="inlineStr">
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="11" t="n"/>
+    </row>
+    <row r="38" ht="47.25" customHeight="1">
+      <c r="B38" s="18" t="n"/>
+      <c r="C38" s="18" t="n"/>
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>▪ 金框符號參與中獎時不會被消除，而是在原位置隨機轉換為以下兩種模式之一。</t>
         </is>
       </c>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="8" t="n"/>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>▪ WHEN A GOLDEN FRAMED SYMBOL IS PART OF A WINNING COMBINATION, IT IS NOT REMOVED AND RANDOMLY TURNS INTO ONE OF THE FOLLOWING TWO MODES AT ITS ORIGINAL POSITION.</t>
         </is>
       </c>
-      <c r="H38" s="7" t="n"/>
-      <c r="I38" s="8" t="n"/>
-    </row>
-    <row r="39">
-      <c r="D39" s="6" t="inlineStr">
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="B39" s="18" t="n"/>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="15" t="inlineStr">
         <is>
           <t>▪ 第一種模式：在原位置變成一個 [WW]。</t>
         </is>
       </c>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="8" t="n"/>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="15" t="inlineStr">
         <is>
           <t>▪ FIRST MODE: THE GOLDEN FRAMED SYMBOL TURNS INTO A [WW].</t>
         </is>
       </c>
-      <c r="H39" s="7" t="n"/>
-      <c r="I39" s="8" t="n"/>
-    </row>
-    <row r="40">
-      <c r="D40" s="6" t="inlineStr">
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="11" t="n"/>
+    </row>
+    <row r="40" ht="63" customHeight="1">
+      <c r="B40" s="16" t="n"/>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>▪ 第二種模式：在原位置變成一個 [W2]，並隨機複製 {2}～{4} 個 [WW] 取代第 {2}～{5} 輪的其他符號（不會取代 [C1] 與百搭符號）。</t>
         </is>
       </c>
-      <c r="E40" s="7" t="n"/>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="15" t="inlineStr">
         <is>
           <t>▪ SECOND MODE: THE GOLDEN FRAMED SYMBOL TURNS INTO A [W2] AND REPLICATES {2} TO {4} [WW] THAT RANDOMLY REPLACE OTHER SYMBOLS ON REELS {2} TO {5} ([C1] AND WILD SYMBOLS ARE NOT REPLACED).</t>
         </is>
       </c>
-      <c r="H40" s="7" t="n"/>
-      <c r="I40" s="8" t="n"/>
-    </row>
-    <row r="42">
-      <c r="B42" s="3" t="inlineStr">
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="11" t="n"/>
+    </row>
+    <row r="41"/>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>MULTIPLIER WILD FEATURE</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="4" t="inlineStr">
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="11" t="n"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>繁中</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="G43" s="13" t="inlineStr">
         <is>
           <t>英文</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="6" t="n">
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="11" t="n"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="B44" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>主要標題</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" s="15" t="inlineStr">
         <is>
           <t>倍數百搭特色</t>
         </is>
       </c>
-      <c r="E44" s="7" t="n"/>
-      <c r="F44" s="8" t="n"/>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="15" t="inlineStr">
         <is>
           <t>MULTIPLIER WILD FEATURE</t>
         </is>
       </c>
-      <c r="H44" s="7" t="n"/>
-      <c r="I44" s="8" t="n"/>
-    </row>
-    <row r="45">
-      <c r="B45" s="6" t="n">
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="11" t="n"/>
+    </row>
+    <row r="45" ht="31.5" customHeight="1">
+      <c r="B45" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>規則說明</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D45" s="15" t="inlineStr">
         <is>
           <t>▪ 金框符號轉換出的 [WW][W2] 有機會帶有 X{2}、X{3} 或 X{5} 倍數。</t>
         </is>
       </c>
-      <c r="E45" s="7" t="n"/>
-      <c r="F45" s="8" t="n"/>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="15" t="inlineStr">
         <is>
           <t>▪ [WW][W2] TRANSFORMED FROM GOLDEN FRAMED SYMBOLS MAY CARRY AN X{2}, X{3} OR X{5} MULTIPLIER.</t>
         </is>
       </c>
-      <c r="H45" s="7" t="n"/>
-      <c r="I45" s="8" t="n"/>
-    </row>
-    <row r="46">
-      <c r="D46" s="6" t="inlineStr">
+      <c r="H45" s="10" t="n"/>
+      <c r="I45" s="11" t="n"/>
+    </row>
+    <row r="46" ht="31.5" customHeight="1">
+      <c r="B46" s="18" t="n"/>
+      <c r="C46" s="18" t="n"/>
+      <c r="D46" s="15" t="inlineStr">
         <is>
           <t>▪ [W2] 複製出的 [WW] 帶有與該 [W2] 相同的倍數。</t>
         </is>
       </c>
-      <c r="E46" s="7" t="n"/>
-      <c r="F46" s="8" t="n"/>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="11" t="n"/>
+      <c r="G46" s="15" t="inlineStr">
         <is>
           <t>▪ [WW] REPLICATED BY A [W2] CARRY THE SAME MULTIPLIER AS THAT [W2].</t>
         </is>
       </c>
-      <c r="H46" s="7" t="n"/>
-      <c r="I46" s="8" t="n"/>
-    </row>
-    <row r="47">
-      <c r="D47" s="6" t="inlineStr">
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="11" t="n"/>
+    </row>
+    <row r="47" ht="47.25" customHeight="1">
+      <c r="B47" s="18" t="n"/>
+      <c r="C47" s="18" t="n"/>
+      <c r="D47" s="15" t="inlineStr">
         <is>
           <t>▪ 每次連線時，本次中獎並被消除的帶倍數百搭符號，其倍數會相加，再乘上當次的贏分倍數。</t>
         </is>
       </c>
-      <c r="E47" s="7" t="n"/>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="6" t="inlineStr">
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="11" t="n"/>
+      <c r="G47" s="15" t="inlineStr">
         <is>
           <t>▪ ON EACH WIN, THE MULTIPLIERS OF ALL MULTIPLIER WILDS THAT ARE PART OF THE WIN AND REMOVED ARE ADDED TOGETHER, THEN MULTIPLIED BY THE CURRENT WIN MULTIPLIER.</t>
         </is>
       </c>
-      <c r="H47" s="7" t="n"/>
-      <c r="I47" s="8" t="n"/>
-    </row>
-    <row r="48">
-      <c r="D48" s="6" t="inlineStr">
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="11" t="n"/>
+    </row>
+    <row r="48" ht="47.25" customHeight="1">
+      <c r="B48" s="16" t="n"/>
+      <c r="C48" s="16" t="n"/>
+      <c r="D48" s="15" t="inlineStr">
         <is>
           <t>▪ 未參與中獎的帶倍數百搭符號會保留在盤面上，直到參與中獎時才計入。</t>
         </is>
       </c>
-      <c r="E48" s="7" t="n"/>
-      <c r="F48" s="8" t="n"/>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="11" t="n"/>
+      <c r="G48" s="15" t="inlineStr">
         <is>
           <t>▪ MULTIPLIER WILDS THAT ARE NOT PART OF A WIN STAY ON THE REELS AND COUNT ONLY WHEN THEY ARE PART OF A LATER WIN.</t>
         </is>
       </c>
-      <c r="H48" s="7" t="n"/>
-      <c r="I48" s="8" t="n"/>
-    </row>
-    <row r="49">
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>▪ 例：贏分倍數 X{3}，本次中獎用到 X{2} 與 X{5} 的百搭符號，所有連線贏分乘以 X{21}（{3} × ({2} + {5})）。</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="n"/>
-      <c r="F49" s="8" t="n"/>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>▪ EXAMPLE: WITH A WIN MULTIPLIER OF X{3} AND MULTIPLIER WILDS OF X{2} AND X{5} IN THE WIN, ALL WINS ARE MULTIPLIED BY X{21} ({3} × ({2} + {5})).</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="n"/>
-      <c r="I49" s="8" t="n"/>
-    </row>
-    <row r="51">
-      <c r="B51" s="3" t="inlineStr">
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="11" t="n"/>
+    </row>
+    <row r="49"/>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>WIN MULTIPLIER FEATURE</t>
         </is>
       </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="4" t="inlineStr">
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="11" t="n"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr">
         <is>
           <t>繁中</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="11" t="n"/>
+      <c r="G51" s="13" t="inlineStr">
         <is>
           <t>英文</t>
         </is>
       </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="6" t="n">
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="11" t="n"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="B52" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C52" s="14" t="inlineStr">
         <is>
           <t>主要標題</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D52" s="15" t="inlineStr">
         <is>
           <t>贏分倍數特色</t>
         </is>
       </c>
-      <c r="E53" s="7" t="n"/>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="11" t="n"/>
+      <c r="G52" s="15" t="inlineStr">
         <is>
           <t>WIN MULTIPLIER FEATURE</t>
         </is>
       </c>
-      <c r="H53" s="7" t="n"/>
-      <c r="I53" s="8" t="n"/>
-    </row>
-    <row r="54">
-      <c r="B54" s="6" t="n">
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="11" t="n"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="B53" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C53" s="14" t="inlineStr">
         <is>
           <t>規則說明</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D53" s="15" t="inlineStr">
         <is>
           <t>▪ 每次旋轉開始時，贏分倍數為 X{1}。</t>
         </is>
       </c>
-      <c r="E54" s="7" t="n"/>
-      <c r="F54" s="8" t="n"/>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="11" t="n"/>
+      <c r="G53" s="15" t="inlineStr">
         <is>
           <t>▪ AT THE START OF EACH SPIN, THE WIN MULTIPLIER IS X{1}.</t>
         </is>
       </c>
-      <c r="H54" s="7" t="n"/>
-      <c r="I54" s="8" t="n"/>
-    </row>
-    <row r="55">
-      <c r="D55" s="6" t="inlineStr">
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="11" t="n"/>
+    </row>
+    <row r="54" ht="47.25" customHeight="1">
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="18" t="n"/>
+      <c r="D54" s="15" t="inlineStr">
         <is>
           <t>▪ 每次消除後若再達成連線，贏分倍數依序提升為 X{2}、X{3}、X{5}、X{10}。</t>
         </is>
       </c>
-      <c r="E55" s="7" t="n"/>
-      <c r="F55" s="8" t="n"/>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="11" t="n"/>
+      <c r="G54" s="15" t="inlineStr">
         <is>
           <t>▪ EACH TIME A NEW WINNING COMBINATION OCCURS AFTER A CASCADE, THE WIN MULTIPLIER INCREASES TO X{2}, X{3}, X{5} AND X{10} IN ORDER.</t>
         </is>
       </c>
-      <c r="H55" s="7" t="n"/>
-      <c r="I55" s="8" t="n"/>
-    </row>
-    <row r="56">
-      <c r="D56" s="6" t="inlineStr">
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="11" t="n"/>
+    </row>
+    <row r="55" ht="31.5" customHeight="1">
+      <c r="B55" s="16" t="n"/>
+      <c r="C55" s="16" t="n"/>
+      <c r="D55" s="15" t="inlineStr">
         <is>
           <t>▪ 贏分倍數達到 X{10} 後維持不變，直到本次旋轉結束。</t>
         </is>
       </c>
-      <c r="E56" s="7" t="n"/>
-      <c r="F56" s="8" t="n"/>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="11" t="n"/>
+      <c r="G55" s="15" t="inlineStr">
         <is>
           <t>▪ ONCE THE WIN MULTIPLIER REACHES X{10}, IT STAYS AT X{10} UNTIL THE SPIN ENDS.</t>
         </is>
       </c>
-      <c r="H56" s="7" t="n"/>
-      <c r="I56" s="8" t="n"/>
-    </row>
-    <row r="58">
-      <c r="B58" s="3" t="inlineStr">
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="11" t="n"/>
+    </row>
+    <row r="56"/>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>FREE GAME FEATURE</t>
         </is>
       </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="4" t="inlineStr">
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="11" t="n"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C58" s="12" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>繁中</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="11" t="n"/>
+      <c r="G58" s="13" t="inlineStr">
         <is>
           <t>英文</t>
         </is>
       </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="6" t="n">
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="11" t="n"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="B59" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C59" s="14" t="inlineStr">
         <is>
           <t>主要標題</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D59" s="15" t="inlineStr">
         <is>
           <t>免費遊戲特色</t>
         </is>
       </c>
-      <c r="E60" s="7" t="n"/>
-      <c r="F60" s="8" t="n"/>
-      <c r="G60" s="6" t="inlineStr">
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="11" t="n"/>
+      <c r="G59" s="15" t="inlineStr">
         <is>
           <t>FREE GAME FEATURE</t>
         </is>
       </c>
-      <c r="H60" s="7" t="n"/>
-      <c r="I60" s="8" t="n"/>
-    </row>
-    <row r="61">
-      <c r="B61" s="6" t="n">
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="11" t="n"/>
+    </row>
+    <row r="60" ht="31.5" customHeight="1">
+      <c r="B60" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C60" s="14" t="inlineStr">
         <is>
           <t>規則說明</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D60" s="15" t="inlineStr">
         <is>
           <t>▪ 當 {3} 個以上 [C1] 出現在任一位置，即可獲得 {10} 場免費遊戲。</t>
         </is>
       </c>
-      <c r="E61" s="7" t="n"/>
-      <c r="F61" s="8" t="n"/>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="11" t="n"/>
+      <c r="G60" s="15" t="inlineStr">
         <is>
           <t>▪ {3} OR MORE [C1] APPEARING IN ANY POSITION AWARD {10} FREE SPINS.</t>
         </is>
       </c>
-      <c r="H61" s="7" t="n"/>
-      <c r="I61" s="8" t="n"/>
-    </row>
-    <row r="62">
-      <c r="D62" s="6" t="inlineStr">
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="11" t="n"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="B61" s="18" t="n"/>
+      <c r="C61" s="18" t="n"/>
+      <c r="D61" s="15" t="inlineStr">
         <is>
           <t>▪ 點擊開始啟動免費遊戲特色。</t>
         </is>
       </c>
-      <c r="E62" s="7" t="n"/>
-      <c r="F62" s="8" t="n"/>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="11" t="n"/>
+      <c r="G61" s="15" t="inlineStr">
         <is>
           <t>▪ CLICK THE START BUTTON TO START THE FREE GAME FEATURE.</t>
         </is>
       </c>
-      <c r="H62" s="7" t="n"/>
-      <c r="I62" s="8" t="n"/>
-    </row>
-    <row r="63">
-      <c r="D63" s="6" t="inlineStr">
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="11" t="n"/>
+    </row>
+    <row r="62" ht="31.5" customHeight="1">
+      <c r="B62" s="18" t="n"/>
+      <c r="C62" s="18" t="n"/>
+      <c r="D62" s="15" t="inlineStr">
         <is>
           <t>▪ 在免費遊戲中，{3} 個以上 [C1] 可再獲得 {5} 場免費遊戲，最多可獲得 {50} 場免費遊戲。</t>
         </is>
       </c>
-      <c r="E63" s="7" t="n"/>
-      <c r="F63" s="8" t="n"/>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="11" t="n"/>
+      <c r="G62" s="15" t="inlineStr">
         <is>
           <t>▪ DURING THE FREE GAME, {3} OR MORE [C1] AWARD {5} MORE FREE SPINS. THE MAXIMUM NUMBER OF FREE SPINS IS {50}.</t>
         </is>
       </c>
-      <c r="H63" s="7" t="n"/>
-      <c r="I63" s="8" t="n"/>
-    </row>
-    <row r="64">
-      <c r="D64" s="6" t="inlineStr">
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="11" t="n"/>
+    </row>
+    <row r="63" ht="31.5" customHeight="1">
+      <c r="B63" s="16" t="n"/>
+      <c r="C63" s="16" t="n"/>
+      <c r="D63" s="15" t="inlineStr">
         <is>
           <t>▪ 在免費遊戲中，投注與觸發免費遊戲特色時相同。</t>
         </is>
       </c>
-      <c r="E64" s="7" t="n"/>
-      <c r="F64" s="8" t="n"/>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="11" t="n"/>
+      <c r="G63" s="15" t="inlineStr">
         <is>
           <t>▪ DURING THE FREE GAME, BET PER SPIN REMAINS THE SAME AS WHEN THE FREE GAME FEATURE WAS TRIGGERED.</t>
         </is>
       </c>
-      <c r="H64" s="7" t="n"/>
-      <c r="I64" s="8" t="n"/>
-    </row>
-    <row r="65">
-      <c r="B65" s="6" t="n">
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="11" t="n"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="B64" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C64" s="14" t="inlineStr">
         <is>
           <t>副標題</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D64" s="15" t="inlineStr">
         <is>
           <t>贏分倍數特色</t>
         </is>
       </c>
-      <c r="E65" s="7" t="n"/>
-      <c r="F65" s="8" t="n"/>
-      <c r="G65" s="6" t="inlineStr">
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="11" t="n"/>
+      <c r="G64" s="15" t="inlineStr">
         <is>
           <t>WIN MULTIPLIER FEATURE</t>
         </is>
       </c>
-      <c r="H65" s="7" t="n"/>
-      <c r="I65" s="8" t="n"/>
-    </row>
-    <row r="66">
-      <c r="B66" s="6" t="n">
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="11" t="n"/>
+    </row>
+    <row r="65" ht="31.5" customHeight="1">
+      <c r="B65" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C65" s="14" t="inlineStr">
         <is>
           <t>規則說明</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D65" s="15" t="inlineStr">
         <is>
           <t>▪ 免費遊戲每次旋轉開始時，贏分倍數為 X{2}。</t>
         </is>
       </c>
-      <c r="E66" s="7" t="n"/>
-      <c r="F66" s="8" t="n"/>
-      <c r="G66" s="6" t="inlineStr">
+      <c r="E65" s="10" t="n"/>
+      <c r="F65" s="11" t="n"/>
+      <c r="G65" s="15" t="inlineStr">
         <is>
           <t>▪ AT THE START OF EACH FREE SPIN, THE WIN MULTIPLIER IS X{2}.</t>
         </is>
       </c>
-      <c r="H66" s="7" t="n"/>
-      <c r="I66" s="8" t="n"/>
-    </row>
-    <row r="67">
-      <c r="D67" s="6" t="inlineStr">
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="11" t="n"/>
+    </row>
+    <row r="66" ht="47.25" customHeight="1">
+      <c r="B66" s="18" t="n"/>
+      <c r="C66" s="18" t="n"/>
+      <c r="D66" s="15" t="inlineStr">
         <is>
           <t>▪ 每次消除後若再達成連線，贏分倍數依序提升為 X{4}、X{6}、X{10}、X{20}。</t>
         </is>
       </c>
-      <c r="E67" s="7" t="n"/>
-      <c r="F67" s="8" t="n"/>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="E66" s="10" t="n"/>
+      <c r="F66" s="11" t="n"/>
+      <c r="G66" s="15" t="inlineStr">
         <is>
           <t>▪ EACH TIME A NEW WINNING COMBINATION OCCURS AFTER A CASCADE, THE WIN MULTIPLIER INCREASES TO X{4}, X{6}, X{10} AND X{20} IN ORDER.</t>
         </is>
       </c>
-      <c r="H67" s="7" t="n"/>
-      <c r="I67" s="8" t="n"/>
-    </row>
-    <row r="68">
-      <c r="D68" s="6" t="inlineStr">
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="11" t="n"/>
+    </row>
+    <row r="67" ht="31.5" customHeight="1">
+      <c r="B67" s="16" t="n"/>
+      <c r="C67" s="16" t="n"/>
+      <c r="D67" s="15" t="inlineStr">
         <is>
           <t>▪ 贏分倍數達到 X{20} 後維持不變，直到本次旋轉結束。</t>
         </is>
       </c>
-      <c r="E68" s="7" t="n"/>
-      <c r="F68" s="8" t="n"/>
-      <c r="G68" s="6" t="inlineStr">
+      <c r="E67" s="10" t="n"/>
+      <c r="F67" s="11" t="n"/>
+      <c r="G67" s="15" t="inlineStr">
         <is>
           <t>▪ ONCE THE WIN MULTIPLIER REACHES X{20}, IT STAYS AT X{20} UNTIL THE SPIN ENDS.</t>
         </is>
       </c>
-      <c r="H68" s="7" t="n"/>
-      <c r="I68" s="8" t="n"/>
-    </row>
-    <row r="70">
-      <c r="B70" s="3" t="inlineStr">
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="11" t="n"/>
+    </row>
+    <row r="68"/>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>EXTRA BET</t>
         </is>
       </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="4" t="inlineStr">
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="11" t="n"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C70" s="12" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D70" s="13" t="inlineStr">
         <is>
           <t>繁中</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="E70" s="10" t="n"/>
+      <c r="F70" s="11" t="n"/>
+      <c r="G70" s="13" t="inlineStr">
         <is>
           <t>英文</t>
         </is>
       </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="6" t="n">
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="11" t="n"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="B71" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C71" s="14" t="inlineStr">
         <is>
           <t>主要標題</t>
         </is>
       </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="D71" s="15" t="inlineStr">
         <is>
           <t>額外投注</t>
         </is>
       </c>
-      <c r="E72" s="7" t="n"/>
-      <c r="F72" s="8" t="n"/>
-      <c r="G72" s="6" t="inlineStr">
+      <c r="E71" s="10" t="n"/>
+      <c r="F71" s="11" t="n"/>
+      <c r="G71" s="15" t="inlineStr">
         <is>
           <t>EXTRA BET</t>
         </is>
       </c>
-      <c r="H72" s="7" t="n"/>
-      <c r="I72" s="8" t="n"/>
-    </row>
-    <row r="73">
-      <c r="B73" s="6" t="n">
+      <c r="H71" s="10" t="n"/>
+      <c r="I71" s="11" t="n"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="B72" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C72" s="14" t="inlineStr">
         <is>
           <t>規則說明</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D72" s="15" t="inlineStr">
         <is>
           <t>▪ 額外投注的扣款為 {2} × 您所選的基礎投注。</t>
         </is>
       </c>
-      <c r="E73" s="7" t="n"/>
-      <c r="F73" s="8" t="n"/>
-      <c r="G73" s="6" t="inlineStr">
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="11" t="n"/>
+      <c r="G72" s="15" t="inlineStr">
         <is>
           <t>▪ EXTRA BET COSTS {2} × THE BASE BET YOU SELECT.</t>
         </is>
       </c>
-      <c r="H73" s="7" t="n"/>
-      <c r="I73" s="8" t="n"/>
-    </row>
-    <row r="74">
-      <c r="D74" s="6" t="inlineStr">
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="11" t="n"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="B73" s="18" t="n"/>
+      <c r="C73" s="18" t="n"/>
+      <c r="D73" s="15" t="inlineStr">
         <is>
           <t>▪ 所有獎金仍依您所選的基礎投注計算。</t>
         </is>
       </c>
-      <c r="E74" s="7" t="n"/>
-      <c r="F74" s="8" t="n"/>
-      <c r="G74" s="6" t="inlineStr">
+      <c r="E73" s="10" t="n"/>
+      <c r="F73" s="11" t="n"/>
+      <c r="G73" s="15" t="inlineStr">
         <is>
           <t>▪ ALL WINS ARE STILL CALCULATED ON THE BASE BET YOU SELECT.</t>
         </is>
       </c>
-      <c r="H74" s="7" t="n"/>
-      <c r="I74" s="8" t="n"/>
-    </row>
-    <row r="75">
-      <c r="D75" s="6" t="inlineStr">
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="11" t="n"/>
+    </row>
+    <row r="74" ht="31.5" customHeight="1">
+      <c r="B74" s="16" t="n"/>
+      <c r="C74" s="16" t="n"/>
+      <c r="D74" s="15" t="inlineStr">
         <is>
           <t>▪ 免費遊戲的觸發機率提升為一般投注的 {5} 倍。</t>
         </is>
       </c>
-      <c r="E75" s="7" t="n"/>
-      <c r="F75" s="8" t="n"/>
-      <c r="G75" s="6" t="inlineStr">
+      <c r="E74" s="10" t="n"/>
+      <c r="F74" s="11" t="n"/>
+      <c r="G74" s="15" t="inlineStr">
         <is>
           <t>▪ THE CHANCE TO TRIGGER THE FREE GAME FEATURE IS {5} TIMES THAT OF THE NORMAL BET.</t>
         </is>
       </c>
-      <c r="H75" s="7" t="n"/>
-      <c r="I75" s="8" t="n"/>
-    </row>
-    <row r="77">
-      <c r="B77" s="3" t="inlineStr">
+      <c r="H74" s="10" t="n"/>
+      <c r="I74" s="11" t="n"/>
+    </row>
+    <row r="75"/>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="B76" s="9" t="inlineStr">
         <is>
           <t>BUY FEATURE</t>
         </is>
       </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="4" t="inlineStr">
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="10" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="11" t="n"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C77" s="12" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D77" s="13" t="inlineStr">
         <is>
           <t>繁中</t>
         </is>
       </c>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="E77" s="10" t="n"/>
+      <c r="F77" s="11" t="n"/>
+      <c r="G77" s="13" t="inlineStr">
         <is>
           <t>英文</t>
         </is>
       </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="6" t="n">
+      <c r="H77" s="10" t="n"/>
+      <c r="I77" s="11" t="n"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="B78" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="C78" s="14" t="inlineStr">
         <is>
           <t>主要標題</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D78" s="15" t="inlineStr">
         <is>
           <t>購買特色</t>
         </is>
       </c>
-      <c r="E79" s="7" t="n"/>
-      <c r="F79" s="8" t="n"/>
-      <c r="G79" s="6" t="inlineStr">
+      <c r="E78" s="10" t="n"/>
+      <c r="F78" s="11" t="n"/>
+      <c r="G78" s="15" t="inlineStr">
         <is>
           <t>BUY FEATURE</t>
         </is>
       </c>
-      <c r="H79" s="7" t="n"/>
-      <c r="I79" s="8" t="n"/>
-    </row>
-    <row r="80">
-      <c r="B80" s="6" t="n">
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="11" t="n"/>
+    </row>
+    <row r="79" ht="31.5" customHeight="1">
+      <c r="B79" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="C79" s="14" t="inlineStr">
         <is>
           <t>規則說明</t>
         </is>
       </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>▪ 點擊「購買特色」按鈕，將開啟「購買特色」選單。</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="n"/>
-      <c r="F80" s="8" t="n"/>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>▪ BY TAPPING ON THE BUY FEATURE BUTTON, YOU WILL OPEN THE BUY FEATURE MENU.</t>
-        </is>
-      </c>
-      <c r="H80" s="7" t="n"/>
-      <c r="I80" s="8" t="n"/>
-    </row>
-    <row r="81">
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>▪ 您可以按「+」或「-」按鈕調整投注額與數量。</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="n"/>
-      <c r="F81" s="8" t="n"/>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>▪ YOU CAN INCREASE OR DECREASE YOUR BET AND QUANTITY BY PRESSING THE "+" OR "-" BUTTONS.</t>
-        </is>
-      </c>
-      <c r="H81" s="7" t="n"/>
-      <c r="I81" s="8" t="n"/>
-    </row>
-    <row r="82">
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>▪ 以所選投注額的 {50} 倍購買，直接觸發免費遊戲特色。</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="n"/>
-      <c r="F82" s="8" t="n"/>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>▪ THE FREE GAME FEATURE CAN BE TRIGGERED DIRECTLY BY BUYING IT FOR {50}X THE SELECTED BET.</t>
-        </is>
-      </c>
-      <c r="H82" s="7" t="n"/>
-      <c r="I82" s="8" t="n"/>
-    </row>
-    <row r="83">
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>▪ 最多可一次購買 {99} 次。</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="n"/>
-      <c r="F83" s="8" t="n"/>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>▪ THE MAXIMUM SELECTED QUANTITY IS {99}.</t>
-        </is>
-      </c>
-      <c r="H83" s="7" t="n"/>
-      <c r="I83" s="8" t="n"/>
-    </row>
-    <row r="84">
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>▪ 總價 = 價格 × 數量，顯示在「購買特色」選單中。</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="n"/>
-      <c r="F84" s="8" t="n"/>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>▪ TOTAL PRICE = PRICE × QUANTITY, WHICH IS DISPLAYED IN THE BUY FEATURE MENU.</t>
-        </is>
-      </c>
-      <c r="H84" s="7" t="n"/>
-      <c r="I84" s="8" t="n"/>
-    </row>
-    <row r="85">
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>▪ 按下「旋轉」按鈕／「購買並開始遊戲」按鈕後，「購買特色」選單中顯示的價格將從玩家的餘額中扣除。</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="n"/>
-      <c r="F85" s="8" t="n"/>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>▪ AFTER PRESSING THE SPIN BUTTON / BUY BUTTON, THE PRICE DISPLAYED IN THE BUY FEATURE MENU IS DEDUCTED FROM THE PLAYER'S BALANCE.</t>
-        </is>
-      </c>
-      <c r="H85" s="7" t="n"/>
-      <c r="I85" s="8" t="n"/>
-    </row>
-    <row r="86">
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>▪ 第一局之後，玩家需按「旋轉」按鈕逐次進行，或點選「自動旋轉」按鈕自動進行剩餘的「購買特色」；剩餘數量為 {0} 時自動旋轉停止。</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="n"/>
-      <c r="F86" s="8" t="n"/>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>▪ AFTER THE FIRST GAME, THE PLAYER PRESSES THE SPIN BUTTON TO PLAY EACH REMAINING BUY FEATURE, OR TAPS THE AUTO SPIN BUTTON TO PLAY THEM AUTOMATICALLY. AUTO SPIN STOPS WHEN THE REMAINING QUANTITY IS {0}.</t>
-        </is>
-      </c>
-      <c r="H86" s="7" t="n"/>
-      <c r="I86" s="8" t="n"/>
-    </row>
-    <row r="87">
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>▪ 如果網路中斷／瀏覽器關閉，剩餘的「購買特色」數量將被取消。</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="n"/>
-      <c r="F87" s="8" t="n"/>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>▪ IN CASE OF NETWORK DISCONNECTION / BROWSER CLOSE, THE REMAINING BUY FEATURE QUANTITY WILL BE CANCELLED.</t>
-        </is>
-      </c>
-      <c r="H87" s="7" t="n"/>
-      <c r="I87" s="8" t="n"/>
-    </row>
-    <row r="88">
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>▪ 在最後一個「購買特色」完成之前，無法調整投注，也無法取消剩餘的「購買特色」。</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="n"/>
-      <c r="F88" s="8" t="n"/>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>▪ THE BET CANNOT BE ADJUSTED AND THE REMAINING BUY FEATURE CANNOT BE CANCELLED BEFORE THE LAST BUY FEATURE IS COMPLETED.</t>
-        </is>
-      </c>
-      <c r="H88" s="7" t="n"/>
-      <c r="I88" s="8" t="n"/>
-    </row>
-    <row r="89">
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>▪ 所有「購買特色」完成後，投注將切換回購買前的投注。</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="n"/>
-      <c r="F89" s="8" t="n"/>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>▪ AFTER ALL BUY FEATURE ROUNDS ARE COMPLETED, THE BET WILL SWITCH BACK TO THE BET BEFORE THE PURCHASE.</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="n"/>
-      <c r="I89" s="8" t="n"/>
-    </row>
-    <row r="91">
-      <c r="B91" s="3" t="inlineStr">
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>▪ 玩家可支付 {50}x 總投注，直接購買一次免費遊戲進場機會。</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="11" t="n"/>
+      <c r="G79" s="15" t="inlineStr">
+        <is>
+          <t>▪ BUY FEATURE CAN BE PURCHASED FOR {50}X TOTAL BET TO ENTER THE FREE GAME FEATURE DIRECTLY.</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="11" t="n"/>
+    </row>
+    <row r="80" ht="31.5" customHeight="1">
+      <c r="B80" s="16" t="n"/>
+      <c r="C80" s="16" t="n"/>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>▪ 完成購買後，將直接觸發一次免費遊戲特色。</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="n"/>
+      <c r="F80" s="11" t="n"/>
+      <c r="G80" s="15" t="inlineStr">
+        <is>
+          <t>▪ COMPLETING THE PURCHASE WILL TRIGGER THE FREE GAME FEATURE DIRECTLY.</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="n"/>
+      <c r="I80" s="11" t="n"/>
+    </row>
+    <row r="81"/>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="B82" s="9" t="inlineStr">
         <is>
           <t>OP JACKPOT</t>
         </is>
       </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="4" t="inlineStr">
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="10" t="n"/>
+      <c r="E82" s="10" t="n"/>
+      <c r="F82" s="10" t="n"/>
+      <c r="G82" s="10" t="n"/>
+      <c r="H82" s="10" t="n"/>
+      <c r="I82" s="11" t="n"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C83" s="12" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D83" s="13" t="inlineStr">
         <is>
           <t>繁中</t>
         </is>
       </c>
-      <c r="G92" s="5" t="inlineStr">
+      <c r="E83" s="10" t="n"/>
+      <c r="F83" s="11" t="n"/>
+      <c r="G83" s="13" t="inlineStr">
         <is>
           <t>英文</t>
         </is>
       </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="6" t="n">
+      <c r="H83" s="10" t="n"/>
+      <c r="I83" s="11" t="n"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="B84" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C93" s="6" t="inlineStr">
+      <c r="C84" s="14" t="inlineStr">
         <is>
           <t>主要標題</t>
         </is>
       </c>
-      <c r="D93" s="6" t="inlineStr">
+      <c r="D84" s="15" t="inlineStr">
         <is>
           <t>OP JACKPOT</t>
         </is>
       </c>
-      <c r="E93" s="7" t="n"/>
-      <c r="F93" s="8" t="n"/>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="E84" s="10" t="n"/>
+      <c r="F84" s="11" t="n"/>
+      <c r="G84" s="15" t="inlineStr">
         <is>
           <t>OP JACKPOT</t>
         </is>
       </c>
-      <c r="H93" s="7" t="n"/>
-      <c r="I93" s="8" t="n"/>
-    </row>
-    <row r="94">
-      <c r="B94" s="6" t="n">
+      <c r="H84" s="10" t="n"/>
+      <c r="I84" s="11" t="n"/>
+    </row>
+    <row r="85" ht="31.5" customHeight="1">
+      <c r="B85" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C94" s="6" t="inlineStr">
+      <c r="C85" s="14" t="inlineStr">
         <is>
           <t>規則說明</t>
         </is>
       </c>
-      <c r="D94" s="6" t="inlineStr">
+      <c r="D85" s="15" t="inlineStr">
         <is>
           <t>▪ 在遊戲中，OP JACKPOT 特色由盤面上的 [C1] 隨機觸發。</t>
         </is>
       </c>
-      <c r="E94" s="7" t="n"/>
-      <c r="F94" s="8" t="n"/>
-      <c r="G94" s="6" t="inlineStr">
+      <c r="E85" s="10" t="n"/>
+      <c r="F85" s="11" t="n"/>
+      <c r="G85" s="15" t="inlineStr">
         <is>
           <t>▪ OP JACKPOT FEATURE IS TRIGGERED RANDOMLY BY {1} OR MORE [C1] ON THE REELS.</t>
         </is>
       </c>
-      <c r="H94" s="7" t="n"/>
-      <c r="I94" s="8" t="n"/>
-    </row>
-    <row r="95">
-      <c r="D95" s="6" t="inlineStr">
+      <c r="H85" s="10" t="n"/>
+      <c r="I85" s="11" t="n"/>
+    </row>
+    <row r="86" ht="31.5" customHeight="1">
+      <c r="B86" s="18" t="n"/>
+      <c r="C86" s="18" t="n"/>
+      <c r="D86" s="15" t="inlineStr">
         <is>
           <t>▪ OP JACKPOT 特色會在畫面中出現 {12} 個 [幣]，其中包括 [GRAND]、[MAJOR]、[MINOR] 及 [MINI]。</t>
         </is>
       </c>
-      <c r="E95" s="7" t="n"/>
-      <c r="F95" s="8" t="n"/>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="E86" s="10" t="n"/>
+      <c r="F86" s="11" t="n"/>
+      <c r="G86" s="15" t="inlineStr">
         <is>
           <t>▪ DURING OP JACKPOT FEATURE, THERE ARE {12} [COIN] WHICH CONSIST OF [GRAND], [MAJOR], [MINOR] AND [MINI].</t>
         </is>
       </c>
-      <c r="H95" s="7" t="n"/>
-      <c r="I95" s="8" t="n"/>
-    </row>
-    <row r="96">
-      <c r="D96" s="6" t="inlineStr">
+      <c r="H86" s="10" t="n"/>
+      <c r="I86" s="11" t="n"/>
+    </row>
+    <row r="87" ht="31.5" customHeight="1">
+      <c r="B87" s="18" t="n"/>
+      <c r="C87" s="18" t="n"/>
+      <c r="D87" s="15" t="inlineStr">
         <is>
           <t>▪ 選擇 {1} 個 [幣] 以揭示 [GRAND]、[MAJOR]、[MINOR] 或 [MINI]。</t>
         </is>
       </c>
-      <c r="E96" s="7" t="n"/>
-      <c r="F96" s="8" t="n"/>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="E87" s="10" t="n"/>
+      <c r="F87" s="11" t="n"/>
+      <c r="G87" s="15" t="inlineStr">
         <is>
           <t>▪ SELECT A [COIN] TO REVEAL [GRAND], [MAJOR], [MINOR], OR [MINI].</t>
         </is>
       </c>
-      <c r="H96" s="7" t="n"/>
-      <c r="I96" s="8" t="n"/>
-    </row>
-    <row r="97">
-      <c r="D97" s="6" t="inlineStr">
+      <c r="H87" s="10" t="n"/>
+      <c r="I87" s="11" t="n"/>
+    </row>
+    <row r="88" ht="31.5" customHeight="1">
+      <c r="B88" s="18" t="n"/>
+      <c r="C88" s="18" t="n"/>
+      <c r="D88" s="15" t="inlineStr">
         <is>
           <t>▪ 當玩家獲得 {3} 個相同的 OP JACKPOT 特色符號，即可獲得該 OP JACKPOT 並結算總獎金。</t>
         </is>
       </c>
-      <c r="E97" s="7" t="n"/>
-      <c r="F97" s="8" t="n"/>
-      <c r="G97" s="6" t="inlineStr">
+      <c r="E88" s="10" t="n"/>
+      <c r="F88" s="11" t="n"/>
+      <c r="G88" s="15" t="inlineStr">
         <is>
           <t>▪ IF PLAYER GETS {3} SAME JACKPOT SYMBOLS WILL WIN THE JACKPOT AND CALCULATE TOTAL WINNINGS.</t>
         </is>
       </c>
-      <c r="H97" s="7" t="n"/>
-      <c r="I97" s="8" t="n"/>
-    </row>
-    <row r="98">
-      <c r="D98" s="6" t="inlineStr">
+      <c r="H88" s="10" t="n"/>
+      <c r="I88" s="11" t="n"/>
+    </row>
+    <row r="89" ht="47.25" customHeight="1">
+      <c r="B89" s="18" t="n"/>
+      <c r="C89" s="18" t="n"/>
+      <c r="D89" s="15" t="inlineStr">
         <is>
           <t>▪ [GRAND] 為連機累進彩金。單場遊戲中，投注選項選擇 {2.00} 以上即可解鎖 [GRAND]。</t>
         </is>
       </c>
-      <c r="E98" s="7" t="n"/>
-      <c r="F98" s="8" t="n"/>
-      <c r="G98" s="6" t="inlineStr">
+      <c r="E89" s="10" t="n"/>
+      <c r="F89" s="11" t="n"/>
+      <c r="G89" s="15" t="inlineStr">
         <is>
           <t>▪ [GRAND] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [GRAND].</t>
         </is>
       </c>
-      <c r="H98" s="7" t="n"/>
-      <c r="I98" s="8" t="n"/>
-    </row>
-    <row r="99">
-      <c r="D99" s="6" t="inlineStr">
+      <c r="H89" s="10" t="n"/>
+      <c r="I89" s="11" t="n"/>
+    </row>
+    <row r="90" ht="47.25" customHeight="1">
+      <c r="B90" s="18" t="n"/>
+      <c r="C90" s="18" t="n"/>
+      <c r="D90" s="15" t="inlineStr">
         <is>
           <t>▪ [MAJOR] 為連機累進彩金。單場遊戲中，投注選項選擇 {2.00} 以上即可解鎖 [MAJOR]。</t>
         </is>
       </c>
-      <c r="E99" s="7" t="n"/>
-      <c r="F99" s="8" t="n"/>
-      <c r="G99" s="6" t="inlineStr">
+      <c r="E90" s="10" t="n"/>
+      <c r="F90" s="11" t="n"/>
+      <c r="G90" s="15" t="inlineStr">
         <is>
           <t>▪ [MAJOR] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [MAJOR].</t>
         </is>
       </c>
-      <c r="H99" s="7" t="n"/>
-      <c r="I99" s="8" t="n"/>
-    </row>
-    <row r="100">
-      <c r="D100" s="6" t="inlineStr">
+      <c r="H90" s="10" t="n"/>
+      <c r="I90" s="11" t="n"/>
+    </row>
+    <row r="91" ht="31.5" customHeight="1">
+      <c r="B91" s="18" t="n"/>
+      <c r="C91" s="18" t="n"/>
+      <c r="D91" s="15" t="inlineStr">
         <is>
           <t>▪ [MINOR] 為紅利彩金，依照投注選項改變。</t>
         </is>
       </c>
-      <c r="E100" s="7" t="n"/>
-      <c r="F100" s="8" t="n"/>
-      <c r="G100" s="6" t="inlineStr">
+      <c r="E91" s="10" t="n"/>
+      <c r="F91" s="11" t="n"/>
+      <c r="G91" s="15" t="inlineStr">
         <is>
           <t>▪ [MINOR] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
         </is>
       </c>
-      <c r="H100" s="7" t="n"/>
-      <c r="I100" s="8" t="n"/>
-    </row>
-    <row r="101">
-      <c r="D101" s="6" t="inlineStr">
+      <c r="H91" s="10" t="n"/>
+      <c r="I91" s="11" t="n"/>
+    </row>
+    <row r="92" ht="31.5" customHeight="1">
+      <c r="B92" s="18" t="n"/>
+      <c r="C92" s="18" t="n"/>
+      <c r="D92" s="15" t="inlineStr">
         <is>
           <t>▪ [MINI] 為紅利彩金，依照投注選項改變。</t>
         </is>
       </c>
-      <c r="E101" s="7" t="n"/>
-      <c r="F101" s="8" t="n"/>
-      <c r="G101" s="6" t="inlineStr">
+      <c r="E92" s="10" t="n"/>
+      <c r="F92" s="11" t="n"/>
+      <c r="G92" s="15" t="inlineStr">
         <is>
           <t>▪ [MINI] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
         </is>
       </c>
-      <c r="H101" s="7" t="n"/>
-      <c r="I101" s="8" t="n"/>
-    </row>
-    <row r="102">
-      <c r="D102" s="6" t="inlineStr">
+      <c r="H92" s="10" t="n"/>
+      <c r="I92" s="11" t="n"/>
+    </row>
+    <row r="93" ht="31.5" customHeight="1">
+      <c r="B93" s="16" t="n"/>
+      <c r="C93" s="16" t="n"/>
+      <c r="D93" s="15" t="inlineStr">
         <is>
           <t>▪ 玩家投注越高，觸發 OP JACKPOT 特色的機會越高。</t>
         </is>
       </c>
-      <c r="E102" s="7" t="n"/>
-      <c r="F102" s="8" t="n"/>
-      <c r="G102" s="6" t="inlineStr">
+      <c r="E93" s="10" t="n"/>
+      <c r="F93" s="11" t="n"/>
+      <c r="G93" s="15" t="inlineStr">
         <is>
           <t>▪ THE HIGHER BET, THE HIGHER CHANCES TO TRIGGER OP JACKPOT FEATURE.</t>
         </is>
       </c>
-      <c r="H102" s="7" t="n"/>
-      <c r="I102" s="8" t="n"/>
-    </row>
-    <row r="103">
-      <c r="B103" s="6" t="n">
+      <c r="H93" s="10" t="n"/>
+      <c r="I93" s="11" t="n"/>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="B94" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="C103" s="6" t="inlineStr">
+      <c r="C94" s="14" t="inlineStr">
         <is>
           <t>主要標題</t>
         </is>
       </c>
-      <c r="D103" s="6" t="inlineStr">
+      <c r="D94" s="15" t="inlineStr">
         <is>
           <t>OP JACKPOT</t>
         </is>
       </c>
-      <c r="E103" s="7" t="n"/>
-      <c r="F103" s="8" t="n"/>
-      <c r="G103" s="6" t="inlineStr">
+      <c r="E94" s="10" t="n"/>
+      <c r="F94" s="11" t="n"/>
+      <c r="G94" s="15" t="inlineStr">
         <is>
           <t>OP JACKPOT</t>
         </is>
       </c>
-      <c r="H103" s="7" t="n"/>
-      <c r="I103" s="8" t="n"/>
-    </row>
-    <row r="104">
-      <c r="B104" s="6" t="n">
+      <c r="H94" s="10" t="n"/>
+      <c r="I94" s="11" t="n"/>
+    </row>
+    <row r="95" ht="31.5" customHeight="1">
+      <c r="B95" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="C104" s="6" t="inlineStr">
+      <c r="C95" s="14" t="inlineStr">
         <is>
           <t>規則說明</t>
         </is>
       </c>
-      <c r="D104" s="6" t="inlineStr">
+      <c r="D95" s="15" t="inlineStr">
         <is>
           <t>在游戏中，OP JACKPOT 特色由特色转轮上 [C1] 随机触发。</t>
         </is>
       </c>
-      <c r="E104" s="7" t="n"/>
-      <c r="F104" s="8" t="n"/>
-      <c r="G104" s="6" t="inlineStr">
+      <c r="E95" s="10" t="n"/>
+      <c r="F95" s="11" t="n"/>
+      <c r="G95" s="15" t="inlineStr">
         <is>
           <t>OP JACKPOT FEATURE IS TRIGGERED RANDOMLY BY {1} OR MORE [C1] ON THE REELS.</t>
         </is>
       </c>
-      <c r="H104" s="7" t="n"/>
-      <c r="I104" s="8" t="n"/>
-    </row>
-    <row r="105">
-      <c r="D105" s="6" t="inlineStr">
+      <c r="H95" s="10" t="n"/>
+      <c r="I95" s="11" t="n"/>
+    </row>
+    <row r="96" ht="31.5" customHeight="1">
+      <c r="B96" s="18" t="n"/>
+      <c r="C96" s="18" t="n"/>
+      <c r="D96" s="15" t="inlineStr">
         <is>
           <t>OP JACKPOT 特色会在画面中出现 {12} 个 [幣]，其中包括 [GRAND]、[MAJOR]、[MINOR] 及 [MINI]。</t>
         </is>
       </c>
-      <c r="E105" s="7" t="n"/>
-      <c r="F105" s="8" t="n"/>
-      <c r="G105" s="6" t="inlineStr">
+      <c r="E96" s="10" t="n"/>
+      <c r="F96" s="11" t="n"/>
+      <c r="G96" s="15" t="inlineStr">
         <is>
           <t>DURING OP JACKPOT FEATURE, THERE ARE {12} [COIN] WHICH CONSIST OF [GRAND], [MAJOR], [MINOR] AND [MINI].</t>
         </is>
       </c>
-      <c r="H105" s="7" t="n"/>
-      <c r="I105" s="8" t="n"/>
-    </row>
-    <row r="106">
-      <c r="D106" s="6" t="inlineStr">
+      <c r="H96" s="10" t="n"/>
+      <c r="I96" s="11" t="n"/>
+    </row>
+    <row r="97" ht="31.5" customHeight="1">
+      <c r="B97" s="18" t="n"/>
+      <c r="C97" s="18" t="n"/>
+      <c r="D97" s="15" t="inlineStr">
         <is>
           <t>选择 {1} 个 [幣] 以揭示 [GRAND]、[MAJOR]、[MINOR] 或 [MINI]。</t>
         </is>
       </c>
-      <c r="E106" s="7" t="n"/>
-      <c r="F106" s="8" t="n"/>
-      <c r="G106" s="6" t="inlineStr">
+      <c r="E97" s="10" t="n"/>
+      <c r="F97" s="11" t="n"/>
+      <c r="G97" s="15" t="inlineStr">
         <is>
           <t>SELECT A [COIN] TO REVEAL [GRAND], [MAJOR], [MINOR], OR [MINI].</t>
         </is>
       </c>
-      <c r="H106" s="7" t="n"/>
-      <c r="I106" s="8" t="n"/>
-    </row>
-    <row r="107">
-      <c r="D107" s="6" t="inlineStr">
+      <c r="H97" s="10" t="n"/>
+      <c r="I97" s="11" t="n"/>
+    </row>
+    <row r="98" ht="31.5" customHeight="1">
+      <c r="B98" s="18" t="n"/>
+      <c r="C98" s="18" t="n"/>
+      <c r="D98" s="15" t="inlineStr">
         <is>
           <t>当玩家获得 {3} 个相同的 OP JACKPOT 特色符号即可获得该 OP JACKPOT 并结算总奖金。</t>
         </is>
       </c>
-      <c r="E107" s="7" t="n"/>
-      <c r="F107" s="8" t="n"/>
-      <c r="G107" s="6" t="inlineStr">
+      <c r="E98" s="10" t="n"/>
+      <c r="F98" s="11" t="n"/>
+      <c r="G98" s="15" t="inlineStr">
         <is>
           <t>IF PLAYER GETS {3} SAME JACKPOT SYMBOLS WILL WIN THE JACKPOT AND CALCULATE TOTAL WINNINGS.</t>
         </is>
       </c>
-      <c r="H107" s="7" t="n"/>
-      <c r="I107" s="8" t="n"/>
-    </row>
-    <row r="108">
-      <c r="D108" s="6" t="inlineStr">
+      <c r="H98" s="10" t="n"/>
+      <c r="I98" s="11" t="n"/>
+    </row>
+    <row r="99" ht="47.25" customHeight="1">
+      <c r="B99" s="18" t="n"/>
+      <c r="C99" s="18" t="n"/>
+      <c r="D99" s="15" t="inlineStr">
         <is>
           <t>[GRAND] 为连机累进彩金。单场游戏中，投注选项选择 {2.00} 以上即可解锁 [GRAND]。</t>
         </is>
       </c>
-      <c r="E108" s="7" t="n"/>
-      <c r="F108" s="8" t="n"/>
-      <c r="G108" s="6" t="inlineStr">
+      <c r="E99" s="10" t="n"/>
+      <c r="F99" s="11" t="n"/>
+      <c r="G99" s="15" t="inlineStr">
         <is>
           <t>[GRAND] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [GRAND].</t>
         </is>
       </c>
-      <c r="H108" s="7" t="n"/>
-      <c r="I108" s="8" t="n"/>
-    </row>
-    <row r="109">
-      <c r="D109" s="6" t="inlineStr">
+      <c r="H99" s="10" t="n"/>
+      <c r="I99" s="11" t="n"/>
+    </row>
+    <row r="100" ht="47.25" customHeight="1">
+      <c r="B100" s="18" t="n"/>
+      <c r="C100" s="18" t="n"/>
+      <c r="D100" s="15" t="inlineStr">
         <is>
           <t>[MAJOR] 为连机累进彩金。单场游戏中，投注选项选择 {2.00} 以上即可解锁 [MAJOR]。</t>
         </is>
       </c>
-      <c r="E109" s="7" t="n"/>
-      <c r="F109" s="8" t="n"/>
-      <c r="G109" s="6" t="inlineStr">
+      <c r="E100" s="10" t="n"/>
+      <c r="F100" s="11" t="n"/>
+      <c r="G100" s="15" t="inlineStr">
         <is>
           <t>[MAJOR] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [MAJOR].</t>
         </is>
       </c>
-      <c r="H109" s="7" t="n"/>
-      <c r="I109" s="8" t="n"/>
-    </row>
-    <row r="110">
-      <c r="D110" s="6" t="inlineStr">
+      <c r="H100" s="10" t="n"/>
+      <c r="I100" s="11" t="n"/>
+    </row>
+    <row r="101" ht="31.5" customHeight="1">
+      <c r="B101" s="18" t="n"/>
+      <c r="C101" s="18" t="n"/>
+      <c r="D101" s="15" t="inlineStr">
         <is>
           <t>[MINOR] 为红利彩金，依照投注选项改变。</t>
         </is>
       </c>
-      <c r="E110" s="7" t="n"/>
-      <c r="F110" s="8" t="n"/>
-      <c r="G110" s="6" t="inlineStr">
+      <c r="E101" s="10" t="n"/>
+      <c r="F101" s="11" t="n"/>
+      <c r="G101" s="15" t="inlineStr">
         <is>
           <t>[MINOR] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
         </is>
       </c>
-      <c r="H110" s="7" t="n"/>
-      <c r="I110" s="8" t="n"/>
-    </row>
-    <row r="111">
-      <c r="D111" s="6" t="inlineStr">
+      <c r="H101" s="10" t="n"/>
+      <c r="I101" s="11" t="n"/>
+    </row>
+    <row r="102" ht="31.5" customHeight="1">
+      <c r="B102" s="18" t="n"/>
+      <c r="C102" s="18" t="n"/>
+      <c r="D102" s="15" t="inlineStr">
         <is>
           <t>[MINI] 为红利彩金，依照投注选项改变。</t>
         </is>
       </c>
-      <c r="E111" s="7" t="n"/>
-      <c r="F111" s="8" t="n"/>
-      <c r="G111" s="6" t="inlineStr">
+      <c r="E102" s="10" t="n"/>
+      <c r="F102" s="11" t="n"/>
+      <c r="G102" s="15" t="inlineStr">
         <is>
           <t>[MINI] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
         </is>
       </c>
-      <c r="H111" s="7" t="n"/>
-      <c r="I111" s="8" t="n"/>
-    </row>
-    <row r="112">
-      <c r="D112" s="6" t="inlineStr">
+      <c r="H102" s="10" t="n"/>
+      <c r="I102" s="11" t="n"/>
+    </row>
+    <row r="103" ht="31.5" customHeight="1">
+      <c r="B103" s="16" t="n"/>
+      <c r="C103" s="16" t="n"/>
+      <c r="D103" s="15" t="inlineStr">
         <is>
           <t>玩家投注越高触发 OP JACKPOT 特色的机会越高。</t>
         </is>
       </c>
-      <c r="E112" s="7" t="n"/>
-      <c r="F112" s="8" t="n"/>
-      <c r="G112" s="6" t="inlineStr">
+      <c r="E103" s="10" t="n"/>
+      <c r="F103" s="11" t="n"/>
+      <c r="G103" s="15" t="inlineStr">
         <is>
           <t>THE HIGHER BET, THE HIGHER CHANCES TO TRIGGER OP JACKPOT FEATURE.</t>
         </is>
       </c>
-      <c r="H112" s="7" t="n"/>
-      <c r="I112" s="8" t="n"/>
-    </row>
-    <row r="114">
-      <c r="B114" s="3" t="inlineStr">
+      <c r="H103" s="10" t="n"/>
+      <c r="I103" s="11" t="n"/>
+    </row>
+    <row r="104"/>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="B105" s="9" t="inlineStr">
         <is>
           <t>LINES / WAYS</t>
         </is>
       </c>
-    </row>
-    <row r="115">
-      <c r="B115" s="4" t="inlineStr">
+      <c r="C105" s="10" t="n"/>
+      <c r="D105" s="10" t="n"/>
+      <c r="E105" s="10" t="n"/>
+      <c r="F105" s="10" t="n"/>
+      <c r="G105" s="10" t="n"/>
+      <c r="H105" s="10" t="n"/>
+      <c r="I105" s="11" t="n"/>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="B106" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
+      <c r="C106" s="12" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="D106" s="13" t="inlineStr">
         <is>
           <t>繁中</t>
         </is>
       </c>
-      <c r="G115" s="5" t="inlineStr">
+      <c r="E106" s="10" t="n"/>
+      <c r="F106" s="11" t="n"/>
+      <c r="G106" s="13" t="inlineStr">
         <is>
           <t>英文</t>
         </is>
       </c>
-    </row>
-    <row r="116">
-      <c r="B116" s="6" t="n">
+      <c r="H106" s="10" t="n"/>
+      <c r="I106" s="11" t="n"/>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="B107" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C116" s="6" t="inlineStr">
+      <c r="C107" s="14" t="inlineStr">
         <is>
           <t>主要標題</t>
         </is>
       </c>
-      <c r="D116" s="6" t="inlineStr">
+      <c r="D107" s="15" t="inlineStr">
         <is>
           <t>最多路數</t>
         </is>
       </c>
-      <c r="E116" s="7" t="n"/>
-      <c r="F116" s="8" t="n"/>
-      <c r="G116" s="6" t="inlineStr">
+      <c r="E107" s="10" t="n"/>
+      <c r="F107" s="11" t="n"/>
+      <c r="G107" s="15" t="inlineStr">
         <is>
           <t>MAXIMUM WAYS</t>
         </is>
       </c>
-      <c r="H116" s="7" t="n"/>
-      <c r="I116" s="8" t="n"/>
-    </row>
-    <row r="117">
-      <c r="B117" s="6" t="n">
+      <c r="H107" s="10" t="n"/>
+      <c r="I107" s="11" t="n"/>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="B108" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C117" s="6" t="inlineStr">
+      <c r="C108" s="14" t="inlineStr">
         <is>
           <t>規則說明</t>
         </is>
       </c>
-      <c r="D117" s="6" t="inlineStr">
+      <c r="D108" s="15" t="inlineStr">
         <is>
           <t>▪ 所有符號必須由最左至右連續出現，方可獲獎。</t>
         </is>
       </c>
-      <c r="E117" s="7" t="n"/>
-      <c r="F117" s="8" t="n"/>
-      <c r="G117" s="6" t="inlineStr">
+      <c r="E108" s="10" t="n"/>
+      <c r="F108" s="11" t="n"/>
+      <c r="G108" s="15" t="inlineStr">
         <is>
           <t>▪ ALL WINS ARE FROM LEFTMOST TO RIGHT ONLY.</t>
         </is>
       </c>
-      <c r="H117" s="7" t="n"/>
-      <c r="I117" s="8" t="n"/>
-    </row>
-    <row r="118">
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>▪ 當同一路有多種獲獎組合，僅會賠付最高的獲獎組合。</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="n"/>
-      <c r="F118" s="8" t="n"/>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>▪ ONLY THE HIGHEST WIN IS PAID WHEN THERE IS MORE THAN ONE WINNING COMBINATION WITH A CERTAIN SYMBOL.</t>
-        </is>
-      </c>
-      <c r="H118" s="7" t="n"/>
-      <c r="I118" s="8" t="n"/>
-    </row>
-    <row r="119">
-      <c r="D119" s="6" t="inlineStr">
+      <c r="H108" s="10" t="n"/>
+      <c r="I108" s="11" t="n"/>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="B109" s="18" t="n"/>
+      <c r="C109" s="18" t="n"/>
+      <c r="D109" s="15" t="inlineStr">
         <is>
           <t>▪ 遊戲設定 = 最多 {1,024} 路。</t>
         </is>
       </c>
-      <c r="E119" s="7" t="n"/>
-      <c r="F119" s="8" t="n"/>
-      <c r="G119" s="6" t="inlineStr">
+      <c r="E109" s="10" t="n"/>
+      <c r="F109" s="11" t="n"/>
+      <c r="G109" s="15" t="inlineStr">
         <is>
           <t>▪ GAME SETTING = {1,024} MAXIMUM WAYS.</t>
         </is>
       </c>
-      <c r="H119" s="7" t="n"/>
-      <c r="I119" s="8" t="n"/>
-    </row>
-    <row r="120">
-      <c r="D120" s="6" t="inlineStr">
+      <c r="H109" s="10" t="n"/>
+      <c r="I109" s="11" t="n"/>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="B110" s="18" t="n"/>
+      <c r="C110" s="18" t="n"/>
+      <c r="D110" s="15" t="inlineStr">
         <is>
           <t>[走線圖- 1,024 MAX WAYS]</t>
         </is>
       </c>
-      <c r="E120" s="7" t="n"/>
-      <c r="F120" s="8" t="n"/>
-      <c r="G120" s="6" t="inlineStr">
+      <c r="E110" s="10" t="n"/>
+      <c r="F110" s="11" t="n"/>
+      <c r="G110" s="15" t="inlineStr">
         <is>
           <t>[走線圖- 1,024 MAX WAYS]</t>
         </is>
       </c>
-      <c r="H120" s="7" t="n"/>
-      <c r="I120" s="8" t="n"/>
-    </row>
-    <row r="121">
-      <c r="D121" s="6" t="inlineStr">
+      <c r="H110" s="10" t="n"/>
+      <c r="I110" s="11" t="n"/>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="B111" s="18" t="n"/>
+      <c r="C111" s="18" t="n"/>
+      <c r="D111" s="15" t="inlineStr">
         <is>
           <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
         </is>
       </c>
-      <c r="E121" s="7" t="n"/>
-      <c r="F121" s="8" t="n"/>
-      <c r="G121" s="6" t="inlineStr">
+      <c r="E111" s="10" t="n"/>
+      <c r="F111" s="11" t="n"/>
+      <c r="G111" s="15" t="inlineStr">
         <is>
           <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
         </is>
       </c>
-      <c r="H121" s="7" t="n"/>
-      <c r="I121" s="8" t="n"/>
-    </row>
-    <row r="122">
-      <c r="D122" s="6" t="inlineStr">
+      <c r="H111" s="10" t="n"/>
+      <c r="I111" s="11" t="n"/>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="B112" s="16" t="n"/>
+      <c r="C112" s="16" t="n"/>
+      <c r="D112" s="15" t="inlineStr">
         <is>
           <t>[走線圖-NO WIN]</t>
         </is>
       </c>
-      <c r="E122" s="7" t="n"/>
-      <c r="F122" s="8" t="n"/>
-      <c r="G122" s="6" t="inlineStr">
+      <c r="E112" s="10" t="n"/>
+      <c r="F112" s="11" t="n"/>
+      <c r="G112" s="15" t="inlineStr">
         <is>
           <t>[走線圖-NO WIN]</t>
         </is>
       </c>
-      <c r="H122" s="7" t="n"/>
-      <c r="I122" s="8" t="n"/>
-    </row>
-    <row r="124">
-      <c r="B124" s="3" t="inlineStr">
+      <c r="H112" s="10" t="n"/>
+      <c r="I112" s="11" t="n"/>
+    </row>
+    <row r="113"/>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="B114" s="9" t="inlineStr">
         <is>
           <t>GAME RULE</t>
         </is>
       </c>
-    </row>
-    <row r="125">
-      <c r="B125" s="4" t="inlineStr">
+      <c r="C114" s="10" t="n"/>
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="10" t="n"/>
+      <c r="F114" s="10" t="n"/>
+      <c r="G114" s="10" t="n"/>
+      <c r="H114" s="10" t="n"/>
+      <c r="I114" s="11" t="n"/>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="B115" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="C125" s="4" t="inlineStr">
+      <c r="C115" s="12" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="D115" s="13" t="inlineStr">
         <is>
           <t>繁中</t>
         </is>
       </c>
-      <c r="G125" s="5" t="inlineStr">
+      <c r="E115" s="10" t="n"/>
+      <c r="F115" s="11" t="n"/>
+      <c r="G115" s="13" t="inlineStr">
         <is>
           <t>英文</t>
         </is>
       </c>
-    </row>
-    <row r="126">
-      <c r="B126" s="6" t="n">
+      <c r="H115" s="10" t="n"/>
+      <c r="I115" s="11" t="n"/>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="B116" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C126" s="6" t="inlineStr">
+      <c r="C116" s="14" t="inlineStr">
         <is>
           <t>主要標題</t>
         </is>
       </c>
-      <c r="D126" s="6" t="inlineStr">
+      <c r="D116" s="15" t="inlineStr">
         <is>
           <t>遊戲規則</t>
         </is>
       </c>
-      <c r="E126" s="7" t="n"/>
-      <c r="F126" s="8" t="n"/>
-      <c r="G126" s="6" t="inlineStr">
+      <c r="E116" s="10" t="n"/>
+      <c r="F116" s="11" t="n"/>
+      <c r="G116" s="15" t="inlineStr">
         <is>
           <t>GAME RULES</t>
         </is>
       </c>
-      <c r="H126" s="7" t="n"/>
-      <c r="I126" s="8" t="n"/>
-    </row>
-    <row r="127">
-      <c r="B127" s="6" t="n">
+      <c r="H116" s="10" t="n"/>
+      <c r="I116" s="11" t="n"/>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="B117" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C127" s="6" t="inlineStr">
+      <c r="C117" s="14" t="inlineStr">
         <is>
           <t>規則說明</t>
         </is>
       </c>
-      <c r="D127" s="6" t="inlineStr">
+      <c r="D117" s="15" t="inlineStr">
         <is>
           <t>▪ 選擇您想要玩的投注選項。</t>
         </is>
       </c>
-      <c r="E127" s="7" t="n"/>
-      <c r="F127" s="8" t="n"/>
-      <c r="G127" s="6" t="inlineStr">
+      <c r="E117" s="10" t="n"/>
+      <c r="F117" s="11" t="n"/>
+      <c r="G117" s="15" t="inlineStr">
         <is>
           <t>▪ SELECT BET OPTION YOU WISH TO PLAY.</t>
         </is>
       </c>
-      <c r="H127" s="7" t="n"/>
-      <c r="I127" s="8" t="n"/>
-    </row>
-    <row r="128">
-      <c r="D128" s="6" t="inlineStr">
+      <c r="H117" s="10" t="n"/>
+      <c r="I117" s="11" t="n"/>
+    </row>
+    <row r="118" ht="31.5" customHeight="1">
+      <c r="B118" s="18" t="n"/>
+      <c r="C118" s="18" t="n"/>
+      <c r="D118" s="15" t="inlineStr">
         <is>
           <t>▪ 所有中獎金額均乘以投注選項，除非是累積獎。</t>
         </is>
       </c>
-      <c r="E128" s="7" t="n"/>
-      <c r="F128" s="8" t="n"/>
-      <c r="G128" s="6" t="inlineStr">
+      <c r="E118" s="10" t="n"/>
+      <c r="F118" s="11" t="n"/>
+      <c r="G118" s="15" t="inlineStr">
         <is>
           <t>▪ ALL WINS ARE MULTIPLIED BY BET OPTION EXCEPT PROGRESSIVES BONUSES.</t>
         </is>
       </c>
-      <c r="H128" s="7" t="n"/>
-      <c r="I128" s="8" t="n"/>
-    </row>
-    <row r="129">
-      <c r="D129" s="6" t="inlineStr">
+      <c r="H118" s="10" t="n"/>
+      <c r="I118" s="11" t="n"/>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="B119" s="18" t="n"/>
+      <c r="C119" s="18" t="n"/>
+      <c r="D119" s="15" t="inlineStr">
         <is>
           <t>▪ 遊戲出現故障時，所有賠付與遊戲結果均視為無效。</t>
         </is>
       </c>
-      <c r="E129" s="7" t="n"/>
-      <c r="F129" s="8" t="n"/>
-      <c r="G129" s="6" t="inlineStr">
+      <c r="E119" s="10" t="n"/>
+      <c r="F119" s="11" t="n"/>
+      <c r="G119" s="15" t="inlineStr">
         <is>
           <t>▪ MALFUNCTION VOIDS ALL PAYS AND PLAYS.</t>
         </is>
       </c>
-      <c r="H129" s="7" t="n"/>
-      <c r="I129" s="8" t="n"/>
-    </row>
-    <row r="130">
-      <c r="D130" s="6" t="inlineStr">
+      <c r="H119" s="10" t="n"/>
+      <c r="I119" s="11" t="n"/>
+    </row>
+    <row r="120" ht="47.25" customHeight="1">
+      <c r="B120" s="16" t="n"/>
+      <c r="C120" s="16" t="n"/>
+      <c r="D120" s="15" t="inlineStr">
         <is>
           <t>▪ 若玩家在免費遊戲期間中斷連線，系統將自動完成該局結算，並將中獎金額加入餘額。</t>
         </is>
       </c>
-      <c r="E130" s="7" t="n"/>
-      <c r="F130" s="8" t="n"/>
-      <c r="G130" s="6" t="inlineStr">
+      <c r="E120" s="10" t="n"/>
+      <c r="F120" s="11" t="n"/>
+      <c r="G120" s="15" t="inlineStr">
         <is>
           <t>▪ IF THE PLAYER LOSES CONNECTION DURING THE FREE GAME FEATURE, THE SYSTEM WILL COMPLETE THE RESULT AUTOMATICALLY AND ADD ANY WINNINGS TO THE BALANCE.</t>
         </is>
       </c>
-      <c r="H130" s="7" t="n"/>
-      <c r="I130" s="8" t="n"/>
+      <c r="H120" s="10" t="n"/>
+      <c r="I120" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="164">
+  <mergeCells count="205">
     <mergeCell ref="G38:I38"/>
+    <mergeCell ref="B53:B55"/>
     <mergeCell ref="G103:I103"/>
     <mergeCell ref="D11:F11"/>
+    <mergeCell ref="C79:C80"/>
     <mergeCell ref="G112:I112"/>
     <mergeCell ref="G13:I13"/>
     <mergeCell ref="D116:F116"/>
@@ -2703,13 +2936,13 @@
     <mergeCell ref="G118:I118"/>
     <mergeCell ref="D66:F66"/>
     <mergeCell ref="G87:I87"/>
-    <mergeCell ref="G127:I127"/>
-    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="C10:C11"/>
     <mergeCell ref="D53:F53"/>
+    <mergeCell ref="C45:C48"/>
     <mergeCell ref="D47:F47"/>
     <mergeCell ref="G95:I95"/>
+    <mergeCell ref="B105:I105"/>
     <mergeCell ref="G89:I89"/>
-    <mergeCell ref="G104:I104"/>
     <mergeCell ref="D37:F37"/>
     <mergeCell ref="D102:F102"/>
     <mergeCell ref="G65:I65"/>
@@ -2718,54 +2951,68 @@
     <mergeCell ref="G73:I73"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="G88:I88"/>
+    <mergeCell ref="D92:F92"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="D39:F39"/>
-    <mergeCell ref="G129:I129"/>
     <mergeCell ref="G63:I63"/>
     <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="B82:I82"/>
+    <mergeCell ref="G90:I90"/>
     <mergeCell ref="D94:F94"/>
-    <mergeCell ref="D129:F129"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="C60:C63"/>
     <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="G52:I52"/>
     <mergeCell ref="D119:F119"/>
+    <mergeCell ref="G115:I115"/>
     <mergeCell ref="G36:I36"/>
-    <mergeCell ref="D128:F128"/>
     <mergeCell ref="G107:I107"/>
     <mergeCell ref="D80:F80"/>
+    <mergeCell ref="C15:C25"/>
+    <mergeCell ref="B5:I5"/>
     <mergeCell ref="D96:F96"/>
-    <mergeCell ref="D105:F105"/>
-    <mergeCell ref="G122:I122"/>
+    <mergeCell ref="B76:I76"/>
     <mergeCell ref="G101:I101"/>
     <mergeCell ref="D120:F120"/>
+    <mergeCell ref="G6:I6"/>
     <mergeCell ref="G37:I37"/>
     <mergeCell ref="D107:F107"/>
+    <mergeCell ref="G78:I78"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="G92:I92"/>
     <mergeCell ref="G30:I30"/>
+    <mergeCell ref="D43:F43"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="D106:F106"/>
     <mergeCell ref="G80:I80"/>
     <mergeCell ref="D93:F93"/>
     <mergeCell ref="G55:I55"/>
+    <mergeCell ref="C31:C32"/>
     <mergeCell ref="G64:I64"/>
     <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D130:F130"/>
-    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="B15:B25"/>
     <mergeCell ref="D83:F83"/>
+    <mergeCell ref="G51:I51"/>
     <mergeCell ref="D117:F117"/>
     <mergeCell ref="D55:F55"/>
     <mergeCell ref="G54:I54"/>
     <mergeCell ref="G119:I119"/>
     <mergeCell ref="G32:I32"/>
+    <mergeCell ref="B60:B63"/>
     <mergeCell ref="D67:F67"/>
     <mergeCell ref="D110:F110"/>
     <mergeCell ref="D85:F85"/>
     <mergeCell ref="G106:I106"/>
     <mergeCell ref="D54:F54"/>
     <mergeCell ref="D60:F60"/>
-    <mergeCell ref="G56:I56"/>
-    <mergeCell ref="G81:I81"/>
     <mergeCell ref="G96:I96"/>
     <mergeCell ref="D100:F100"/>
-    <mergeCell ref="G105:I105"/>
+    <mergeCell ref="G43:I43"/>
     <mergeCell ref="D109:F109"/>
+    <mergeCell ref="G71:I71"/>
+    <mergeCell ref="B79:B80"/>
     <mergeCell ref="G120:I120"/>
     <mergeCell ref="G98:I98"/>
     <mergeCell ref="D31:F31"/>
@@ -2773,90 +3020,115 @@
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="D111:F111"/>
+    <mergeCell ref="B114:I114"/>
+    <mergeCell ref="B45:B48"/>
     <mergeCell ref="D108:F108"/>
     <mergeCell ref="D86:F86"/>
-    <mergeCell ref="G82:I82"/>
+    <mergeCell ref="B50:I50"/>
     <mergeCell ref="D95:F95"/>
-    <mergeCell ref="D104:F104"/>
+    <mergeCell ref="B31:B32"/>
     <mergeCell ref="G10:I10"/>
     <mergeCell ref="G66:I66"/>
+    <mergeCell ref="B65:B67"/>
     <mergeCell ref="D32:F32"/>
     <mergeCell ref="G53:I53"/>
     <mergeCell ref="G93:I93"/>
     <mergeCell ref="D97:F97"/>
+    <mergeCell ref="C72:C74"/>
     <mergeCell ref="G74:I74"/>
     <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G68:I68"/>
+    <mergeCell ref="D78:F78"/>
     <mergeCell ref="G83:I83"/>
     <mergeCell ref="D87:F87"/>
     <mergeCell ref="G108:I108"/>
-    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="G58:I58"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="C95:C103"/>
     <mergeCell ref="G45:I45"/>
     <mergeCell ref="G110:I110"/>
+    <mergeCell ref="D58:F58"/>
     <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D121:F121"/>
+    <mergeCell ref="G29:I29"/>
     <mergeCell ref="G100:I100"/>
+    <mergeCell ref="B95:B103"/>
     <mergeCell ref="D73:F73"/>
     <mergeCell ref="G94:I94"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="G47:I47"/>
     <mergeCell ref="G109:I109"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="D82:F82"/>
     <mergeCell ref="G44:I44"/>
     <mergeCell ref="G84:I84"/>
+    <mergeCell ref="B69:I69"/>
     <mergeCell ref="G31:I31"/>
     <mergeCell ref="G46:I46"/>
     <mergeCell ref="G102:I102"/>
+    <mergeCell ref="D35:F35"/>
     <mergeCell ref="G40:I40"/>
+    <mergeCell ref="C108:C112"/>
     <mergeCell ref="G111:I111"/>
     <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D59:F59"/>
     <mergeCell ref="G12:I12"/>
+    <mergeCell ref="D115:F115"/>
     <mergeCell ref="G72:I72"/>
     <mergeCell ref="G86:I86"/>
     <mergeCell ref="D99:F99"/>
+    <mergeCell ref="G70:I70"/>
     <mergeCell ref="D84:F84"/>
     <mergeCell ref="D36:F36"/>
     <mergeCell ref="G97:I97"/>
     <mergeCell ref="D45:F45"/>
+    <mergeCell ref="C37:C40"/>
     <mergeCell ref="D101:F101"/>
+    <mergeCell ref="D6:F6"/>
     <mergeCell ref="G7:I7"/>
+    <mergeCell ref="D77:F77"/>
     <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G128:I128"/>
     <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="C85:C93"/>
+    <mergeCell ref="D70:F70"/>
     <mergeCell ref="D48:F48"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="G121:I121"/>
+    <mergeCell ref="B108:B112"/>
     <mergeCell ref="D72:F72"/>
     <mergeCell ref="D103:F103"/>
     <mergeCell ref="D112:F112"/>
+    <mergeCell ref="B117:B120"/>
     <mergeCell ref="D62:F62"/>
     <mergeCell ref="D118:F118"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D127:F127"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="G91:I91"/>
+    <mergeCell ref="B85:B93"/>
     <mergeCell ref="D64:F64"/>
     <mergeCell ref="D38:F38"/>
     <mergeCell ref="G85:I85"/>
     <mergeCell ref="D89:F89"/>
     <mergeCell ref="D98:F98"/>
     <mergeCell ref="G99:I99"/>
+    <mergeCell ref="C117:C120"/>
     <mergeCell ref="G60:I60"/>
+    <mergeCell ref="B34:I34"/>
     <mergeCell ref="D79:F79"/>
-    <mergeCell ref="G75:I75"/>
+    <mergeCell ref="B28:I28"/>
     <mergeCell ref="D88:F88"/>
-    <mergeCell ref="G130:I130"/>
+    <mergeCell ref="G59:I59"/>
     <mergeCell ref="D63:F63"/>
+    <mergeCell ref="G77:I77"/>
     <mergeCell ref="G11:I11"/>
     <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D81:F81"/>
     <mergeCell ref="G117:I117"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="C65:C67"/>
     <mergeCell ref="G67:I67"/>
     <mergeCell ref="D65:F65"/>
     <mergeCell ref="G61:I61"/>
-    <mergeCell ref="G126:I126"/>
     <mergeCell ref="G39:I39"/>
     <mergeCell ref="G48:I48"/>
+    <mergeCell ref="D52:F52"/>
     <mergeCell ref="G116:I116"/>
-    <mergeCell ref="D49:F49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Slots/H045_超級鑽石/文件/101015_Help.xlsx
+++ b/Slots/H045_超級鑽石/文件/101015_Help.xlsx
@@ -658,7 +658,7 @@
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
     <col width="8.69921875" customWidth="1" min="2" max="2"/>
-    <col width="9.8984375" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -667,14 +667,15 @@
     <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>11.Help</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>說明頁</t>
@@ -745,7 +746,7 @@
       <c r="H7" s="10" t="n"/>
       <c r="I7" s="11" t="n"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" ht="31.5" customHeight="1">
       <c r="B8" s="14" t="n">
         <v>2</v>
       </c>
@@ -793,7 +794,7 @@
       <c r="H9" s="10" t="n"/>
       <c r="I9" s="11" t="n"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" ht="31.5" customHeight="1">
       <c r="B10" s="14" t="n">
         <v>4</v>
       </c>
@@ -1281,7 +1282,7 @@
       <c r="H30" s="10" t="n"/>
       <c r="I30" s="11" t="n"/>
     </row>
-    <row r="31" ht="47.25" customHeight="1">
+    <row r="31" ht="63" customHeight="1">
       <c r="B31" s="14" t="n">
         <v>2</v>
       </c>
@@ -1412,7 +1413,7 @@
       <c r="H37" s="10" t="n"/>
       <c r="I37" s="11" t="n"/>
     </row>
-    <row r="38" ht="47.25" customHeight="1">
+    <row r="38" ht="78.75" customHeight="1">
       <c r="B38" s="18" t="n"/>
       <c r="C38" s="18" t="n"/>
       <c r="D38" s="15" t="inlineStr">
@@ -1430,7 +1431,7 @@
       <c r="H38" s="10" t="n"/>
       <c r="I38" s="11" t="n"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" ht="31.5" customHeight="1">
       <c r="B39" s="18" t="n"/>
       <c r="C39" s="18" t="n"/>
       <c r="D39" s="15" t="inlineStr">
@@ -1448,7 +1449,7 @@
       <c r="H39" s="10" t="n"/>
       <c r="I39" s="11" t="n"/>
     </row>
-    <row r="40" ht="63" customHeight="1">
+    <row r="40" ht="78.75" customHeight="1">
       <c r="B40" s="16" t="n"/>
       <c r="C40" s="16" t="n"/>
       <c r="D40" s="15" t="inlineStr">
@@ -1531,7 +1532,7 @@
       <c r="H44" s="10" t="n"/>
       <c r="I44" s="11" t="n"/>
     </row>
-    <row r="45" ht="31.5" customHeight="1">
+    <row r="45" ht="47.25" customHeight="1">
       <c r="B45" s="14" t="n">
         <v>2</v>
       </c>
@@ -1573,7 +1574,7 @@
       <c r="H46" s="10" t="n"/>
       <c r="I46" s="11" t="n"/>
     </row>
-    <row r="47" ht="47.25" customHeight="1">
+    <row r="47" ht="78.75" customHeight="1">
       <c r="B47" s="18" t="n"/>
       <c r="C47" s="18" t="n"/>
       <c r="D47" s="15" t="inlineStr">
@@ -1674,7 +1675,7 @@
       <c r="H52" s="10" t="n"/>
       <c r="I52" s="11" t="n"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" ht="31.5" customHeight="1">
       <c r="B53" s="14" t="n">
         <v>2</v>
       </c>
@@ -1698,7 +1699,7 @@
       <c r="H53" s="10" t="n"/>
       <c r="I53" s="11" t="n"/>
     </row>
-    <row r="54" ht="47.25" customHeight="1">
+    <row r="54" ht="63" customHeight="1">
       <c r="B54" s="18" t="n"/>
       <c r="C54" s="18" t="n"/>
       <c r="D54" s="15" t="inlineStr">
@@ -1823,7 +1824,7 @@
       <c r="H60" s="10" t="n"/>
       <c r="I60" s="11" t="n"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" ht="31.5" customHeight="1">
       <c r="B61" s="18" t="n"/>
       <c r="C61" s="18" t="n"/>
       <c r="D61" s="15" t="inlineStr">
@@ -1841,7 +1842,7 @@
       <c r="H61" s="10" t="n"/>
       <c r="I61" s="11" t="n"/>
     </row>
-    <row r="62" ht="31.5" customHeight="1">
+    <row r="62" ht="47.25" customHeight="1">
       <c r="B62" s="18" t="n"/>
       <c r="C62" s="18" t="n"/>
       <c r="D62" s="15" t="inlineStr">
@@ -1859,7 +1860,7 @@
       <c r="H62" s="10" t="n"/>
       <c r="I62" s="11" t="n"/>
     </row>
-    <row r="63" ht="31.5" customHeight="1">
+    <row r="63" ht="47.25" customHeight="1">
       <c r="B63" s="16" t="n"/>
       <c r="C63" s="16" t="n"/>
       <c r="D63" s="15" t="inlineStr">
@@ -1925,7 +1926,7 @@
       <c r="H65" s="10" t="n"/>
       <c r="I65" s="11" t="n"/>
     </row>
-    <row r="66" ht="47.25" customHeight="1">
+    <row r="66" ht="63" customHeight="1">
       <c r="B66" s="18" t="n"/>
       <c r="C66" s="18" t="n"/>
       <c r="D66" s="15" t="inlineStr">
@@ -2026,7 +2027,7 @@
       <c r="H71" s="10" t="n"/>
       <c r="I71" s="11" t="n"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" ht="31.5" customHeight="1">
       <c r="B72" s="14" t="n">
         <v>2</v>
       </c>
@@ -2050,7 +2051,7 @@
       <c r="H72" s="10" t="n"/>
       <c r="I72" s="11" t="n"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" ht="31.5" customHeight="1">
       <c r="B73" s="18" t="n"/>
       <c r="C73" s="18" t="n"/>
       <c r="D73" s="15" t="inlineStr">
@@ -2068,7 +2069,7 @@
       <c r="H73" s="10" t="n"/>
       <c r="I73" s="11" t="n"/>
     </row>
-    <row r="74" ht="31.5" customHeight="1">
+    <row r="74" ht="47.25" customHeight="1">
       <c r="B74" s="16" t="n"/>
       <c r="C74" s="16" t="n"/>
       <c r="D74" s="15" t="inlineStr">
@@ -2151,7 +2152,7 @@
       <c r="H78" s="10" t="n"/>
       <c r="I78" s="11" t="n"/>
     </row>
-    <row r="79" ht="31.5" customHeight="1">
+    <row r="79" ht="47.25" customHeight="1">
       <c r="B79" s="14" t="n">
         <v>2</v>
       </c>
@@ -2258,7 +2259,7 @@
       <c r="H84" s="10" t="n"/>
       <c r="I84" s="11" t="n"/>
     </row>
-    <row r="85" ht="31.5" customHeight="1">
+    <row r="85" ht="47.25" customHeight="1">
       <c r="B85" s="14" t="n">
         <v>2</v>
       </c>
@@ -2282,7 +2283,7 @@
       <c r="H85" s="10" t="n"/>
       <c r="I85" s="11" t="n"/>
     </row>
-    <row r="86" ht="31.5" customHeight="1">
+    <row r="86" ht="47.25" customHeight="1">
       <c r="B86" s="18" t="n"/>
       <c r="C86" s="18" t="n"/>
       <c r="D86" s="15" t="inlineStr">
@@ -2318,7 +2319,7 @@
       <c r="H87" s="10" t="n"/>
       <c r="I87" s="11" t="n"/>
     </row>
-    <row r="88" ht="31.5" customHeight="1">
+    <row r="88" ht="47.25" customHeight="1">
       <c r="B88" s="18" t="n"/>
       <c r="C88" s="18" t="n"/>
       <c r="D88" s="15" t="inlineStr">
@@ -2336,7 +2337,7 @@
       <c r="H88" s="10" t="n"/>
       <c r="I88" s="11" t="n"/>
     </row>
-    <row r="89" ht="47.25" customHeight="1">
+    <row r="89" ht="63" customHeight="1">
       <c r="B89" s="18" t="n"/>
       <c r="C89" s="18" t="n"/>
       <c r="D89" s="15" t="inlineStr">
@@ -2354,7 +2355,7 @@
       <c r="H89" s="10" t="n"/>
       <c r="I89" s="11" t="n"/>
     </row>
-    <row r="90" ht="47.25" customHeight="1">
+    <row r="90" ht="63" customHeight="1">
       <c r="B90" s="18" t="n"/>
       <c r="C90" s="18" t="n"/>
       <c r="D90" s="15" t="inlineStr">
@@ -2474,7 +2475,7 @@
       <c r="H95" s="10" t="n"/>
       <c r="I95" s="11" t="n"/>
     </row>
-    <row r="96" ht="31.5" customHeight="1">
+    <row r="96" ht="47.25" customHeight="1">
       <c r="B96" s="18" t="n"/>
       <c r="C96" s="18" t="n"/>
       <c r="D96" s="15" t="inlineStr">
@@ -2510,7 +2511,7 @@
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="11" t="n"/>
     </row>
-    <row r="98" ht="31.5" customHeight="1">
+    <row r="98" ht="47.25" customHeight="1">
       <c r="B98" s="18" t="n"/>
       <c r="C98" s="18" t="n"/>
       <c r="D98" s="15" t="inlineStr">
@@ -2528,7 +2529,7 @@
       <c r="H98" s="10" t="n"/>
       <c r="I98" s="11" t="n"/>
     </row>
-    <row r="99" ht="47.25" customHeight="1">
+    <row r="99" ht="63" customHeight="1">
       <c r="B99" s="18" t="n"/>
       <c r="C99" s="18" t="n"/>
       <c r="D99" s="15" t="inlineStr">
@@ -2546,7 +2547,7 @@
       <c r="H99" s="10" t="n"/>
       <c r="I99" s="11" t="n"/>
     </row>
-    <row r="100" ht="47.25" customHeight="1">
+    <row r="100" ht="63" customHeight="1">
       <c r="B100" s="18" t="n"/>
       <c r="C100" s="18" t="n"/>
       <c r="D100" s="15" t="inlineStr">
@@ -2683,7 +2684,7 @@
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="11" t="n"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" ht="31.5" customHeight="1">
       <c r="B108" s="14" t="n">
         <v>2</v>
       </c>
@@ -2904,7 +2905,7 @@
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="11" t="n"/>
     </row>
-    <row r="120" ht="47.25" customHeight="1">
+    <row r="120" ht="63" customHeight="1">
       <c r="B120" s="16" t="n"/>
       <c r="C120" s="16" t="n"/>
       <c r="D120" s="15" t="inlineStr">
@@ -2923,7 +2924,7 @@
       <c r="I120" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="205">
+  <mergeCells count="207">
     <mergeCell ref="G38:I38"/>
     <mergeCell ref="B53:B55"/>
     <mergeCell ref="G103:I103"/>
@@ -3035,6 +3036,7 @@
     <mergeCell ref="G93:I93"/>
     <mergeCell ref="D97:F97"/>
     <mergeCell ref="C72:C74"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="G74:I74"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D78:F78"/>
@@ -3048,6 +3050,7 @@
     <mergeCell ref="G45:I45"/>
     <mergeCell ref="G110:I110"/>
     <mergeCell ref="D58:F58"/>
+    <mergeCell ref="A1:I2"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="G100:I100"/>

--- a/Slots/H045_超級鑽石/文件/101015_Help.xlsx
+++ b/Slots/H045_超級鑽石/文件/101015_Help.xlsx
@@ -653,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -2427,234 +2427,227 @@
       <c r="H93" s="10" t="n"/>
       <c r="I93" s="11" t="n"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
-      <c r="B94" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C94" s="14" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
-      <c r="D94" s="15" t="inlineStr">
-        <is>
-          <t>OP JACKPOT</t>
-        </is>
-      </c>
-      <c r="E94" s="10" t="n"/>
-      <c r="F94" s="11" t="n"/>
-      <c r="G94" s="15" t="inlineStr">
-        <is>
-          <t>OP JACKPOT</t>
-        </is>
-      </c>
-      <c r="H94" s="10" t="n"/>
-      <c r="I94" s="11" t="n"/>
-    </row>
-    <row r="95" ht="31.5" customHeight="1">
-      <c r="B95" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="C95" s="14" t="inlineStr">
-        <is>
-          <t>規則說明</t>
-        </is>
-      </c>
-      <c r="D95" s="15" t="inlineStr">
-        <is>
-          <t>在游戏中，OP JACKPOT 特色由特色转轮上 [C1] 随机触发。</t>
-        </is>
-      </c>
+    <row r="94"/>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>LINES / WAYS</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="n"/>
+      <c r="D95" s="10" t="n"/>
       <c r="E95" s="10" t="n"/>
-      <c r="F95" s="11" t="n"/>
-      <c r="G95" s="15" t="inlineStr">
-        <is>
-          <t>OP JACKPOT FEATURE IS TRIGGERED RANDOMLY BY {1} OR MORE [C1] ON THE REELS.</t>
-        </is>
-      </c>
+      <c r="F95" s="10" t="n"/>
+      <c r="G95" s="10" t="n"/>
       <c r="H95" s="10" t="n"/>
       <c r="I95" s="11" t="n"/>
     </row>
-    <row r="96" ht="47.25" customHeight="1">
-      <c r="B96" s="18" t="n"/>
-      <c r="C96" s="18" t="n"/>
-      <c r="D96" s="15" t="inlineStr">
-        <is>
-          <t>OP JACKPOT 特色会在画面中出现 {12} 个 [幣]，其中包括 [GRAND]、[MAJOR]、[MINOR] 及 [MINI]。</t>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D96" s="13" t="inlineStr">
+        <is>
+          <t>繁中</t>
         </is>
       </c>
       <c r="E96" s="10" t="n"/>
       <c r="F96" s="11" t="n"/>
-      <c r="G96" s="15" t="inlineStr">
-        <is>
-          <t>DURING OP JACKPOT FEATURE, THERE ARE {12} [COIN] WHICH CONSIST OF [GRAND], [MAJOR], [MINOR] AND [MINI].</t>
+      <c r="G96" s="13" t="inlineStr">
+        <is>
+          <t>英文</t>
         </is>
       </c>
       <c r="H96" s="10" t="n"/>
       <c r="I96" s="11" t="n"/>
     </row>
-    <row r="97" ht="31.5" customHeight="1">
-      <c r="B97" s="18" t="n"/>
-      <c r="C97" s="18" t="n"/>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="B97" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>主要標題</t>
+        </is>
+      </c>
       <c r="D97" s="15" t="inlineStr">
         <is>
-          <t>选择 {1} 个 [幣] 以揭示 [GRAND]、[MAJOR]、[MINOR] 或 [MINI]。</t>
+          <t>最多路數</t>
         </is>
       </c>
       <c r="E97" s="10" t="n"/>
       <c r="F97" s="11" t="n"/>
       <c r="G97" s="15" t="inlineStr">
         <is>
-          <t>SELECT A [COIN] TO REVEAL [GRAND], [MAJOR], [MINOR], OR [MINI].</t>
+          <t>MAXIMUM WAYS</t>
         </is>
       </c>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="11" t="n"/>
     </row>
-    <row r="98" ht="47.25" customHeight="1">
-      <c r="B98" s="18" t="n"/>
-      <c r="C98" s="18" t="n"/>
+    <row r="98" ht="31.5" customHeight="1">
+      <c r="B98" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>当玩家获得 {3} 个相同的 OP JACKPOT 特色符号即可获得该 OP JACKPOT 并结算总奖金。</t>
+          <t>▪ 所有符號必須由最左至右連續出現，方可獲獎。</t>
         </is>
       </c>
       <c r="E98" s="10" t="n"/>
       <c r="F98" s="11" t="n"/>
       <c r="G98" s="15" t="inlineStr">
         <is>
-          <t>IF PLAYER GETS {3} SAME JACKPOT SYMBOLS WILL WIN THE JACKPOT AND CALCULATE TOTAL WINNINGS.</t>
+          <t>▪ ALL WINS ARE FROM LEFTMOST TO RIGHT ONLY.</t>
         </is>
       </c>
       <c r="H98" s="10" t="n"/>
       <c r="I98" s="11" t="n"/>
     </row>
-    <row r="99" ht="63" customHeight="1">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="B99" s="18" t="n"/>
       <c r="C99" s="18" t="n"/>
       <c r="D99" s="15" t="inlineStr">
         <is>
-          <t>[GRAND] 为连机累进彩金。单场游戏中，投注选项选择 {2.00} 以上即可解锁 [GRAND]。</t>
+          <t>▪ 遊戲設定 = 最多 {1,024} 路。</t>
         </is>
       </c>
       <c r="E99" s="10" t="n"/>
       <c r="F99" s="11" t="n"/>
       <c r="G99" s="15" t="inlineStr">
         <is>
-          <t>[GRAND] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [GRAND].</t>
+          <t>▪ GAME SETTING = {1,024} MAXIMUM WAYS.</t>
         </is>
       </c>
       <c r="H99" s="10" t="n"/>
       <c r="I99" s="11" t="n"/>
     </row>
-    <row r="100" ht="63" customHeight="1">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="B100" s="18" t="n"/>
       <c r="C100" s="18" t="n"/>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>[MAJOR] 为连机累进彩金。单场游戏中，投注选项选择 {2.00} 以上即可解锁 [MAJOR]。</t>
+          <t>[走線圖- 1,024 MAX WAYS]</t>
         </is>
       </c>
       <c r="E100" s="10" t="n"/>
       <c r="F100" s="11" t="n"/>
       <c r="G100" s="15" t="inlineStr">
         <is>
-          <t>[MAJOR] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [MAJOR].</t>
+          <t>[走線圖- 1,024 MAX WAYS]</t>
         </is>
       </c>
       <c r="H100" s="10" t="n"/>
       <c r="I100" s="11" t="n"/>
     </row>
-    <row r="101" ht="31.5" customHeight="1">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="B101" s="18" t="n"/>
       <c r="C101" s="18" t="n"/>
       <c r="D101" s="15" t="inlineStr">
         <is>
-          <t>[MINOR] 为红利彩金，依照投注选项改变。</t>
+          <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
         </is>
       </c>
       <c r="E101" s="10" t="n"/>
       <c r="F101" s="11" t="n"/>
       <c r="G101" s="15" t="inlineStr">
         <is>
-          <t>[MINOR] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
+          <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
         </is>
       </c>
       <c r="H101" s="10" t="n"/>
       <c r="I101" s="11" t="n"/>
     </row>
-    <row r="102" ht="31.5" customHeight="1">
-      <c r="B102" s="18" t="n"/>
-      <c r="C102" s="18" t="n"/>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="B102" s="16" t="n"/>
+      <c r="C102" s="16" t="n"/>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>[MINI] 为红利彩金，依照投注选项改变。</t>
+          <t>[走線圖-NO WIN]</t>
         </is>
       </c>
       <c r="E102" s="10" t="n"/>
       <c r="F102" s="11" t="n"/>
       <c r="G102" s="15" t="inlineStr">
         <is>
-          <t>[MINI] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
+          <t>[走線圖-NO WIN]</t>
         </is>
       </c>
       <c r="H102" s="10" t="n"/>
       <c r="I102" s="11" t="n"/>
     </row>
-    <row r="103" ht="31.5" customHeight="1">
-      <c r="B103" s="16" t="n"/>
-      <c r="C103" s="16" t="n"/>
-      <c r="D103" s="15" t="inlineStr">
-        <is>
-          <t>玩家投注越高触发 OP JACKPOT 特色的机会越高。</t>
-        </is>
-      </c>
-      <c r="E103" s="10" t="n"/>
-      <c r="F103" s="11" t="n"/>
-      <c r="G103" s="15" t="inlineStr">
-        <is>
-          <t>THE HIGHER BET, THE HIGHER CHANCES TO TRIGGER OP JACKPOT FEATURE.</t>
-        </is>
-      </c>
-      <c r="H103" s="10" t="n"/>
-      <c r="I103" s="11" t="n"/>
-    </row>
-    <row r="104"/>
+    <row r="103"/>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>GAME RULE</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="n"/>
+      <c r="D104" s="10" t="n"/>
+      <c r="E104" s="10" t="n"/>
+      <c r="F104" s="10" t="n"/>
+      <c r="G104" s="10" t="n"/>
+      <c r="H104" s="10" t="n"/>
+      <c r="I104" s="11" t="n"/>
+    </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t>LINES / WAYS</t>
-        </is>
-      </c>
-      <c r="C105" s="10" t="n"/>
-      <c r="D105" s="10" t="n"/>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D105" s="13" t="inlineStr">
+        <is>
+          <t>繁中</t>
+        </is>
+      </c>
       <c r="E105" s="10" t="n"/>
-      <c r="F105" s="10" t="n"/>
-      <c r="G105" s="10" t="n"/>
+      <c r="F105" s="11" t="n"/>
+      <c r="G105" s="13" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
       <c r="H105" s="10" t="n"/>
       <c r="I105" s="11" t="n"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="B106" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C106" s="12" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D106" s="13" t="inlineStr">
-        <is>
-          <t>繁中</t>
+      <c r="B106" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>主要標題</t>
+        </is>
+      </c>
+      <c r="D106" s="15" t="inlineStr">
+        <is>
+          <t>遊戲規則</t>
         </is>
       </c>
       <c r="E106" s="10" t="n"/>
       <c r="F106" s="11" t="n"/>
-      <c r="G106" s="13" t="inlineStr">
-        <is>
-          <t>英文</t>
+      <c r="G106" s="15" t="inlineStr">
+        <is>
+          <t>GAME RULES</t>
         </is>
       </c>
       <c r="H106" s="10" t="n"/>
@@ -2662,47 +2655,41 @@
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="B107" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107" s="14" t="inlineStr">
         <is>
-          <t>主要標題</t>
+          <t>規則說明</t>
         </is>
       </c>
       <c r="D107" s="15" t="inlineStr">
         <is>
-          <t>最多路數</t>
+          <t>▪ 選擇您想要玩的投注選項。</t>
         </is>
       </c>
       <c r="E107" s="10" t="n"/>
       <c r="F107" s="11" t="n"/>
       <c r="G107" s="15" t="inlineStr">
         <is>
-          <t>MAXIMUM WAYS</t>
+          <t>▪ SELECT BET OPTION YOU WISH TO PLAY.</t>
         </is>
       </c>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="11" t="n"/>
     </row>
     <row r="108" ht="31.5" customHeight="1">
-      <c r="B108" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C108" s="14" t="inlineStr">
-        <is>
-          <t>規則說明</t>
-        </is>
-      </c>
+      <c r="B108" s="18" t="n"/>
+      <c r="C108" s="18" t="n"/>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>▪ 所有符號必須由最左至右連續出現，方可獲獎。</t>
+          <t>▪ 所有中獎金額均乘以投注選項，除非是累積獎。</t>
         </is>
       </c>
       <c r="E108" s="10" t="n"/>
       <c r="F108" s="11" t="n"/>
       <c r="G108" s="15" t="inlineStr">
         <is>
-          <t>▪ ALL WINS ARE FROM LEFTMOST TO RIGHT ONLY.</t>
+          <t>▪ ALL WINS ARE MULTIPLIED BY BET OPTION EXCEPT PROGRESSIVES BONUSES.</t>
         </is>
       </c>
       <c r="H108" s="10" t="n"/>
@@ -2713,236 +2700,51 @@
       <c r="C109" s="18" t="n"/>
       <c r="D109" s="15" t="inlineStr">
         <is>
-          <t>▪ 遊戲設定 = 最多 {1,024} 路。</t>
+          <t>▪ 遊戲出現故障時，所有賠付與遊戲結果均視為無效。</t>
         </is>
       </c>
       <c r="E109" s="10" t="n"/>
       <c r="F109" s="11" t="n"/>
       <c r="G109" s="15" t="inlineStr">
         <is>
-          <t>▪ GAME SETTING = {1,024} MAXIMUM WAYS.</t>
+          <t>▪ MALFUNCTION VOIDS ALL PAYS AND PLAYS.</t>
         </is>
       </c>
       <c r="H109" s="10" t="n"/>
       <c r="I109" s="11" t="n"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
-      <c r="B110" s="18" t="n"/>
-      <c r="C110" s="18" t="n"/>
+    <row r="110" ht="63" customHeight="1">
+      <c r="B110" s="16" t="n"/>
+      <c r="C110" s="16" t="n"/>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>[走線圖- 1,024 MAX WAYS]</t>
+          <t>▪ 若玩家在免費遊戲期間中斷連線，系統將自動完成該局結算，並將中獎金額加入餘額。</t>
         </is>
       </c>
       <c r="E110" s="10" t="n"/>
       <c r="F110" s="11" t="n"/>
       <c r="G110" s="15" t="inlineStr">
         <is>
-          <t>[走線圖- 1,024 MAX WAYS]</t>
+          <t>▪ IF THE PLAYER LOSES CONNECTION DURING THE FREE GAME FEATURE, THE SYSTEM WILL COMPLETE THE RESULT AUTOMATICALLY AND ADD ANY WINNINGS TO THE BALANCE.</t>
         </is>
       </c>
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="11" t="n"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
-      <c r="B111" s="18" t="n"/>
-      <c r="C111" s="18" t="n"/>
-      <c r="D111" s="15" t="inlineStr">
-        <is>
-          <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
-        </is>
-      </c>
-      <c r="E111" s="10" t="n"/>
-      <c r="F111" s="11" t="n"/>
-      <c r="G111" s="15" t="inlineStr">
-        <is>
-          <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
-        </is>
-      </c>
-      <c r="H111" s="10" t="n"/>
-      <c r="I111" s="11" t="n"/>
-    </row>
-    <row r="112" ht="15.75" customHeight="1">
-      <c r="B112" s="16" t="n"/>
-      <c r="C112" s="16" t="n"/>
-      <c r="D112" s="15" t="inlineStr">
-        <is>
-          <t>[走線圖-NO WIN]</t>
-        </is>
-      </c>
-      <c r="E112" s="10" t="n"/>
-      <c r="F112" s="11" t="n"/>
-      <c r="G112" s="15" t="inlineStr">
-        <is>
-          <t>[走線圖-NO WIN]</t>
-        </is>
-      </c>
-      <c r="H112" s="10" t="n"/>
-      <c r="I112" s="11" t="n"/>
-    </row>
-    <row r="113"/>
-    <row r="114" ht="15.75" customHeight="1">
-      <c r="B114" s="9" t="inlineStr">
-        <is>
-          <t>GAME RULE</t>
-        </is>
-      </c>
-      <c r="C114" s="10" t="n"/>
-      <c r="D114" s="10" t="n"/>
-      <c r="E114" s="10" t="n"/>
-      <c r="F114" s="10" t="n"/>
-      <c r="G114" s="10" t="n"/>
-      <c r="H114" s="10" t="n"/>
-      <c r="I114" s="11" t="n"/>
-    </row>
-    <row r="115" ht="15.75" customHeight="1">
-      <c r="B115" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C115" s="12" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D115" s="13" t="inlineStr">
-        <is>
-          <t>繁中</t>
-        </is>
-      </c>
-      <c r="E115" s="10" t="n"/>
-      <c r="F115" s="11" t="n"/>
-      <c r="G115" s="13" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
-      <c r="H115" s="10" t="n"/>
-      <c r="I115" s="11" t="n"/>
-    </row>
-    <row r="116" ht="15.75" customHeight="1">
-      <c r="B116" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C116" s="14" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
-      <c r="D116" s="15" t="inlineStr">
-        <is>
-          <t>遊戲規則</t>
-        </is>
-      </c>
-      <c r="E116" s="10" t="n"/>
-      <c r="F116" s="11" t="n"/>
-      <c r="G116" s="15" t="inlineStr">
-        <is>
-          <t>GAME RULES</t>
-        </is>
-      </c>
-      <c r="H116" s="10" t="n"/>
-      <c r="I116" s="11" t="n"/>
-    </row>
-    <row r="117" ht="15.75" customHeight="1">
-      <c r="B117" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C117" s="14" t="inlineStr">
-        <is>
-          <t>規則說明</t>
-        </is>
-      </c>
-      <c r="D117" s="15" t="inlineStr">
-        <is>
-          <t>▪ 選擇您想要玩的投注選項。</t>
-        </is>
-      </c>
-      <c r="E117" s="10" t="n"/>
-      <c r="F117" s="11" t="n"/>
-      <c r="G117" s="15" t="inlineStr">
-        <is>
-          <t>▪ SELECT BET OPTION YOU WISH TO PLAY.</t>
-        </is>
-      </c>
-      <c r="H117" s="10" t="n"/>
-      <c r="I117" s="11" t="n"/>
-    </row>
-    <row r="118" ht="31.5" customHeight="1">
-      <c r="B118" s="18" t="n"/>
-      <c r="C118" s="18" t="n"/>
-      <c r="D118" s="15" t="inlineStr">
-        <is>
-          <t>▪ 所有中獎金額均乘以投注選項，除非是累積獎。</t>
-        </is>
-      </c>
-      <c r="E118" s="10" t="n"/>
-      <c r="F118" s="11" t="n"/>
-      <c r="G118" s="15" t="inlineStr">
-        <is>
-          <t>▪ ALL WINS ARE MULTIPLIED BY BET OPTION EXCEPT PROGRESSIVES BONUSES.</t>
-        </is>
-      </c>
-      <c r="H118" s="10" t="n"/>
-      <c r="I118" s="11" t="n"/>
-    </row>
-    <row r="119" ht="15.75" customHeight="1">
-      <c r="B119" s="18" t="n"/>
-      <c r="C119" s="18" t="n"/>
-      <c r="D119" s="15" t="inlineStr">
-        <is>
-          <t>▪ 遊戲出現故障時，所有賠付與遊戲結果均視為無效。</t>
-        </is>
-      </c>
-      <c r="E119" s="10" t="n"/>
-      <c r="F119" s="11" t="n"/>
-      <c r="G119" s="15" t="inlineStr">
-        <is>
-          <t>▪ MALFUNCTION VOIDS ALL PAYS AND PLAYS.</t>
-        </is>
-      </c>
-      <c r="H119" s="10" t="n"/>
-      <c r="I119" s="11" t="n"/>
-    </row>
-    <row r="120" ht="63" customHeight="1">
-      <c r="B120" s="16" t="n"/>
-      <c r="C120" s="16" t="n"/>
-      <c r="D120" s="15" t="inlineStr">
-        <is>
-          <t>▪ 若玩家在免費遊戲期間中斷連線，系統將自動完成該局結算，並將中獎金額加入餘額。</t>
-        </is>
-      </c>
-      <c r="E120" s="10" t="n"/>
-      <c r="F120" s="11" t="n"/>
-      <c r="G120" s="15" t="inlineStr">
-        <is>
-          <t>▪ IF THE PLAYER LOSES CONNECTION DURING THE FREE GAME FEATURE, THE SYSTEM WILL COMPLETE THE RESULT AUTOMATICALLY AND ADD ANY WINNINGS TO THE BALANCE.</t>
-        </is>
-      </c>
-      <c r="H120" s="10" t="n"/>
-      <c r="I120" s="11" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="207">
+  <mergeCells count="185">
     <mergeCell ref="G38:I38"/>
     <mergeCell ref="B53:B55"/>
-    <mergeCell ref="G103:I103"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="C79:C80"/>
-    <mergeCell ref="G112:I112"/>
     <mergeCell ref="G13:I13"/>
-    <mergeCell ref="D116:F116"/>
     <mergeCell ref="G62:I62"/>
-    <mergeCell ref="G118:I118"/>
     <mergeCell ref="D66:F66"/>
     <mergeCell ref="G87:I87"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="D53:F53"/>
     <mergeCell ref="C45:C48"/>
     <mergeCell ref="D47:F47"/>
-    <mergeCell ref="G95:I95"/>
-    <mergeCell ref="B105:I105"/>
     <mergeCell ref="G89:I89"/>
     <mergeCell ref="D37:F37"/>
     <mergeCell ref="D102:F102"/>
@@ -2960,14 +2762,11 @@
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="B82:I82"/>
     <mergeCell ref="G90:I90"/>
-    <mergeCell ref="D94:F94"/>
     <mergeCell ref="B72:B74"/>
     <mergeCell ref="C60:C63"/>
     <mergeCell ref="G9:I9"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="G52:I52"/>
-    <mergeCell ref="D119:F119"/>
-    <mergeCell ref="G115:I115"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="G107:I107"/>
     <mergeCell ref="D80:F80"/>
@@ -2975,8 +2774,8 @@
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="D96:F96"/>
     <mergeCell ref="B76:I76"/>
+    <mergeCell ref="D105:F105"/>
     <mergeCell ref="G101:I101"/>
-    <mergeCell ref="D120:F120"/>
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="G37:I37"/>
     <mergeCell ref="D107:F107"/>
@@ -2993,13 +2792,12 @@
     <mergeCell ref="C31:C32"/>
     <mergeCell ref="G64:I64"/>
     <mergeCell ref="D74:F74"/>
+    <mergeCell ref="B107:B110"/>
     <mergeCell ref="B15:B25"/>
     <mergeCell ref="D83:F83"/>
     <mergeCell ref="G51:I51"/>
-    <mergeCell ref="D117:F117"/>
     <mergeCell ref="D55:F55"/>
     <mergeCell ref="G54:I54"/>
-    <mergeCell ref="G119:I119"/>
     <mergeCell ref="G32:I32"/>
     <mergeCell ref="B60:B63"/>
     <mergeCell ref="D67:F67"/>
@@ -3009,24 +2807,22 @@
     <mergeCell ref="D54:F54"/>
     <mergeCell ref="D60:F60"/>
     <mergeCell ref="G96:I96"/>
+    <mergeCell ref="C98:C102"/>
     <mergeCell ref="D100:F100"/>
+    <mergeCell ref="G105:I105"/>
     <mergeCell ref="G43:I43"/>
     <mergeCell ref="D109:F109"/>
     <mergeCell ref="G71:I71"/>
     <mergeCell ref="B79:B80"/>
-    <mergeCell ref="G120:I120"/>
     <mergeCell ref="G98:I98"/>
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="D46:F46"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="G8:I8"/>
-    <mergeCell ref="D111:F111"/>
-    <mergeCell ref="B114:I114"/>
     <mergeCell ref="B45:B48"/>
     <mergeCell ref="D108:F108"/>
     <mergeCell ref="D86:F86"/>
     <mergeCell ref="B50:I50"/>
-    <mergeCell ref="D95:F95"/>
     <mergeCell ref="B31:B32"/>
     <mergeCell ref="G10:I10"/>
     <mergeCell ref="G66:I66"/>
@@ -3046,7 +2842,6 @@
     <mergeCell ref="G58:I58"/>
     <mergeCell ref="C53:C55"/>
     <mergeCell ref="D71:F71"/>
-    <mergeCell ref="C95:C103"/>
     <mergeCell ref="G45:I45"/>
     <mergeCell ref="G110:I110"/>
     <mergeCell ref="D58:F58"/>
@@ -3054,12 +2849,10 @@
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="G100:I100"/>
-    <mergeCell ref="B95:B103"/>
     <mergeCell ref="D73:F73"/>
-    <mergeCell ref="G94:I94"/>
+    <mergeCell ref="G109:I109"/>
     <mergeCell ref="D51:F51"/>
     <mergeCell ref="G47:I47"/>
-    <mergeCell ref="G109:I109"/>
     <mergeCell ref="G44:I44"/>
     <mergeCell ref="G84:I84"/>
     <mergeCell ref="B69:I69"/>
@@ -3068,18 +2861,17 @@
     <mergeCell ref="G102:I102"/>
     <mergeCell ref="D35:F35"/>
     <mergeCell ref="G40:I40"/>
-    <mergeCell ref="C108:C112"/>
-    <mergeCell ref="G111:I111"/>
     <mergeCell ref="D44:F44"/>
     <mergeCell ref="D59:F59"/>
     <mergeCell ref="G12:I12"/>
-    <mergeCell ref="D115:F115"/>
     <mergeCell ref="G72:I72"/>
     <mergeCell ref="G86:I86"/>
     <mergeCell ref="D99:F99"/>
     <mergeCell ref="G70:I70"/>
     <mergeCell ref="D84:F84"/>
+    <mergeCell ref="B95:I95"/>
     <mergeCell ref="D36:F36"/>
+    <mergeCell ref="B104:I104"/>
     <mergeCell ref="G97:I97"/>
     <mergeCell ref="D45:F45"/>
     <mergeCell ref="C37:C40"/>
@@ -3087,18 +2879,14 @@
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="D77:F77"/>
+    <mergeCell ref="C107:C110"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D61:F61"/>
     <mergeCell ref="C85:C93"/>
     <mergeCell ref="D70:F70"/>
     <mergeCell ref="D48:F48"/>
-    <mergeCell ref="B108:B112"/>
     <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D103:F103"/>
-    <mergeCell ref="D112:F112"/>
-    <mergeCell ref="B117:B120"/>
     <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D118:F118"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="G35:I35"/>
     <mergeCell ref="B10:B11"/>
@@ -3111,7 +2899,6 @@
     <mergeCell ref="D89:F89"/>
     <mergeCell ref="D98:F98"/>
     <mergeCell ref="G99:I99"/>
-    <mergeCell ref="C117:C120"/>
     <mergeCell ref="G60:I60"/>
     <mergeCell ref="B34:I34"/>
     <mergeCell ref="D79:F79"/>
@@ -3122,7 +2909,6 @@
     <mergeCell ref="G77:I77"/>
     <mergeCell ref="G11:I11"/>
     <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G117:I117"/>
     <mergeCell ref="D90:F90"/>
     <mergeCell ref="C65:C67"/>
     <mergeCell ref="G67:I67"/>
@@ -3130,8 +2916,8 @@
     <mergeCell ref="G61:I61"/>
     <mergeCell ref="G39:I39"/>
     <mergeCell ref="G48:I48"/>
+    <mergeCell ref="B98:B102"/>
     <mergeCell ref="D52:F52"/>
-    <mergeCell ref="G116:I116"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Slots/H045_超級鑽石/文件/101015_Help.xlsx
+++ b/Slots/H045_超級鑽石/文件/101015_Help.xlsx
@@ -653,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I110"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -764,7 +764,7 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>▪ ALL WINS ARE FROM LEFTMOST TO RIGHT ONLY.</t>
+          <t>▪ ALL WINS MUST BE ON CONSECUTIVE REELS FROM LEFTMOST TO RIGHT.</t>
         </is>
       </c>
       <c r="H8" s="10" t="n"/>
@@ -818,19 +818,19 @@
       <c r="H10" s="10" t="n"/>
       <c r="I10" s="11" t="n"/>
     </row>
-    <row r="11" ht="31.5" customHeight="1">
+    <row r="11" ht="47.25" customHeight="1">
       <c r="B11" s="16" t="n"/>
       <c r="C11" s="16" t="n"/>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>▪ [WW][W2] 只會在金框符號被消除後產生。</t>
+          <t>▪ [WW][W2] 只會由參與中獎的金框符號轉換產生。</t>
         </is>
       </c>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>▪ [WW][W2] ARE AWARDED ONLY AFTER A GOLDEN FRAMED SYMBOL IS REMOVED.</t>
+          <t>▪ [WW][W2] ARE CREATED ONLY FROM GOLDEN FRAMED SYMBOLS THAT ARE PART OF A WINNING COMBINATION.</t>
         </is>
       </c>
       <c r="H11" s="10" t="n"/>
@@ -860,7 +860,7 @@
       <c r="H12" s="10" t="n"/>
       <c r="I12" s="11" t="n"/>
     </row>
-    <row r="13" ht="47.25" customHeight="1">
+    <row r="13" ht="63" customHeight="1">
       <c r="B13" s="14" t="n">
         <v>6</v>
       </c>
@@ -871,14 +871,14 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>▪ 當 {3} 個以上 [C1] 出現在任一位置，即可觸發免費遊戲特色，獲得 {10} 場免費遊戲。</t>
+          <t>▪ 所有連消結束後，若最終盤面出現 {3} 個以上 [C1]，即可觸發免費遊戲特色，獲得 {10} 場免費遊戲。</t>
         </is>
       </c>
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="11" t="n"/>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>▪ {3} OR MORE [C1] APPEARING IN ANY POSITION WILL TRIGGER THE FREE GAME FEATURE WITH {10} FREE SPINS.</t>
+          <t>▪ AFTER ALL CASCADES END, {3} OR MORE [C1] ON THE FINAL REELS WILL TRIGGER THE FREE GAME FEATURE AND AWARD {10} FREE SPINS.</t>
         </is>
       </c>
       <c r="H13" s="10" t="n"/>
@@ -1217,197 +1217,214 @@
       <c r="I25" s="17" t="n"/>
     </row>
     <row r="26"/>
-    <row r="27"/>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>CASCADING FEATURE</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
+      <c r="H27" s="10" t="n"/>
+      <c r="I27" s="11" t="n"/>
+    </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>CASCADING FEATURE</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>繁中</t>
+        </is>
+      </c>
       <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
       <c r="H28" s="10" t="n"/>
       <c r="I28" s="11" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>繁中</t>
+      <c r="B29" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>主要標題</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>消除特色</t>
         </is>
       </c>
       <c r="E29" s="10" t="n"/>
       <c r="F29" s="11" t="n"/>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>英文</t>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>CASCADING FEATURE</t>
         </is>
       </c>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="11" t="n"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" ht="63" customHeight="1">
       <c r="B30" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>主要標題</t>
+          <t>規則說明</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>消除特色</t>
+          <t>▪ 遊戲中若達成連線，除金框符號外的中獎符號將被消除，並在原位置補上新的符號。</t>
         </is>
       </c>
       <c r="E30" s="10" t="n"/>
       <c r="F30" s="11" t="n"/>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>CASCADING FEATURE</t>
+          <t>▪ ALL SYMBOLS IN WINNING COMBINATIONS, EXCEPT GOLDEN FRAMED SYMBOLS, WILL BE REMOVED AND NEW SYMBOLS WILL FILL THE EMPTY POSITIONS IN PLACE.</t>
         </is>
       </c>
       <c r="H30" s="10" t="n"/>
       <c r="I30" s="11" t="n"/>
     </row>
-    <row r="31" ht="63" customHeight="1">
-      <c r="B31" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>規則說明</t>
-        </is>
-      </c>
+    <row r="31" ht="31.5" customHeight="1">
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="16" t="n"/>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>▪ 遊戲中若達成連線，除金框符號外的中獎符號將被消除，並在原位置補上新的符號。</t>
+          <t>▪ 消除特色會持續發生，直到沒有新的連線為止。</t>
         </is>
       </c>
       <c r="E31" s="10" t="n"/>
       <c r="F31" s="11" t="n"/>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>▪ ALL SYMBOLS IN WINNING COMBINATIONS, EXCEPT GOLDEN FRAMED SYMBOLS, WILL BE REMOVED AND NEW SYMBOLS WILL FILL THE EMPTY POSITIONS.</t>
+          <t>▪ THE FEATURE CONTINUES UNTIL THERE ARE NO NEW WINNING COMBINATIONS.</t>
         </is>
       </c>
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="11" t="n"/>
     </row>
-    <row r="32" ht="31.5" customHeight="1">
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>▪ 消除特色會持續發生，直到沒有新的連線為止。</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="15" t="inlineStr">
-        <is>
-          <t>▪ THE FEATURE CONTINUES UNTIL THERE ARE NO NEW WINNING COMBINATIONS.</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="n"/>
-      <c r="I32" s="11" t="n"/>
-    </row>
-    <row r="33"/>
+    <row r="32"/>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>GOLDEN FRAMED FEATURE</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="11" t="n"/>
+    </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>GOLDEN FRAMED FEATURE</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>繁中</t>
+        </is>
+      </c>
       <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
+      <c r="F34" s="11" t="n"/>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
       <c r="H34" s="10" t="n"/>
       <c r="I34" s="11" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>繁中</t>
+      <c r="B35" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>主要標題</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>金框符號特色</t>
         </is>
       </c>
       <c r="E35" s="10" t="n"/>
       <c r="F35" s="11" t="n"/>
-      <c r="G35" s="13" t="inlineStr">
-        <is>
-          <t>英文</t>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>GOLDEN FRAMED FEATURE</t>
         </is>
       </c>
       <c r="H35" s="10" t="n"/>
       <c r="I35" s="11" t="n"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" ht="31.5" customHeight="1">
       <c r="B36" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>主要標題</t>
+          <t>規則說明</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>金框符號特色</t>
+          <t>▪ 金框符號只會出現在第 {2}、{3}、{4} 輪。</t>
         </is>
       </c>
       <c r="E36" s="10" t="n"/>
       <c r="F36" s="11" t="n"/>
       <c r="G36" s="15" t="inlineStr">
         <is>
-          <t>GOLDEN FRAMED FEATURE</t>
+          <t>▪ GOLDEN FRAMED SYMBOLS APPEAR ON REELS {2}, {3} AND {4} ONLY.</t>
         </is>
       </c>
       <c r="H36" s="10" t="n"/>
       <c r="I36" s="11" t="n"/>
     </row>
     <row r="37" ht="31.5" customHeight="1">
-      <c r="B37" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>規則說明</t>
-        </is>
-      </c>
+      <c r="B37" s="18" t="n"/>
+      <c r="C37" s="18" t="n"/>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>▪ 金框符號只會出現在第 {2}、{3}、{4} 輪。</t>
+          <t>▪ 金框符號與原符號的賠率相同。</t>
         </is>
       </c>
       <c r="E37" s="10" t="n"/>
       <c r="F37" s="11" t="n"/>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>▪ GOLDEN FRAMED SYMBOLS APPEAR ON REELS {2}, {3} AND {4} ONLY.</t>
+          <t>▪ GOLDEN FRAMED SYMBOLS PAY THE SAME AS THEIR ORIGINAL SYMBOLS.</t>
         </is>
       </c>
       <c r="H37" s="10" t="n"/>
@@ -1574,764 +1591,764 @@
       <c r="H46" s="10" t="n"/>
       <c r="I46" s="11" t="n"/>
     </row>
-    <row r="47" ht="78.75" customHeight="1">
+    <row r="47" ht="94.5" customHeight="1">
       <c r="B47" s="18" t="n"/>
       <c r="C47" s="18" t="n"/>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>▪ 每次連線時，本次中獎並被消除的帶倍數百搭符號，其倍數會相加，再乘上當次的贏分倍數。</t>
+          <t>▪ 每次連線時，本次中獎並被消除的帶倍數百搭符號，其倍數會相加，再乘上當次的連消倍數，最後作用於本次所有中獎組合的得分。</t>
         </is>
       </c>
       <c r="E47" s="10" t="n"/>
       <c r="F47" s="11" t="n"/>
       <c r="G47" s="15" t="inlineStr">
         <is>
-          <t>▪ ON EACH WIN, THE MULTIPLIERS OF ALL MULTIPLIER WILDS THAT ARE PART OF THE WIN AND REMOVED ARE ADDED TOGETHER, THEN MULTIPLIED BY THE CURRENT WIN MULTIPLIER.</t>
+          <t>▪ ON EACH WIN, THE MULTIPLIERS OF ALL MULTIPLIER WILDS THAT ARE PART OF THE WIN AND REMOVED ARE ADDED TOGETHER, MULTIPLIED BY THE CURRENT CASCADE MULTIPLIER, AND APPLIED TO ALL WINNING COMBINATIONS OF THAT WIN.</t>
         </is>
       </c>
       <c r="H47" s="10" t="n"/>
       <c r="I47" s="11" t="n"/>
     </row>
-    <row r="48" ht="47.25" customHeight="1">
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
+    <row r="48" ht="31.5" customHeight="1">
+      <c r="B48" s="18" t="n"/>
+      <c r="C48" s="18" t="n"/>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>▪ 未參與中獎的帶倍數百搭符號會保留在盤面上，直到參與中獎時才計入。</t>
+          <t>▪ 本次中獎沒有帶倍數百搭符號時，只乘上連消倍數。</t>
         </is>
       </c>
       <c r="E48" s="10" t="n"/>
       <c r="F48" s="11" t="n"/>
       <c r="G48" s="15" t="inlineStr">
         <is>
-          <t>▪ MULTIPLIER WILDS THAT ARE NOT PART OF A WIN STAY ON THE REELS AND COUNT ONLY WHEN THEY ARE PART OF A LATER WIN.</t>
+          <t>▪ WITHOUT MULTIPLIER WILDS IN THE WIN, ONLY THE CASCADE MULTIPLIER APPLIES.</t>
         </is>
       </c>
       <c r="H48" s="10" t="n"/>
       <c r="I48" s="11" t="n"/>
     </row>
-    <row r="49"/>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>WIN MULTIPLIER FEATURE</t>
-        </is>
-      </c>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="10" t="n"/>
-      <c r="F50" s="10" t="n"/>
-      <c r="G50" s="10" t="n"/>
-      <c r="H50" s="10" t="n"/>
-      <c r="I50" s="11" t="n"/>
-    </row>
+    <row r="49" ht="47.25" customHeight="1">
+      <c r="B49" s="16" t="n"/>
+      <c r="C49" s="16" t="n"/>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>▪ 未參與中獎的帶倍數百搭符號會保留在盤面上，直到參與中獎時才計入。</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="11" t="n"/>
+      <c r="G49" s="15" t="inlineStr">
+        <is>
+          <t>▪ MULTIPLIER WILDS THAT ARE NOT PART OF A WIN STAY ON THE REELS AND COUNT ONLY WHEN THEY ARE PART OF A LATER WIN.</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="11" t="n"/>
+    </row>
+    <row r="50"/>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D51" s="13" t="inlineStr">
-        <is>
-          <t>繁中</t>
-        </is>
-      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>CASCADE MULTIPLIER FEATURE</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
       <c r="E51" s="10" t="n"/>
-      <c r="F51" s="11" t="n"/>
-      <c r="G51" s="13" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
       <c r="H51" s="10" t="n"/>
       <c r="I51" s="11" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="B52" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="14" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>贏分倍數特色</t>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>繁中</t>
         </is>
       </c>
       <c r="E52" s="10" t="n"/>
       <c r="F52" s="11" t="n"/>
-      <c r="G52" s="15" t="inlineStr">
-        <is>
-          <t>WIN MULTIPLIER FEATURE</t>
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>英文</t>
         </is>
       </c>
       <c r="H52" s="10" t="n"/>
       <c r="I52" s="11" t="n"/>
     </row>
-    <row r="53" ht="31.5" customHeight="1">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="B53" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>規則說明</t>
+          <t>主要標題</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>▪ 每次旋轉開始時，贏分倍數為 X{1}。</t>
+          <t>連消倍數特色</t>
         </is>
       </c>
       <c r="E53" s="10" t="n"/>
       <c r="F53" s="11" t="n"/>
       <c r="G53" s="15" t="inlineStr">
         <is>
-          <t>▪ AT THE START OF EACH SPIN, THE WIN MULTIPLIER IS X{1}.</t>
+          <t>CASCADE MULTIPLIER FEATURE</t>
         </is>
       </c>
       <c r="H53" s="10" t="n"/>
       <c r="I53" s="11" t="n"/>
     </row>
-    <row r="54" ht="63" customHeight="1">
-      <c r="B54" s="18" t="n"/>
-      <c r="C54" s="18" t="n"/>
+    <row r="54" ht="31.5" customHeight="1">
+      <c r="B54" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>▪ 每次消除後若再達成連線，贏分倍數依序提升為 X{2}、X{3}、X{5}、X{10}。</t>
+          <t>▪ 每次旋轉開始時，連消倍數為 X{1}。</t>
         </is>
       </c>
       <c r="E54" s="10" t="n"/>
       <c r="F54" s="11" t="n"/>
       <c r="G54" s="15" t="inlineStr">
         <is>
-          <t>▪ EACH TIME A NEW WINNING COMBINATION OCCURS AFTER A CASCADE, THE WIN MULTIPLIER INCREASES TO X{2}, X{3}, X{5} AND X{10} IN ORDER.</t>
+          <t>▪ AT THE START OF EACH SPIN, THE CASCADE MULTIPLIER IS X{1}.</t>
         </is>
       </c>
       <c r="H54" s="10" t="n"/>
       <c r="I54" s="11" t="n"/>
     </row>
-    <row r="55" ht="31.5" customHeight="1">
-      <c r="B55" s="16" t="n"/>
-      <c r="C55" s="16" t="n"/>
+    <row r="55" ht="63" customHeight="1">
+      <c r="B55" s="18" t="n"/>
+      <c r="C55" s="18" t="n"/>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>▪ 贏分倍數達到 X{10} 後維持不變，直到本次旋轉結束。</t>
+          <t>▪ 每次消除後若再達成連線，連消倍數依序提升為 X{2}、X{3}、X{5}、X{10}。</t>
         </is>
       </c>
       <c r="E55" s="10" t="n"/>
       <c r="F55" s="11" t="n"/>
       <c r="G55" s="15" t="inlineStr">
         <is>
-          <t>▪ ONCE THE WIN MULTIPLIER REACHES X{10}, IT STAYS AT X{10} UNTIL THE SPIN ENDS.</t>
+          <t>▪ EACH TIME A NEW WINNING COMBINATION OCCURS AFTER A CASCADE, THE CASCADE MULTIPLIER INCREASES TO X{2}, X{3}, X{5} AND X{10} IN ORDER.</t>
         </is>
       </c>
       <c r="H55" s="10" t="n"/>
       <c r="I55" s="11" t="n"/>
     </row>
-    <row r="56"/>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="B57" s="9" t="inlineStr">
+    <row r="56" ht="47.25" customHeight="1">
+      <c r="B56" s="16" t="n"/>
+      <c r="C56" s="16" t="n"/>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>▪ 連消倍數達到 X{10} 後維持不變，直到本次旋轉結束。</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="11" t="n"/>
+      <c r="G56" s="15" t="inlineStr">
+        <is>
+          <t>▪ ONCE THE CASCADE MULTIPLIER REACHES X{10}, IT STAYS AT X{10} UNTIL THE SPIN ENDS.</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="11" t="n"/>
+    </row>
+    <row r="57"/>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>FREE GAME FEATURE</t>
         </is>
       </c>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-      <c r="E57" s="10" t="n"/>
-      <c r="F57" s="10" t="n"/>
-      <c r="G57" s="10" t="n"/>
-      <c r="H57" s="10" t="n"/>
-      <c r="I57" s="11" t="n"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C58" s="12" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D58" s="13" t="inlineStr">
-        <is>
-          <t>繁中</t>
-        </is>
-      </c>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
       <c r="E58" s="10" t="n"/>
-      <c r="F58" s="11" t="n"/>
-      <c r="G58" s="13" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
       <c r="H58" s="10" t="n"/>
       <c r="I58" s="11" t="n"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="B59" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" s="14" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
-      <c r="D59" s="15" t="inlineStr">
-        <is>
-          <t>免費遊戲特色</t>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>繁中</t>
         </is>
       </c>
       <c r="E59" s="10" t="n"/>
       <c r="F59" s="11" t="n"/>
-      <c r="G59" s="15" t="inlineStr">
-        <is>
-          <t>FREE GAME FEATURE</t>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>英文</t>
         </is>
       </c>
       <c r="H59" s="10" t="n"/>
       <c r="I59" s="11" t="n"/>
     </row>
-    <row r="60" ht="31.5" customHeight="1">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="B60" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>規則說明</t>
+          <t>主要標題</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>▪ 當 {3} 個以上 [C1] 出現在任一位置，即可獲得 {10} 場免費遊戲。</t>
+          <t>免費遊戲特色</t>
         </is>
       </c>
       <c r="E60" s="10" t="n"/>
       <c r="F60" s="11" t="n"/>
       <c r="G60" s="15" t="inlineStr">
         <is>
-          <t>▪ {3} OR MORE [C1] APPEARING IN ANY POSITION AWARD {10} FREE SPINS.</t>
+          <t>FREE GAME FEATURE</t>
         </is>
       </c>
       <c r="H60" s="10" t="n"/>
       <c r="I60" s="11" t="n"/>
     </row>
-    <row r="61" ht="31.5" customHeight="1">
-      <c r="B61" s="18" t="n"/>
-      <c r="C61" s="18" t="n"/>
+    <row r="61" ht="47.25" customHeight="1">
+      <c r="B61" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>▪ 點擊開始啟動免費遊戲特色。</t>
+          <t>▪ 所有連消結束後，若最終盤面出現 {3} 個以上 [C1]，即可獲得 {10} 場免費遊戲。</t>
         </is>
       </c>
       <c r="E61" s="10" t="n"/>
       <c r="F61" s="11" t="n"/>
       <c r="G61" s="15" t="inlineStr">
         <is>
-          <t>▪ CLICK THE START BUTTON TO START THE FREE GAME FEATURE.</t>
+          <t>▪ AFTER ALL CASCADES END, {3} OR MORE [C1] ON THE FINAL REELS AWARD {10} FREE SPINS.</t>
         </is>
       </c>
       <c r="H61" s="10" t="n"/>
       <c r="I61" s="11" t="n"/>
     </row>
-    <row r="62" ht="47.25" customHeight="1">
-      <c r="B62" s="18" t="n"/>
-      <c r="C62" s="18" t="n"/>
+    <row r="62" ht="63" customHeight="1">
+      <c r="B62" s="16" t="n"/>
+      <c r="C62" s="16" t="n"/>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>▪ 在免費遊戲中，{3} 個以上 [C1] 可再獲得 {5} 場免費遊戲，最多可獲得 {50} 場免費遊戲。</t>
+          <t>▪ 在免費遊戲中，每次旋轉的連消結束後，若最終盤面出現 {3} 個以上 [C1]，可再獲得 {5} 場免費遊戲，最多可獲得 {50} 場免費遊戲。</t>
         </is>
       </c>
       <c r="E62" s="10" t="n"/>
       <c r="F62" s="11" t="n"/>
       <c r="G62" s="15" t="inlineStr">
         <is>
-          <t>▪ DURING THE FREE GAME, {3} OR MORE [C1] AWARD {5} MORE FREE SPINS. THE MAXIMUM NUMBER OF FREE SPINS IS {50}.</t>
+          <t>▪ DURING THE FREE GAME, {3} OR MORE [C1] ON THE FINAL REELS AFTER ALL CASCADES OF A SPIN AWARD {5} MORE FREE SPINS, UP TO A MAXIMUM OF {50} FREE SPINS.</t>
         </is>
       </c>
       <c r="H62" s="10" t="n"/>
       <c r="I62" s="11" t="n"/>
     </row>
-    <row r="63" ht="47.25" customHeight="1">
-      <c r="B63" s="16" t="n"/>
-      <c r="C63" s="16" t="n"/>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="B63" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>副標題</t>
+        </is>
+      </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>▪ 在免費遊戲中，投注與觸發免費遊戲特色時相同。</t>
+          <t>連消倍數特色</t>
         </is>
       </c>
       <c r="E63" s="10" t="n"/>
       <c r="F63" s="11" t="n"/>
       <c r="G63" s="15" t="inlineStr">
         <is>
-          <t>▪ DURING THE FREE GAME, BET PER SPIN REMAINS THE SAME AS WHEN THE FREE GAME FEATURE WAS TRIGGERED.</t>
+          <t>CASCADE MULTIPLIER FEATURE</t>
         </is>
       </c>
       <c r="H63" s="10" t="n"/>
       <c r="I63" s="11" t="n"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" ht="31.5" customHeight="1">
       <c r="B64" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>副標題</t>
+          <t>規則說明</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>贏分倍數特色</t>
+          <t>▪ 免費遊戲每次旋轉開始時，連消倍數為 X{2}。</t>
         </is>
       </c>
       <c r="E64" s="10" t="n"/>
       <c r="F64" s="11" t="n"/>
       <c r="G64" s="15" t="inlineStr">
         <is>
-          <t>WIN MULTIPLIER FEATURE</t>
+          <t>▪ AT THE START OF EACH FREE SPIN, THE CASCADE MULTIPLIER IS X{2}.</t>
         </is>
       </c>
       <c r="H64" s="10" t="n"/>
       <c r="I64" s="11" t="n"/>
     </row>
-    <row r="65" ht="31.5" customHeight="1">
-      <c r="B65" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="C65" s="14" t="inlineStr">
-        <is>
-          <t>規則說明</t>
-        </is>
-      </c>
+    <row r="65" ht="63" customHeight="1">
+      <c r="B65" s="18" t="n"/>
+      <c r="C65" s="18" t="n"/>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>▪ 免費遊戲每次旋轉開始時，贏分倍數為 X{2}。</t>
+          <t>▪ 每次消除後若再達成連線，連消倍數依序提升為 X{4}、X{6}、X{10}、X{20}。</t>
         </is>
       </c>
       <c r="E65" s="10" t="n"/>
       <c r="F65" s="11" t="n"/>
       <c r="G65" s="15" t="inlineStr">
         <is>
-          <t>▪ AT THE START OF EACH FREE SPIN, THE WIN MULTIPLIER IS X{2}.</t>
+          <t>▪ EACH TIME A NEW WINNING COMBINATION OCCURS AFTER A CASCADE, THE CASCADE MULTIPLIER INCREASES TO X{4}, X{6}, X{10} AND X{20} IN ORDER.</t>
         </is>
       </c>
       <c r="H65" s="10" t="n"/>
       <c r="I65" s="11" t="n"/>
     </row>
-    <row r="66" ht="63" customHeight="1">
-      <c r="B66" s="18" t="n"/>
-      <c r="C66" s="18" t="n"/>
+    <row r="66" ht="47.25" customHeight="1">
+      <c r="B66" s="16" t="n"/>
+      <c r="C66" s="16" t="n"/>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>▪ 每次消除後若再達成連線，贏分倍數依序提升為 X{4}、X{6}、X{10}、X{20}。</t>
+          <t>▪ 連消倍數達到 X{20} 後維持不變，直到本次旋轉結束。</t>
         </is>
       </c>
       <c r="E66" s="10" t="n"/>
       <c r="F66" s="11" t="n"/>
       <c r="G66" s="15" t="inlineStr">
         <is>
-          <t>▪ EACH TIME A NEW WINNING COMBINATION OCCURS AFTER A CASCADE, THE WIN MULTIPLIER INCREASES TO X{4}, X{6}, X{10} AND X{20} IN ORDER.</t>
+          <t>▪ ONCE THE CASCADE MULTIPLIER REACHES X{20}, IT STAYS AT X{20} UNTIL THE SPIN ENDS.</t>
         </is>
       </c>
       <c r="H66" s="10" t="n"/>
       <c r="I66" s="11" t="n"/>
     </row>
-    <row r="67" ht="31.5" customHeight="1">
-      <c r="B67" s="16" t="n"/>
-      <c r="C67" s="16" t="n"/>
-      <c r="D67" s="15" t="inlineStr">
-        <is>
-          <t>▪ 贏分倍數達到 X{20} 後維持不變，直到本次旋轉結束。</t>
-        </is>
-      </c>
-      <c r="E67" s="10" t="n"/>
-      <c r="F67" s="11" t="n"/>
-      <c r="G67" s="15" t="inlineStr">
-        <is>
-          <t>▪ ONCE THE WIN MULTIPLIER REACHES X{20}, IT STAYS AT X{20} UNTIL THE SPIN ENDS.</t>
-        </is>
-      </c>
-      <c r="H67" s="10" t="n"/>
-      <c r="I67" s="11" t="n"/>
-    </row>
-    <row r="68"/>
+    <row r="67"/>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>EXTRA BET</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="10" t="n"/>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="10" t="n"/>
+      <c r="I68" s="11" t="n"/>
+    </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>EXTRA BET</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="n"/>
-      <c r="D69" s="10" t="n"/>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>繁中</t>
+        </is>
+      </c>
       <c r="E69" s="10" t="n"/>
-      <c r="F69" s="10" t="n"/>
-      <c r="G69" s="10" t="n"/>
+      <c r="F69" s="11" t="n"/>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
       <c r="H69" s="10" t="n"/>
       <c r="I69" s="11" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="B70" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C70" s="12" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D70" s="13" t="inlineStr">
-        <is>
-          <t>繁中</t>
+      <c r="B70" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>主要標題</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>額外投注</t>
         </is>
       </c>
       <c r="E70" s="10" t="n"/>
       <c r="F70" s="11" t="n"/>
-      <c r="G70" s="13" t="inlineStr">
-        <is>
-          <t>英文</t>
+      <c r="G70" s="15" t="inlineStr">
+        <is>
+          <t>EXTRA BET</t>
         </is>
       </c>
       <c r="H70" s="10" t="n"/>
       <c r="I70" s="11" t="n"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" ht="31.5" customHeight="1">
       <c r="B71" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>主要標題</t>
+          <t>規則說明</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>額外投注</t>
+          <t>▪ 額外投注的扣款為 {2} × 您所選的基礎投注。</t>
         </is>
       </c>
       <c r="E71" s="10" t="n"/>
       <c r="F71" s="11" t="n"/>
       <c r="G71" s="15" t="inlineStr">
         <is>
-          <t>EXTRA BET</t>
+          <t>▪ EXTRA BET COSTS {2} × THE BASE BET YOU SELECT.</t>
         </is>
       </c>
       <c r="H71" s="10" t="n"/>
       <c r="I71" s="11" t="n"/>
     </row>
     <row r="72" ht="31.5" customHeight="1">
-      <c r="B72" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>規則說明</t>
-        </is>
-      </c>
+      <c r="B72" s="18" t="n"/>
+      <c r="C72" s="18" t="n"/>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>▪ 額外投注的扣款為 {2} × 您所選的基礎投注。</t>
+          <t>▪ 所有獎金仍依您所選的基礎投注計算。</t>
         </is>
       </c>
       <c r="E72" s="10" t="n"/>
       <c r="F72" s="11" t="n"/>
       <c r="G72" s="15" t="inlineStr">
         <is>
-          <t>▪ EXTRA BET COSTS {2} × THE BASE BET YOU SELECT.</t>
+          <t>▪ ALL WINS ARE STILL CALCULATED ON THE BASE BET YOU SELECT.</t>
         </is>
       </c>
       <c r="H72" s="10" t="n"/>
       <c r="I72" s="11" t="n"/>
     </row>
-    <row r="73" ht="31.5" customHeight="1">
-      <c r="B73" s="18" t="n"/>
-      <c r="C73" s="18" t="n"/>
+    <row r="73" ht="47.25" customHeight="1">
+      <c r="B73" s="16" t="n"/>
+      <c r="C73" s="16" t="n"/>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>▪ 所有獎金仍依您所選的基礎投注計算。</t>
+          <t>▪ 免費遊戲的觸發機率提升為一般投注的 {5} 倍。</t>
         </is>
       </c>
       <c r="E73" s="10" t="n"/>
       <c r="F73" s="11" t="n"/>
       <c r="G73" s="15" t="inlineStr">
         <is>
-          <t>▪ ALL WINS ARE STILL CALCULATED ON THE BASE BET YOU SELECT.</t>
+          <t>▪ THE CHANCE TO TRIGGER THE FREE GAME FEATURE IS {5} TIMES THAT OF THE NORMAL BET.</t>
         </is>
       </c>
       <c r="H73" s="10" t="n"/>
       <c r="I73" s="11" t="n"/>
     </row>
-    <row r="74" ht="47.25" customHeight="1">
-      <c r="B74" s="16" t="n"/>
-      <c r="C74" s="16" t="n"/>
-      <c r="D74" s="15" t="inlineStr">
-        <is>
-          <t>▪ 免費遊戲的觸發機率提升為一般投注的 {5} 倍。</t>
-        </is>
-      </c>
-      <c r="E74" s="10" t="n"/>
-      <c r="F74" s="11" t="n"/>
-      <c r="G74" s="15" t="inlineStr">
-        <is>
-          <t>▪ THE CHANCE TO TRIGGER THE FREE GAME FEATURE IS {5} TIMES THAT OF THE NORMAL BET.</t>
-        </is>
-      </c>
-      <c r="H74" s="10" t="n"/>
-      <c r="I74" s="11" t="n"/>
-    </row>
-    <row r="75"/>
+    <row r="74"/>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>BUY FEATURE</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="n"/>
+      <c r="D75" s="10" t="n"/>
+      <c r="E75" s="10" t="n"/>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="11" t="n"/>
+    </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t>BUY FEATURE</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="n"/>
-      <c r="D76" s="10" t="n"/>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D76" s="13" t="inlineStr">
+        <is>
+          <t>繁中</t>
+        </is>
+      </c>
       <c r="E76" s="10" t="n"/>
-      <c r="F76" s="10" t="n"/>
-      <c r="G76" s="10" t="n"/>
+      <c r="F76" s="11" t="n"/>
+      <c r="G76" s="13" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
       <c r="H76" s="10" t="n"/>
       <c r="I76" s="11" t="n"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="B77" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D77" s="13" t="inlineStr">
-        <is>
-          <t>繁中</t>
+      <c r="B77" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>主要標題</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>購買特色</t>
         </is>
       </c>
       <c r="E77" s="10" t="n"/>
       <c r="F77" s="11" t="n"/>
-      <c r="G77" s="13" t="inlineStr">
-        <is>
-          <t>英文</t>
+      <c r="G77" s="15" t="inlineStr">
+        <is>
+          <t>BUY FEATURE</t>
         </is>
       </c>
       <c r="H77" s="10" t="n"/>
       <c r="I77" s="11" t="n"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" ht="47.25" customHeight="1">
       <c r="B78" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>主要標題</t>
+          <t>規則說明</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>購買特色</t>
+          <t>▪ 玩家可支付 {50}x 總投注，直接購買一次免費遊戲進場機會。</t>
         </is>
       </c>
       <c r="E78" s="10" t="n"/>
       <c r="F78" s="11" t="n"/>
       <c r="G78" s="15" t="inlineStr">
         <is>
-          <t>BUY FEATURE</t>
+          <t>▪ BUY FEATURE CAN BE PURCHASED FOR {50}X TOTAL BET TO ENTER THE FREE GAME FEATURE DIRECTLY.</t>
         </is>
       </c>
       <c r="H78" s="10" t="n"/>
       <c r="I78" s="11" t="n"/>
     </row>
-    <row r="79" ht="47.25" customHeight="1">
-      <c r="B79" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C79" s="14" t="inlineStr">
-        <is>
-          <t>規則說明</t>
-        </is>
-      </c>
+    <row r="79" ht="31.5" customHeight="1">
+      <c r="B79" s="16" t="n"/>
+      <c r="C79" s="16" t="n"/>
       <c r="D79" s="15" t="inlineStr">
         <is>
-          <t>▪ 玩家可支付 {50}x 總投注，直接購買一次免費遊戲進場機會。</t>
+          <t>▪ 完成購買後，將直接觸發一次免費遊戲特色。</t>
         </is>
       </c>
       <c r="E79" s="10" t="n"/>
       <c r="F79" s="11" t="n"/>
       <c r="G79" s="15" t="inlineStr">
         <is>
-          <t>▪ BUY FEATURE CAN BE PURCHASED FOR {50}X TOTAL BET TO ENTER THE FREE GAME FEATURE DIRECTLY.</t>
+          <t>▪ COMPLETING THE PURCHASE WILL TRIGGER THE FREE GAME FEATURE DIRECTLY.</t>
         </is>
       </c>
       <c r="H79" s="10" t="n"/>
       <c r="I79" s="11" t="n"/>
     </row>
-    <row r="80" ht="31.5" customHeight="1">
-      <c r="B80" s="16" t="n"/>
-      <c r="C80" s="16" t="n"/>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>▪ 完成購買後，將直接觸發一次免費遊戲特色。</t>
-        </is>
-      </c>
-      <c r="E80" s="10" t="n"/>
-      <c r="F80" s="11" t="n"/>
-      <c r="G80" s="15" t="inlineStr">
-        <is>
-          <t>▪ COMPLETING THE PURCHASE WILL TRIGGER THE FREE GAME FEATURE DIRECTLY.</t>
-        </is>
-      </c>
-      <c r="H80" s="10" t="n"/>
-      <c r="I80" s="11" t="n"/>
-    </row>
-    <row r="81"/>
+    <row r="80"/>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>OP JACKPOT</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="n"/>
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="11" t="n"/>
+    </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>OP JACKPOT</t>
-        </is>
-      </c>
-      <c r="C82" s="10" t="n"/>
-      <c r="D82" s="10" t="n"/>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="inlineStr">
+        <is>
+          <t>繁中</t>
+        </is>
+      </c>
       <c r="E82" s="10" t="n"/>
-      <c r="F82" s="10" t="n"/>
-      <c r="G82" s="10" t="n"/>
+      <c r="F82" s="11" t="n"/>
+      <c r="G82" s="13" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
       <c r="H82" s="10" t="n"/>
       <c r="I82" s="11" t="n"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="B83" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C83" s="12" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D83" s="13" t="inlineStr">
-        <is>
-          <t>繁中</t>
+      <c r="B83" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>主要標題</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t>OP JACKPOT</t>
         </is>
       </c>
       <c r="E83" s="10" t="n"/>
       <c r="F83" s="11" t="n"/>
-      <c r="G83" s="13" t="inlineStr">
-        <is>
-          <t>英文</t>
+      <c r="G83" s="15" t="inlineStr">
+        <is>
+          <t>OP JACKPOT</t>
         </is>
       </c>
       <c r="H83" s="10" t="n"/>
       <c r="I83" s="11" t="n"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" ht="47.25" customHeight="1">
       <c r="B84" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>主要標題</t>
+          <t>規則說明</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>OP JACKPOT</t>
+          <t>▪ 在遊戲中，OP JACKPOT 特色由盤面上的 {1} 個或以上 [C1] 隨機觸發。</t>
         </is>
       </c>
       <c r="E84" s="10" t="n"/>
       <c r="F84" s="11" t="n"/>
       <c r="G84" s="15" t="inlineStr">
         <is>
-          <t>OP JACKPOT</t>
+          <t>▪ OP JACKPOT FEATURE IS TRIGGERED RANDOMLY BY {1} OR MORE [C1] ON THE REELS.</t>
         </is>
       </c>
       <c r="H84" s="10" t="n"/>
       <c r="I84" s="11" t="n"/>
     </row>
     <row r="85" ht="47.25" customHeight="1">
-      <c r="B85" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C85" s="14" t="inlineStr">
-        <is>
-          <t>規則說明</t>
-        </is>
-      </c>
+      <c r="B85" s="18" t="n"/>
+      <c r="C85" s="18" t="n"/>
       <c r="D85" s="15" t="inlineStr">
         <is>
-          <t>▪ 在遊戲中，OP JACKPOT 特色由盤面上的 [C1] 隨機觸發。</t>
+          <t>▪ OP JACKPOT 特色會在畫面中出現 {12} 個 [幣]，其中包括 [GRAND]、[MAJOR]、[MINOR] 及 [MINI]。</t>
         </is>
       </c>
       <c r="E85" s="10" t="n"/>
       <c r="F85" s="11" t="n"/>
       <c r="G85" s="15" t="inlineStr">
         <is>
-          <t>▪ OP JACKPOT FEATURE IS TRIGGERED RANDOMLY BY {1} OR MORE [C1] ON THE REELS.</t>
+          <t>▪ DURING OP JACKPOT FEATURE, THERE ARE {12} [COIN] WHICH CONSIST OF [GRAND], [MAJOR], [MINOR] AND [MINI].</t>
         </is>
       </c>
       <c r="H85" s="10" t="n"/>
       <c r="I85" s="11" t="n"/>
     </row>
-    <row r="86" ht="47.25" customHeight="1">
+    <row r="86" ht="31.5" customHeight="1">
       <c r="B86" s="18" t="n"/>
       <c r="C86" s="18" t="n"/>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>▪ OP JACKPOT 特色會在畫面中出現 {12} 個 [幣]，其中包括 [GRAND]、[MAJOR]、[MINOR] 及 [MINI]。</t>
+          <t>▪ 選擇 {1} 個 [幣] 以揭示 [GRAND]、[MAJOR]、[MINOR] 或 [MINI]。</t>
         </is>
       </c>
       <c r="E86" s="10" t="n"/>
       <c r="F86" s="11" t="n"/>
       <c r="G86" s="15" t="inlineStr">
         <is>
-          <t>▪ DURING OP JACKPOT FEATURE, THERE ARE {12} [COIN] WHICH CONSIST OF [GRAND], [MAJOR], [MINOR] AND [MINI].</t>
+          <t>▪ SELECT A [COIN] TO REVEAL [GRAND], [MAJOR], [MINOR], OR [MINI].</t>
         </is>
       </c>
       <c r="H86" s="10" t="n"/>
       <c r="I86" s="11" t="n"/>
     </row>
-    <row r="87" ht="31.5" customHeight="1">
+    <row r="87" ht="47.25" customHeight="1">
       <c r="B87" s="18" t="n"/>
       <c r="C87" s="18" t="n"/>
       <c r="D87" s="15" t="inlineStr">
         <is>
-          <t>▪ 選擇 {1} 個 [幣] 以揭示 [GRAND]、[MAJOR]、[MINOR] 或 [MINI]。</t>
+          <t>▪ 當玩家獲得 {3} 個相同的 OP JACKPOT 特色符號，即可獲得該 OP JACKPOT 並結算總獎金。</t>
         </is>
       </c>
       <c r="E87" s="10" t="n"/>
       <c r="F87" s="11" t="n"/>
       <c r="G87" s="15" t="inlineStr">
         <is>
-          <t>▪ SELECT A [COIN] TO REVEAL [GRAND], [MAJOR], [MINOR], OR [MINI].</t>
+          <t>▪ IF PLAYER GETS {3} SAME JACKPOT SYMBOLS WILL WIN THE JACKPOT AND CALCULATE TOTAL WINNINGS.</t>
         </is>
       </c>
       <c r="H87" s="10" t="n"/>
       <c r="I87" s="11" t="n"/>
     </row>
-    <row r="88" ht="47.25" customHeight="1">
+    <row r="88" ht="63" customHeight="1">
       <c r="B88" s="18" t="n"/>
       <c r="C88" s="18" t="n"/>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>▪ 當玩家獲得 {3} 個相同的 OP JACKPOT 特色符號，即可獲得該 OP JACKPOT 並結算總獎金。</t>
+          <t>▪ [GRAND] 為連機累進彩金。單場遊戲中，投注選項選擇 {2.00} 以上即可解鎖 [GRAND]。</t>
         </is>
       </c>
       <c r="E88" s="10" t="n"/>
       <c r="F88" s="11" t="n"/>
       <c r="G88" s="15" t="inlineStr">
         <is>
-          <t>▪ IF PLAYER GETS {3} SAME JACKPOT SYMBOLS WILL WIN THE JACKPOT AND CALCULATE TOTAL WINNINGS.</t>
+          <t>▪ [GRAND] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [GRAND].</t>
         </is>
       </c>
       <c r="H88" s="10" t="n"/>
@@ -2342,32 +2359,32 @@
       <c r="C89" s="18" t="n"/>
       <c r="D89" s="15" t="inlineStr">
         <is>
-          <t>▪ [GRAND] 為連機累進彩金。單場遊戲中，投注選項選擇 {2.00} 以上即可解鎖 [GRAND]。</t>
+          <t>▪ [MAJOR] 為連機累進彩金。單場遊戲中，投注選項選擇 {2.00} 以上即可解鎖 [MAJOR]。</t>
         </is>
       </c>
       <c r="E89" s="10" t="n"/>
       <c r="F89" s="11" t="n"/>
       <c r="G89" s="15" t="inlineStr">
         <is>
-          <t>▪ [GRAND] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [GRAND].</t>
+          <t>▪ [MAJOR] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [MAJOR].</t>
         </is>
       </c>
       <c r="H89" s="10" t="n"/>
       <c r="I89" s="11" t="n"/>
     </row>
-    <row r="90" ht="63" customHeight="1">
+    <row r="90" ht="31.5" customHeight="1">
       <c r="B90" s="18" t="n"/>
       <c r="C90" s="18" t="n"/>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>▪ [MAJOR] 為連機累進彩金。單場遊戲中，投注選項選擇 {2.00} 以上即可解鎖 [MAJOR]。</t>
+          <t>▪ [MINOR] 為紅利彩金，依照投注選項改變。</t>
         </is>
       </c>
       <c r="E90" s="10" t="n"/>
       <c r="F90" s="11" t="n"/>
       <c r="G90" s="15" t="inlineStr">
         <is>
-          <t>▪ [MAJOR] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [MAJOR].</t>
+          <t>▪ [MINOR] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
         </is>
       </c>
       <c r="H90" s="10" t="n"/>
@@ -2378,139 +2395,139 @@
       <c r="C91" s="18" t="n"/>
       <c r="D91" s="15" t="inlineStr">
         <is>
-          <t>▪ [MINOR] 為紅利彩金，依照投注選項改變。</t>
+          <t>▪ [MINI] 為紅利彩金，依照投注選項改變。</t>
         </is>
       </c>
       <c r="E91" s="10" t="n"/>
       <c r="F91" s="11" t="n"/>
       <c r="G91" s="15" t="inlineStr">
         <is>
-          <t>▪ [MINOR] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
+          <t>▪ [MINI] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
         </is>
       </c>
       <c r="H91" s="10" t="n"/>
       <c r="I91" s="11" t="n"/>
     </row>
     <row r="92" ht="31.5" customHeight="1">
-      <c r="B92" s="18" t="n"/>
-      <c r="C92" s="18" t="n"/>
+      <c r="B92" s="16" t="n"/>
+      <c r="C92" s="16" t="n"/>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>▪ [MINI] 為紅利彩金，依照投注選項改變。</t>
+          <t>▪ 玩家投注越高，觸發 OP JACKPOT 特色的機會越高。</t>
         </is>
       </c>
       <c r="E92" s="10" t="n"/>
       <c r="F92" s="11" t="n"/>
       <c r="G92" s="15" t="inlineStr">
         <is>
-          <t>▪ [MINI] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
+          <t>▪ THE HIGHER BET, THE HIGHER CHANCES TO TRIGGER OP JACKPOT FEATURE.</t>
         </is>
       </c>
       <c r="H92" s="10" t="n"/>
       <c r="I92" s="11" t="n"/>
     </row>
-    <row r="93" ht="31.5" customHeight="1">
-      <c r="B93" s="16" t="n"/>
-      <c r="C93" s="16" t="n"/>
-      <c r="D93" s="15" t="inlineStr">
-        <is>
-          <t>▪ 玩家投注越高，觸發 OP JACKPOT 特色的機會越高。</t>
-        </is>
-      </c>
-      <c r="E93" s="10" t="n"/>
-      <c r="F93" s="11" t="n"/>
-      <c r="G93" s="15" t="inlineStr">
-        <is>
-          <t>▪ THE HIGHER BET, THE HIGHER CHANCES TO TRIGGER OP JACKPOT FEATURE.</t>
-        </is>
-      </c>
-      <c r="H93" s="10" t="n"/>
-      <c r="I93" s="11" t="n"/>
-    </row>
-    <row r="94"/>
+    <row r="93"/>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>WAY GAME</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="n"/>
+      <c r="D94" s="10" t="n"/>
+      <c r="E94" s="10" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
+      <c r="H94" s="10" t="n"/>
+      <c r="I94" s="11" t="n"/>
+    </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>LINES / WAYS</t>
-        </is>
-      </c>
-      <c r="C95" s="10" t="n"/>
-      <c r="D95" s="10" t="n"/>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D95" s="13" t="inlineStr">
+        <is>
+          <t>繁中</t>
+        </is>
+      </c>
       <c r="E95" s="10" t="n"/>
-      <c r="F95" s="10" t="n"/>
-      <c r="G95" s="10" t="n"/>
+      <c r="F95" s="11" t="n"/>
+      <c r="G95" s="13" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
       <c r="H95" s="10" t="n"/>
       <c r="I95" s="11" t="n"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="B96" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C96" s="12" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D96" s="13" t="inlineStr">
-        <is>
-          <t>繁中</t>
+      <c r="B96" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" s="14" t="inlineStr">
+        <is>
+          <t>主要標題</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>最多路數</t>
         </is>
       </c>
       <c r="E96" s="10" t="n"/>
       <c r="F96" s="11" t="n"/>
-      <c r="G96" s="13" t="inlineStr">
-        <is>
-          <t>英文</t>
+      <c r="G96" s="15" t="inlineStr">
+        <is>
+          <t>MAXIMUM WAYS</t>
         </is>
       </c>
       <c r="H96" s="10" t="n"/>
       <c r="I96" s="11" t="n"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" ht="63" customHeight="1">
       <c r="B97" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97" s="14" t="inlineStr">
         <is>
-          <t>主要標題</t>
+          <t>規則說明</t>
         </is>
       </c>
       <c r="D97" s="15" t="inlineStr">
         <is>
-          <t>最多路數</t>
+          <t>▪ 本遊戲為 {5} 輪 × {4} 列盤面，相同符號須出現在由左至右連續相鄰的轉輪上方可獲獎。</t>
         </is>
       </c>
       <c r="E97" s="10" t="n"/>
       <c r="F97" s="11" t="n"/>
       <c r="G97" s="15" t="inlineStr">
         <is>
-          <t>MAXIMUM WAYS</t>
+          <t>▪ THE GAME USES {5} REELS × {4} ROWS. MATCHING SYMBOLS MUST APPEAR ON CONSECUTIVE ADJACENT REELS FROM LEFT TO RIGHT TO WIN.</t>
         </is>
       </c>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="11" t="n"/>
     </row>
-    <row r="98" ht="31.5" customHeight="1">
-      <c r="B98" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C98" s="14" t="inlineStr">
-        <is>
-          <t>規則說明</t>
-        </is>
-      </c>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="B98" s="18" t="n"/>
+      <c r="C98" s="18" t="n"/>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>▪ 所有符號必須由最左至右連續出現，方可獲獎。</t>
+          <t>▪ 遊戲設定 = 最多 {1,024} 路。</t>
         </is>
       </c>
       <c r="E98" s="10" t="n"/>
       <c r="F98" s="11" t="n"/>
       <c r="G98" s="15" t="inlineStr">
         <is>
-          <t>▪ ALL WINS ARE FROM LEFTMOST TO RIGHT ONLY.</t>
+          <t>▪ GAME SETTING = {1,024} MAXIMUM WAYS.</t>
         </is>
       </c>
       <c r="H98" s="10" t="n"/>
@@ -2521,14 +2538,14 @@
       <c r="C99" s="18" t="n"/>
       <c r="D99" s="15" t="inlineStr">
         <is>
-          <t>▪ 遊戲設定 = 最多 {1,024} 路。</t>
+          <t>[走線圖- 1,024 MAX WAYS]</t>
         </is>
       </c>
       <c r="E99" s="10" t="n"/>
       <c r="F99" s="11" t="n"/>
       <c r="G99" s="15" t="inlineStr">
         <is>
-          <t>▪ GAME SETTING = {1,024} MAXIMUM WAYS.</t>
+          <t>[走線圖- 1,024 MAX WAYS]</t>
         </is>
       </c>
       <c r="H99" s="10" t="n"/>
@@ -2539,91 +2556,97 @@
       <c r="C100" s="18" t="n"/>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>[走線圖- 1,024 MAX WAYS]</t>
+          <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
         </is>
       </c>
       <c r="E100" s="10" t="n"/>
       <c r="F100" s="11" t="n"/>
       <c r="G100" s="15" t="inlineStr">
         <is>
-          <t>[走線圖- 1,024 MAX WAYS]</t>
+          <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
         </is>
       </c>
       <c r="H100" s="10" t="n"/>
       <c r="I100" s="11" t="n"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="B101" s="18" t="n"/>
-      <c r="C101" s="18" t="n"/>
+      <c r="B101" s="16" t="n"/>
+      <c r="C101" s="16" t="n"/>
       <c r="D101" s="15" t="inlineStr">
         <is>
-          <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
+          <t>[走線圖-NO WIN]</t>
         </is>
       </c>
       <c r="E101" s="10" t="n"/>
       <c r="F101" s="11" t="n"/>
       <c r="G101" s="15" t="inlineStr">
         <is>
-          <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
+          <t>[走線圖-NO WIN]</t>
         </is>
       </c>
       <c r="H101" s="10" t="n"/>
       <c r="I101" s="11" t="n"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
-      <c r="B102" s="16" t="n"/>
-      <c r="C102" s="16" t="n"/>
-      <c r="D102" s="15" t="inlineStr">
-        <is>
-          <t>[走線圖-NO WIN]</t>
-        </is>
-      </c>
-      <c r="E102" s="10" t="n"/>
-      <c r="F102" s="11" t="n"/>
-      <c r="G102" s="15" t="inlineStr">
-        <is>
-          <t>[走線圖-NO WIN]</t>
-        </is>
-      </c>
-      <c r="H102" s="10" t="n"/>
-      <c r="I102" s="11" t="n"/>
-    </row>
-    <row r="103"/>
+    <row r="102"/>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>GAME RULE</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="n"/>
+      <c r="D103" s="10" t="n"/>
+      <c r="E103" s="10" t="n"/>
+      <c r="F103" s="10" t="n"/>
+      <c r="G103" s="10" t="n"/>
+      <c r="H103" s="10" t="n"/>
+      <c r="I103" s="11" t="n"/>
+    </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="B104" s="9" t="inlineStr">
-        <is>
-          <t>GAME RULE</t>
-        </is>
-      </c>
-      <c r="C104" s="10" t="n"/>
-      <c r="D104" s="10" t="n"/>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D104" s="13" t="inlineStr">
+        <is>
+          <t>繁中</t>
+        </is>
+      </c>
       <c r="E104" s="10" t="n"/>
-      <c r="F104" s="10" t="n"/>
-      <c r="G104" s="10" t="n"/>
+      <c r="F104" s="11" t="n"/>
+      <c r="G104" s="13" t="inlineStr">
+        <is>
+          <t>英文</t>
+        </is>
+      </c>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="11" t="n"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="B105" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C105" s="12" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D105" s="13" t="inlineStr">
-        <is>
-          <t>繁中</t>
+      <c r="B105" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" s="14" t="inlineStr">
+        <is>
+          <t>主要標題</t>
+        </is>
+      </c>
+      <c r="D105" s="15" t="inlineStr">
+        <is>
+          <t>遊戲規則</t>
         </is>
       </c>
       <c r="E105" s="10" t="n"/>
       <c r="F105" s="11" t="n"/>
-      <c r="G105" s="13" t="inlineStr">
-        <is>
-          <t>英文</t>
+      <c r="G105" s="15" t="inlineStr">
+        <is>
+          <t>GAME RULES</t>
         </is>
       </c>
       <c r="H105" s="10" t="n"/>
@@ -2631,293 +2654,270 @@
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="B106" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>主要標題</t>
+          <t>規則說明</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>遊戲規則</t>
+          <t>▪ 選擇您想要玩的投注選項。</t>
         </is>
       </c>
       <c r="E106" s="10" t="n"/>
       <c r="F106" s="11" t="n"/>
       <c r="G106" s="15" t="inlineStr">
         <is>
-          <t>GAME RULES</t>
+          <t>▪ SELECT BET OPTION YOU WISH TO PLAY.</t>
         </is>
       </c>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="11" t="n"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
-      <c r="B107" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C107" s="14" t="inlineStr">
-        <is>
-          <t>規則說明</t>
-        </is>
-      </c>
+    <row r="107" ht="31.5" customHeight="1">
+      <c r="B107" s="18" t="n"/>
+      <c r="C107" s="18" t="n"/>
       <c r="D107" s="15" t="inlineStr">
         <is>
-          <t>▪ 選擇您想要玩的投注選項。</t>
+          <t>▪ 所有中獎金額均乘以投注選項，除非是累積獎。</t>
         </is>
       </c>
       <c r="E107" s="10" t="n"/>
       <c r="F107" s="11" t="n"/>
       <c r="G107" s="15" t="inlineStr">
         <is>
-          <t>▪ SELECT BET OPTION YOU WISH TO PLAY.</t>
+          <t>▪ ALL WINS ARE MULTIPLIED BY BET OPTION EXCEPT PROGRESSIVES BONUSES.</t>
         </is>
       </c>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="11" t="n"/>
     </row>
-    <row r="108" ht="31.5" customHeight="1">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="B108" s="18" t="n"/>
       <c r="C108" s="18" t="n"/>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>▪ 所有中獎金額均乘以投注選項，除非是累積獎。</t>
+          <t>▪ 遊戲出現故障時，所有賠付與遊戲結果均視為無效。</t>
         </is>
       </c>
       <c r="E108" s="10" t="n"/>
       <c r="F108" s="11" t="n"/>
       <c r="G108" s="15" t="inlineStr">
         <is>
-          <t>▪ ALL WINS ARE MULTIPLIED BY BET OPTION EXCEPT PROGRESSIVES BONUSES.</t>
+          <t>▪ MALFUNCTION VOIDS ALL PAYS AND PLAYS.</t>
         </is>
       </c>
       <c r="H108" s="10" t="n"/>
       <c r="I108" s="11" t="n"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
-      <c r="B109" s="18" t="n"/>
-      <c r="C109" s="18" t="n"/>
+    <row r="109" ht="63" customHeight="1">
+      <c r="B109" s="16" t="n"/>
+      <c r="C109" s="16" t="n"/>
       <c r="D109" s="15" t="inlineStr">
         <is>
-          <t>▪ 遊戲出現故障時，所有賠付與遊戲結果均視為無效。</t>
+          <t>▪ 若玩家在免費遊戲期間中斷連線，系統將自動完成該局結算，並將中獎金額加入餘額。</t>
         </is>
       </c>
       <c r="E109" s="10" t="n"/>
       <c r="F109" s="11" t="n"/>
       <c r="G109" s="15" t="inlineStr">
         <is>
-          <t>▪ MALFUNCTION VOIDS ALL PAYS AND PLAYS.</t>
+          <t>▪ IF THE PLAYER LOSES CONNECTION DURING THE FREE GAME FEATURE, THE SYSTEM WILL COMPLETE THE RESULT AUTOMATICALLY AND ADD ANY WINNINGS TO THE BALANCE.</t>
         </is>
       </c>
       <c r="H109" s="10" t="n"/>
       <c r="I109" s="11" t="n"/>
     </row>
-    <row r="110" ht="63" customHeight="1">
-      <c r="B110" s="16" t="n"/>
-      <c r="C110" s="16" t="n"/>
-      <c r="D110" s="15" t="inlineStr">
-        <is>
-          <t>▪ 若玩家在免費遊戲期間中斷連線，系統將自動完成該局結算，並將中獎金額加入餘額。</t>
-        </is>
-      </c>
-      <c r="E110" s="10" t="n"/>
-      <c r="F110" s="11" t="n"/>
-      <c r="G110" s="15" t="inlineStr">
-        <is>
-          <t>▪ IF THE PLAYER LOSES CONNECTION DURING THE FREE GAME FEATURE, THE SYSTEM WILL COMPLETE THE RESULT AUTOMATICALLY AND ADD ANY WINNINGS TO THE BALANCE.</t>
-        </is>
-      </c>
-      <c r="H110" s="10" t="n"/>
-      <c r="I110" s="11" t="n"/>
-    </row>
+    <row r="110" ht="63" customHeight="1"/>
   </sheetData>
   <mergeCells count="185">
+    <mergeCell ref="C30:C31"/>
     <mergeCell ref="G38:I38"/>
-    <mergeCell ref="B53:B55"/>
     <mergeCell ref="D11:F11"/>
-    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="D76:F76"/>
     <mergeCell ref="G13:I13"/>
     <mergeCell ref="G62:I62"/>
+    <mergeCell ref="B61:B62"/>
     <mergeCell ref="D66:F66"/>
     <mergeCell ref="G87:I87"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="D53:F53"/>
-    <mergeCell ref="C45:C48"/>
     <mergeCell ref="D47:F47"/>
+    <mergeCell ref="G95:I95"/>
+    <mergeCell ref="D28:F28"/>
     <mergeCell ref="G89:I89"/>
+    <mergeCell ref="G104:I104"/>
     <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D102:F102"/>
     <mergeCell ref="G65:I65"/>
     <mergeCell ref="G79:I79"/>
     <mergeCell ref="D12:F12"/>
+    <mergeCell ref="B78:B79"/>
     <mergeCell ref="G73:I73"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="G88:I88"/>
+    <mergeCell ref="B36:B40"/>
     <mergeCell ref="D92:F92"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="D39:F39"/>
+    <mergeCell ref="B45:B49"/>
     <mergeCell ref="G63:I63"/>
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="D29:F29"/>
-    <mergeCell ref="B82:I82"/>
     <mergeCell ref="G90:I90"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="C60:C63"/>
     <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B37:B40"/>
     <mergeCell ref="G52:I52"/>
+    <mergeCell ref="B68:I68"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="G107:I107"/>
-    <mergeCell ref="D80:F80"/>
     <mergeCell ref="C15:C25"/>
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="D96:F96"/>
-    <mergeCell ref="B76:I76"/>
     <mergeCell ref="D105:F105"/>
     <mergeCell ref="G101:I101"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="B75:I75"/>
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="G37:I37"/>
     <mergeCell ref="D107:F107"/>
+    <mergeCell ref="G69:I69"/>
+    <mergeCell ref="C36:C40"/>
     <mergeCell ref="G78:I78"/>
+    <mergeCell ref="B106:B109"/>
     <mergeCell ref="D91:F91"/>
     <mergeCell ref="G92:I92"/>
     <mergeCell ref="G30:I30"/>
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="D106:F106"/>
-    <mergeCell ref="G80:I80"/>
-    <mergeCell ref="D93:F93"/>
     <mergeCell ref="G55:I55"/>
-    <mergeCell ref="C31:C32"/>
     <mergeCell ref="G64:I64"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="B107:B110"/>
     <mergeCell ref="B15:B25"/>
     <mergeCell ref="D83:F83"/>
-    <mergeCell ref="G51:I51"/>
     <mergeCell ref="D55:F55"/>
     <mergeCell ref="G54:I54"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="B60:B63"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D110:F110"/>
+    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="C106:C109"/>
+    <mergeCell ref="C64:C66"/>
     <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D54:F54"/>
     <mergeCell ref="G106:I106"/>
-    <mergeCell ref="D54:F54"/>
     <mergeCell ref="D60:F60"/>
+    <mergeCell ref="G56:I56"/>
     <mergeCell ref="G96:I96"/>
-    <mergeCell ref="C98:C102"/>
+    <mergeCell ref="D69:F69"/>
     <mergeCell ref="D100:F100"/>
     <mergeCell ref="G105:I105"/>
     <mergeCell ref="G43:I43"/>
     <mergeCell ref="D109:F109"/>
+    <mergeCell ref="B30:B31"/>
     <mergeCell ref="G71:I71"/>
-    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="B33:I33"/>
     <mergeCell ref="G98:I98"/>
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="D46:F46"/>
+    <mergeCell ref="B51:I51"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="G8:I8"/>
-    <mergeCell ref="B45:B48"/>
     <mergeCell ref="D108:F108"/>
     <mergeCell ref="D86:F86"/>
-    <mergeCell ref="B50:I50"/>
-    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C71:C73"/>
+    <mergeCell ref="G82:I82"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="D104:F104"/>
     <mergeCell ref="G10:I10"/>
     <mergeCell ref="G66:I66"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="D32:F32"/>
     <mergeCell ref="G53:I53"/>
-    <mergeCell ref="G93:I93"/>
     <mergeCell ref="D97:F97"/>
-    <mergeCell ref="C72:C74"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="G74:I74"/>
     <mergeCell ref="D7:F7"/>
+    <mergeCell ref="B27:I27"/>
     <mergeCell ref="D78:F78"/>
     <mergeCell ref="G83:I83"/>
     <mergeCell ref="D87:F87"/>
     <mergeCell ref="G108:I108"/>
-    <mergeCell ref="G58:I58"/>
-    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="B84:B92"/>
     <mergeCell ref="D71:F71"/>
     <mergeCell ref="G45:I45"/>
-    <mergeCell ref="G110:I110"/>
-    <mergeCell ref="D58:F58"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="G100:I100"/>
     <mergeCell ref="D73:F73"/>
     <mergeCell ref="G109:I109"/>
-    <mergeCell ref="D51:F51"/>
     <mergeCell ref="G47:I47"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="B97:B101"/>
     <mergeCell ref="G44:I44"/>
     <mergeCell ref="G84:I84"/>
-    <mergeCell ref="B69:I69"/>
+    <mergeCell ref="B103:I103"/>
     <mergeCell ref="G31:I31"/>
     <mergeCell ref="G46:I46"/>
-    <mergeCell ref="G102:I102"/>
     <mergeCell ref="D35:F35"/>
     <mergeCell ref="G40:I40"/>
+    <mergeCell ref="C78:C79"/>
     <mergeCell ref="D44:F44"/>
     <mergeCell ref="D59:F59"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="G72:I72"/>
     <mergeCell ref="G86:I86"/>
+    <mergeCell ref="C45:C49"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="C97:C101"/>
     <mergeCell ref="D99:F99"/>
     <mergeCell ref="G70:I70"/>
     <mergeCell ref="D84:F84"/>
-    <mergeCell ref="B95:I95"/>
     <mergeCell ref="D36:F36"/>
-    <mergeCell ref="B104:I104"/>
     <mergeCell ref="G97:I97"/>
     <mergeCell ref="D45:F45"/>
-    <mergeCell ref="C37:C40"/>
     <mergeCell ref="D101:F101"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="D77:F77"/>
-    <mergeCell ref="C107:C110"/>
+    <mergeCell ref="C84:C92"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D61:F61"/>
-    <mergeCell ref="C85:C93"/>
+    <mergeCell ref="B81:I81"/>
     <mergeCell ref="D70:F70"/>
     <mergeCell ref="D48:F48"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="B58:I58"/>
     <mergeCell ref="D72:F72"/>
+    <mergeCell ref="B64:B66"/>
     <mergeCell ref="D62:F62"/>
     <mergeCell ref="B42:I42"/>
+    <mergeCell ref="D56:F56"/>
     <mergeCell ref="G35:I35"/>
     <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="G76:I76"/>
     <mergeCell ref="G91:I91"/>
-    <mergeCell ref="B85:B93"/>
     <mergeCell ref="D64:F64"/>
     <mergeCell ref="D38:F38"/>
     <mergeCell ref="G85:I85"/>
+    <mergeCell ref="C61:C62"/>
     <mergeCell ref="D89:F89"/>
     <mergeCell ref="D98:F98"/>
     <mergeCell ref="G99:I99"/>
     <mergeCell ref="G60:I60"/>
-    <mergeCell ref="B34:I34"/>
     <mergeCell ref="D79:F79"/>
-    <mergeCell ref="B28:I28"/>
     <mergeCell ref="D88:F88"/>
+    <mergeCell ref="B71:B73"/>
     <mergeCell ref="G59:I59"/>
     <mergeCell ref="D63:F63"/>
     <mergeCell ref="G77:I77"/>
     <mergeCell ref="G11:I11"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D90:F90"/>
-    <mergeCell ref="C65:C67"/>
-    <mergeCell ref="G67:I67"/>
     <mergeCell ref="D65:F65"/>
     <mergeCell ref="G61:I61"/>
     <mergeCell ref="G39:I39"/>
     <mergeCell ref="G48:I48"/>
-    <mergeCell ref="B98:B102"/>
+    <mergeCell ref="B94:I94"/>
     <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D49:F49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Slots/H045_超級鑽石/文件/101015_Help.xlsx
+++ b/Slots/H045_超級鑽石/文件/101015_Help.xlsx
@@ -653,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -805,14 +805,14 @@
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>▪ [WW][W2] 可替代除 [C1] 以外的所有符號。</t>
+          <t>▪ [WW] 與 [W2] 可替代除 [C1] 以外的所有符號。</t>
         </is>
       </c>
       <c r="E10" s="10" t="n"/>
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>▪ [WW][W2] SUBSTITUTE FOR ALL SYMBOLS EXCEPT [C1].</t>
+          <t>▪ [WW] AND [W2] SUBSTITUTE FOR ALL SYMBOLS EXCEPT [C1].</t>
         </is>
       </c>
       <c r="H10" s="10" t="n"/>
@@ -823,14 +823,14 @@
       <c r="C11" s="16" t="n"/>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>▪ [WW][W2] 只會由參與中獎的金框符號轉換產生。</t>
+          <t>▪ [WW] 與 [W2] 只會由參與中獎的金框符號轉換產生。</t>
         </is>
       </c>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>▪ [WW][W2] ARE CREATED ONLY FROM GOLDEN FRAMED SYMBOLS THAT ARE PART OF A WINNING COMBINATION.</t>
+          <t>▪ [WW] AND [W2] ARE CREATED ONLY FROM GOLDEN FRAMED SYMBOLS THAT ARE PART OF A WINNING COMBINATION.</t>
         </is>
       </c>
       <c r="H11" s="10" t="n"/>
@@ -847,14 +847,14 @@
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>免費遊戲獎賞</t>
+          <t>散佈符號</t>
         </is>
       </c>
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>FREE GAME BONUS</t>
+          <t>SCATTER SYMBOL</t>
         </is>
       </c>
       <c r="H12" s="10" t="n"/>
@@ -871,7 +871,7 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>▪ 所有連消結束後，若最終盤面出現 {3} 個以上 [C1]，即可觸發免費遊戲特色，獲得 {10} 場免費遊戲。</t>
+          <t>▪ 所有連消結束後，若最終盤面出現 {3} 個或以上 [C1]，即可觸發免費遊戲特色，獲得 {10} 場免費遊戲。</t>
         </is>
       </c>
       <c r="E13" s="10" t="n"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>▪ 遊戲中若達成連線，除金框符號外的中獎符號將被消除，並在原位置補上新的符號。</t>
+          <t>▪ 遊戲中若出現中獎組合，除金框符號外的中獎符號將被消除，並在原位置補上新的符號。</t>
         </is>
       </c>
       <c r="E30" s="10" t="n"/>
@@ -1310,7 +1310,7 @@
       <c r="C31" s="16" t="n"/>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>▪ 消除特色會持續發生，直到沒有新的連線為止。</t>
+          <t>▪ 消除特色會持續發生，直到沒有新的中獎組合為止。</t>
         </is>
       </c>
       <c r="E31" s="10" t="n"/>
@@ -1560,14 +1560,14 @@
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>▪ 金框符號轉換出的 [WW][W2] 有機會帶有 X{2}、X{3} 或 X{5} 倍數。</t>
+          <t>▪ 金框符號轉換出的 [WW] 與 [W2] 有機會帶有 X{2}、X{3} 或 X{5} 倍數。</t>
         </is>
       </c>
       <c r="E45" s="10" t="n"/>
       <c r="F45" s="11" t="n"/>
       <c r="G45" s="15" t="inlineStr">
         <is>
-          <t>▪ [WW][W2] TRANSFORMED FROM GOLDEN FRAMED SYMBOLS MAY CARRY AN X{2}, X{3} OR X{5} MULTIPLIER.</t>
+          <t>▪ [WW] AND [W2] TRANSFORMED FROM GOLDEN FRAMED SYMBOLS MAY CARRY AN X{2}, X{3} OR X{5} MULTIPLIER.</t>
         </is>
       </c>
       <c r="H45" s="10" t="n"/>
@@ -1596,7 +1596,7 @@
       <c r="C47" s="18" t="n"/>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>▪ 每次連線時，本次中獎並被消除的帶倍數百搭符號，其倍數會相加，再乘上當次的連消倍數，最後作用於本次所有中獎組合的得分。</t>
+          <t>▪ 每次中獎時，本次中獎並被消除的帶倍數百搭符號，其倍數會相加，再乘上當次的連消倍數，最後作用於本次所有中獎組合的得分。</t>
         </is>
       </c>
       <c r="E47" s="10" t="n"/>
@@ -1739,7 +1739,7 @@
       <c r="C55" s="18" t="n"/>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>▪ 每次消除後若再達成連線，連消倍數依序提升為 X{2}、X{3}、X{5}、X{10}。</t>
+          <t>▪ 每次消除後若再出現中獎組合，連消倍數依序提升為 X{2}、X{3}、X{5}、X{10}。</t>
         </is>
       </c>
       <c r="E55" s="10" t="n"/>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>▪ 所有連消結束後，若最終盤面出現 {3} 個以上 [C1]，即可獲得 {10} 場免費遊戲。</t>
+          <t>▪ 所有連消結束後，若最終盤面出現 {3} 個或以上 [C1]，即可獲得 {10} 場免費遊戲。</t>
         </is>
       </c>
       <c r="E61" s="10" t="n"/>
@@ -1859,478 +1859,478 @@
       <c r="H61" s="10" t="n"/>
       <c r="I61" s="11" t="n"/>
     </row>
-    <row r="62" ht="63" customHeight="1">
-      <c r="B62" s="16" t="n"/>
-      <c r="C62" s="16" t="n"/>
+    <row r="62" ht="47.25" customHeight="1">
+      <c r="B62" s="18" t="n"/>
+      <c r="C62" s="18" t="n"/>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>▪ 在免費遊戲中，每次旋轉的連消結束後，若最終盤面出現 {3} 個以上 [C1]，可再獲得 {5} 場免費遊戲，最多可獲得 {50} 場免費遊戲。</t>
+          <t>▪ 在免費遊戲中，每次旋轉的連消結束後，若最終盤面出現 {3} 個或以上 [C1]，可再獲得 {5} 場免費遊戲。</t>
         </is>
       </c>
       <c r="E62" s="10" t="n"/>
       <c r="F62" s="11" t="n"/>
       <c r="G62" s="15" t="inlineStr">
         <is>
-          <t>▪ DURING THE FREE GAME, {3} OR MORE [C1] ON THE FINAL REELS AFTER ALL CASCADES OF A SPIN AWARD {5} MORE FREE SPINS, UP TO A MAXIMUM OF {50} FREE SPINS.</t>
+          <t>▪ DURING THE FREE GAME, {3} OR MORE [C1] ON THE FINAL REELS AFTER ALL CASCADES OF A SPIN AWARD {5} ADDITIONAL FREE SPINS.</t>
         </is>
       </c>
       <c r="H62" s="10" t="n"/>
       <c r="I62" s="11" t="n"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="B63" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C63" s="14" t="inlineStr">
-        <is>
-          <t>副標題</t>
-        </is>
-      </c>
+    <row r="63" ht="31.5" customHeight="1">
+      <c r="B63" s="16" t="n"/>
+      <c r="C63" s="16" t="n"/>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>連消倍數特色</t>
+          <t>▪ 每次免費遊戲特色最多可進行 {50} 場免費遊戲。</t>
         </is>
       </c>
       <c r="E63" s="10" t="n"/>
       <c r="F63" s="11" t="n"/>
       <c r="G63" s="15" t="inlineStr">
         <is>
-          <t>CASCADE MULTIPLIER FEATURE</t>
+          <t>▪ A MAXIMUM OF {50} FREE SPINS MAY BE PLAYED DURING EACH FREE GAME FEATURE.</t>
         </is>
       </c>
       <c r="H63" s="10" t="n"/>
       <c r="I63" s="11" t="n"/>
     </row>
-    <row r="64" ht="31.5" customHeight="1">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="B64" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>規則說明</t>
+          <t>副標題</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>▪ 免費遊戲每次旋轉開始時，連消倍數為 X{2}。</t>
+          <t>連消倍數特色</t>
         </is>
       </c>
       <c r="E64" s="10" t="n"/>
       <c r="F64" s="11" t="n"/>
       <c r="G64" s="15" t="inlineStr">
         <is>
-          <t>▪ AT THE START OF EACH FREE SPIN, THE CASCADE MULTIPLIER IS X{2}.</t>
+          <t>CASCADE MULTIPLIER FEATURE</t>
         </is>
       </c>
       <c r="H64" s="10" t="n"/>
       <c r="I64" s="11" t="n"/>
     </row>
-    <row r="65" ht="63" customHeight="1">
-      <c r="B65" s="18" t="n"/>
-      <c r="C65" s="18" t="n"/>
+    <row r="65" ht="31.5" customHeight="1">
+      <c r="B65" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>▪ 每次消除後若再達成連線，連消倍數依序提升為 X{4}、X{6}、X{10}、X{20}。</t>
+          <t>▪ 免費遊戲每次旋轉開始時，連消倍數為 X{2}。</t>
         </is>
       </c>
       <c r="E65" s="10" t="n"/>
       <c r="F65" s="11" t="n"/>
       <c r="G65" s="15" t="inlineStr">
         <is>
-          <t>▪ EACH TIME A NEW WINNING COMBINATION OCCURS AFTER A CASCADE, THE CASCADE MULTIPLIER INCREASES TO X{4}, X{6}, X{10} AND X{20} IN ORDER.</t>
+          <t>▪ AT THE START OF EACH FREE SPIN, THE CASCADE MULTIPLIER IS X{2}.</t>
         </is>
       </c>
       <c r="H65" s="10" t="n"/>
       <c r="I65" s="11" t="n"/>
     </row>
-    <row r="66" ht="47.25" customHeight="1">
-      <c r="B66" s="16" t="n"/>
-      <c r="C66" s="16" t="n"/>
+    <row r="66" ht="63" customHeight="1">
+      <c r="B66" s="18" t="n"/>
+      <c r="C66" s="18" t="n"/>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>▪ 連消倍數達到 X{20} 後維持不變，直到本次旋轉結束。</t>
+          <t>▪ 每次消除後若再出現中獎組合，連消倍數依序提升為 X{4}、X{6}、X{10}、X{20}。</t>
         </is>
       </c>
       <c r="E66" s="10" t="n"/>
       <c r="F66" s="11" t="n"/>
       <c r="G66" s="15" t="inlineStr">
         <is>
-          <t>▪ ONCE THE CASCADE MULTIPLIER REACHES X{20}, IT STAYS AT X{20} UNTIL THE SPIN ENDS.</t>
+          <t>▪ EACH TIME A NEW WINNING COMBINATION OCCURS AFTER A CASCADE, THE CASCADE MULTIPLIER INCREASES TO X{4}, X{6}, X{10} AND X{20} IN ORDER.</t>
         </is>
       </c>
       <c r="H66" s="10" t="n"/>
       <c r="I66" s="11" t="n"/>
     </row>
-    <row r="67"/>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="B68" s="9" t="inlineStr">
+    <row r="67" ht="47.25" customHeight="1">
+      <c r="B67" s="16" t="n"/>
+      <c r="C67" s="16" t="n"/>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>▪ 連消倍數達到 X{20} 後維持不變，直到本次旋轉結束。</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="n"/>
+      <c r="F67" s="11" t="n"/>
+      <c r="G67" s="15" t="inlineStr">
+        <is>
+          <t>▪ ONCE THE CASCADE MULTIPLIER REACHES X{20}, IT STAYS AT X{20} UNTIL THE SPIN ENDS.</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="11" t="n"/>
+    </row>
+    <row r="68"/>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>EXTRA BET</t>
         </is>
       </c>
-      <c r="C68" s="10" t="n"/>
-      <c r="D68" s="10" t="n"/>
-      <c r="E68" s="10" t="n"/>
-      <c r="F68" s="10" t="n"/>
-      <c r="G68" s="10" t="n"/>
-      <c r="H68" s="10" t="n"/>
-      <c r="I68" s="11" t="n"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="B69" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C69" s="12" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D69" s="13" t="inlineStr">
-        <is>
-          <t>繁中</t>
-        </is>
-      </c>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="10" t="n"/>
       <c r="E69" s="10" t="n"/>
-      <c r="F69" s="11" t="n"/>
-      <c r="G69" s="13" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
       <c r="H69" s="10" t="n"/>
       <c r="I69" s="11" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="B70" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
-      <c r="D70" s="15" t="inlineStr">
-        <is>
-          <t>額外投注</t>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>繁中</t>
         </is>
       </c>
       <c r="E70" s="10" t="n"/>
       <c r="F70" s="11" t="n"/>
-      <c r="G70" s="15" t="inlineStr">
-        <is>
-          <t>EXTRA BET</t>
+      <c r="G70" s="13" t="inlineStr">
+        <is>
+          <t>英文</t>
         </is>
       </c>
       <c r="H70" s="10" t="n"/>
       <c r="I70" s="11" t="n"/>
     </row>
-    <row r="71" ht="31.5" customHeight="1">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="B71" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>規則說明</t>
+          <t>主要標題</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>▪ 額外投注的扣款為 {2} × 您所選的基礎投注。</t>
+          <t>額外投注</t>
         </is>
       </c>
       <c r="E71" s="10" t="n"/>
       <c r="F71" s="11" t="n"/>
       <c r="G71" s="15" t="inlineStr">
         <is>
-          <t>▪ EXTRA BET COSTS {2} × THE BASE BET YOU SELECT.</t>
+          <t>EXTRA BET</t>
         </is>
       </c>
       <c r="H71" s="10" t="n"/>
       <c r="I71" s="11" t="n"/>
     </row>
     <row r="72" ht="31.5" customHeight="1">
-      <c r="B72" s="18" t="n"/>
-      <c r="C72" s="18" t="n"/>
+      <c r="B72" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>▪ 所有獎金仍依您所選的基礎投注計算。</t>
+          <t>▪ 額外投注的扣款為您所選基礎投注的 {2}X。</t>
         </is>
       </c>
       <c r="E72" s="10" t="n"/>
       <c r="F72" s="11" t="n"/>
       <c r="G72" s="15" t="inlineStr">
         <is>
-          <t>▪ ALL WINS ARE STILL CALCULATED ON THE BASE BET YOU SELECT.</t>
+          <t>▪ EXTRA BET COSTS {2}X THE BASE BET YOU SELECT.</t>
         </is>
       </c>
       <c r="H72" s="10" t="n"/>
       <c r="I72" s="11" t="n"/>
     </row>
-    <row r="73" ht="47.25" customHeight="1">
-      <c r="B73" s="16" t="n"/>
-      <c r="C73" s="16" t="n"/>
+    <row r="73" ht="31.5" customHeight="1">
+      <c r="B73" s="18" t="n"/>
+      <c r="C73" s="18" t="n"/>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>▪ 免費遊戲的觸發機率提升為一般投注的 {5} 倍。</t>
+          <t>▪ 所有獎金仍依您所選的基礎投注計算。</t>
         </is>
       </c>
       <c r="E73" s="10" t="n"/>
       <c r="F73" s="11" t="n"/>
       <c r="G73" s="15" t="inlineStr">
         <is>
-          <t>▪ THE CHANCE TO TRIGGER THE FREE GAME FEATURE IS {5} TIMES THAT OF THE NORMAL BET.</t>
+          <t>▪ ALL WINS ARE STILL CALCULATED ON THE BASE BET YOU SELECT.</t>
         </is>
       </c>
       <c r="H73" s="10" t="n"/>
       <c r="I73" s="11" t="n"/>
     </row>
-    <row r="74"/>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="B75" s="9" t="inlineStr">
+    <row r="74" ht="47.25" customHeight="1">
+      <c r="B74" s="16" t="n"/>
+      <c r="C74" s="16" t="n"/>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>▪ 免費遊戲的觸發機率提升為一般投注的 {5} 倍。</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="n"/>
+      <c r="F74" s="11" t="n"/>
+      <c r="G74" s="15" t="inlineStr">
+        <is>
+          <t>▪ THE CHANCE TO TRIGGER THE FREE GAME FEATURE IS {5} TIMES THAT OF THE NORMAL BET.</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="n"/>
+      <c r="I74" s="11" t="n"/>
+    </row>
+    <row r="75"/>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="B76" s="9" t="inlineStr">
         <is>
           <t>BUY FEATURE</t>
         </is>
       </c>
-      <c r="C75" s="10" t="n"/>
-      <c r="D75" s="10" t="n"/>
-      <c r="E75" s="10" t="n"/>
-      <c r="F75" s="10" t="n"/>
-      <c r="G75" s="10" t="n"/>
-      <c r="H75" s="10" t="n"/>
-      <c r="I75" s="11" t="n"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="B76" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C76" s="12" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D76" s="13" t="inlineStr">
-        <is>
-          <t>繁中</t>
-        </is>
-      </c>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="10" t="n"/>
       <c r="E76" s="10" t="n"/>
-      <c r="F76" s="11" t="n"/>
-      <c r="G76" s="13" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
       <c r="H76" s="10" t="n"/>
       <c r="I76" s="11" t="n"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="B77" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C77" s="14" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
-      <c r="D77" s="15" t="inlineStr">
-        <is>
-          <t>購買特色</t>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="inlineStr">
+        <is>
+          <t>繁中</t>
         </is>
       </c>
       <c r="E77" s="10" t="n"/>
       <c r="F77" s="11" t="n"/>
-      <c r="G77" s="15" t="inlineStr">
-        <is>
-          <t>BUY FEATURE</t>
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>英文</t>
         </is>
       </c>
       <c r="H77" s="10" t="n"/>
       <c r="I77" s="11" t="n"/>
     </row>
-    <row r="78" ht="47.25" customHeight="1">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="B78" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>規則說明</t>
+          <t>主要標題</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>▪ 玩家可支付 {50}x 總投注，直接購買一次免費遊戲進場機會。</t>
+          <t>購買特色</t>
         </is>
       </c>
       <c r="E78" s="10" t="n"/>
       <c r="F78" s="11" t="n"/>
       <c r="G78" s="15" t="inlineStr">
         <is>
-          <t>▪ BUY FEATURE CAN BE PURCHASED FOR {50}X TOTAL BET TO ENTER THE FREE GAME FEATURE DIRECTLY.</t>
+          <t>BUY FEATURE</t>
         </is>
       </c>
       <c r="H78" s="10" t="n"/>
       <c r="I78" s="11" t="n"/>
     </row>
-    <row r="79" ht="31.5" customHeight="1">
-      <c r="B79" s="16" t="n"/>
-      <c r="C79" s="16" t="n"/>
+    <row r="79" ht="47.25" customHeight="1">
+      <c r="B79" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D79" s="15" t="inlineStr">
         <is>
-          <t>▪ 完成購買後，將直接觸發一次免費遊戲特色。</t>
+          <t>▪ 玩家可支付 {50}x 總投注，直接購買一次免費遊戲進場機會。</t>
         </is>
       </c>
       <c r="E79" s="10" t="n"/>
       <c r="F79" s="11" t="n"/>
       <c r="G79" s="15" t="inlineStr">
         <is>
-          <t>▪ COMPLETING THE PURCHASE WILL TRIGGER THE FREE GAME FEATURE DIRECTLY.</t>
+          <t>▪ BUY FEATURE CAN BE PURCHASED FOR {50}X TOTAL BET TO ENTER THE FREE GAME FEATURE DIRECTLY.</t>
         </is>
       </c>
       <c r="H79" s="10" t="n"/>
       <c r="I79" s="11" t="n"/>
     </row>
-    <row r="80"/>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="B81" s="9" t="inlineStr">
+    <row r="80" ht="31.5" customHeight="1">
+      <c r="B80" s="16" t="n"/>
+      <c r="C80" s="16" t="n"/>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>▪ 完成購買後，將直接觸發一次免費遊戲特色。</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="n"/>
+      <c r="F80" s="11" t="n"/>
+      <c r="G80" s="15" t="inlineStr">
+        <is>
+          <t>▪ COMPLETING THE PURCHASE WILL TRIGGER THE FREE GAME FEATURE DIRECTLY.</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="n"/>
+      <c r="I80" s="11" t="n"/>
+    </row>
+    <row r="81"/>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="B82" s="9" t="inlineStr">
         <is>
           <t>OP JACKPOT</t>
         </is>
       </c>
-      <c r="C81" s="10" t="n"/>
-      <c r="D81" s="10" t="n"/>
-      <c r="E81" s="10" t="n"/>
-      <c r="F81" s="10" t="n"/>
-      <c r="G81" s="10" t="n"/>
-      <c r="H81" s="10" t="n"/>
-      <c r="I81" s="11" t="n"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D82" s="13" t="inlineStr">
-        <is>
-          <t>繁中</t>
-        </is>
-      </c>
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="10" t="n"/>
       <c r="E82" s="10" t="n"/>
-      <c r="F82" s="11" t="n"/>
-      <c r="G82" s="13" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="F82" s="10" t="n"/>
+      <c r="G82" s="10" t="n"/>
       <c r="H82" s="10" t="n"/>
       <c r="I82" s="11" t="n"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="B83" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C83" s="14" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
-      <c r="D83" s="15" t="inlineStr">
-        <is>
-          <t>OP JACKPOT</t>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D83" s="13" t="inlineStr">
+        <is>
+          <t>繁中</t>
         </is>
       </c>
       <c r="E83" s="10" t="n"/>
       <c r="F83" s="11" t="n"/>
-      <c r="G83" s="15" t="inlineStr">
-        <is>
-          <t>OP JACKPOT</t>
+      <c r="G83" s="13" t="inlineStr">
+        <is>
+          <t>英文</t>
         </is>
       </c>
       <c r="H83" s="10" t="n"/>
       <c r="I83" s="11" t="n"/>
     </row>
-    <row r="84" ht="47.25" customHeight="1">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="B84" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>規則說明</t>
+          <t>主要標題</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>▪ 在遊戲中，OP JACKPOT 特色由盤面上的 {1} 個或以上 [C1] 隨機觸發。</t>
+          <t>OP JACKPOT</t>
         </is>
       </c>
       <c r="E84" s="10" t="n"/>
       <c r="F84" s="11" t="n"/>
       <c r="G84" s="15" t="inlineStr">
         <is>
-          <t>▪ OP JACKPOT FEATURE IS TRIGGERED RANDOMLY BY {1} OR MORE [C1] ON THE REELS.</t>
+          <t>OP JACKPOT</t>
         </is>
       </c>
       <c r="H84" s="10" t="n"/>
       <c r="I84" s="11" t="n"/>
     </row>
     <row r="85" ht="47.25" customHeight="1">
-      <c r="B85" s="18" t="n"/>
-      <c r="C85" s="18" t="n"/>
+      <c r="B85" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D85" s="15" t="inlineStr">
         <is>
-          <t>▪ OP JACKPOT 特色會在畫面中出現 {12} 個 [幣]，其中包括 [GRAND]、[MAJOR]、[MINOR] 及 [MINI]。</t>
+          <t>▪ 在遊戲中，OP JACKPOT 特色由盤面上的 {1} 個或以上 [C1] 隨機觸發。</t>
         </is>
       </c>
       <c r="E85" s="10" t="n"/>
       <c r="F85" s="11" t="n"/>
       <c r="G85" s="15" t="inlineStr">
         <is>
-          <t>▪ DURING OP JACKPOT FEATURE, THERE ARE {12} [COIN] WHICH CONSIST OF [GRAND], [MAJOR], [MINOR] AND [MINI].</t>
+          <t>▪ THE OP JACKPOT FEATURE IS TRIGGERED RANDOMLY BY {1} OR MORE [C1] ON THE REELS.</t>
         </is>
       </c>
       <c r="H85" s="10" t="n"/>
       <c r="I85" s="11" t="n"/>
     </row>
-    <row r="86" ht="31.5" customHeight="1">
+    <row r="86" ht="47.25" customHeight="1">
       <c r="B86" s="18" t="n"/>
       <c r="C86" s="18" t="n"/>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>▪ 選擇 {1} 個 [幣] 以揭示 [GRAND]、[MAJOR]、[MINOR] 或 [MINI]。</t>
+          <t>▪ OP JACKPOT 特色會在畫面中出現 {12} 個 [幣]，其中包括 [GRAND]、[MAJOR]、[MINOR] 及 [MINI]。</t>
         </is>
       </c>
       <c r="E86" s="10" t="n"/>
       <c r="F86" s="11" t="n"/>
       <c r="G86" s="15" t="inlineStr">
         <is>
-          <t>▪ SELECT A [COIN] TO REVEAL [GRAND], [MAJOR], [MINOR], OR [MINI].</t>
+          <t>▪ DURING THE OP JACKPOT FEATURE, THERE ARE {12} [COIN], WHICH CONSIST OF [GRAND], [MAJOR], [MINOR], AND [MINI].</t>
         </is>
       </c>
       <c r="H86" s="10" t="n"/>
       <c r="I86" s="11" t="n"/>
     </row>
-    <row r="87" ht="47.25" customHeight="1">
+    <row r="87" ht="31.5" customHeight="1">
       <c r="B87" s="18" t="n"/>
       <c r="C87" s="18" t="n"/>
       <c r="D87" s="15" t="inlineStr">
         <is>
-          <t>▪ 當玩家獲得 {3} 個相同的 OP JACKPOT 特色符號，即可獲得該 OP JACKPOT 並結算總獎金。</t>
+          <t>▪ 選擇 {1} 個 [幣] 以揭示 [GRAND]、[MAJOR]、[MINOR] 或 [MINI]。</t>
         </is>
       </c>
       <c r="E87" s="10" t="n"/>
       <c r="F87" s="11" t="n"/>
       <c r="G87" s="15" t="inlineStr">
         <is>
-          <t>▪ IF PLAYER GETS {3} SAME JACKPOT SYMBOLS WILL WIN THE JACKPOT AND CALCULATE TOTAL WINNINGS.</t>
+          <t>▪ SELECT A [COIN] TO REVEAL [GRAND], [MAJOR], [MINOR], OR [MINI].</t>
         </is>
       </c>
       <c r="H87" s="10" t="n"/>
@@ -2341,14 +2341,14 @@
       <c r="C88" s="18" t="n"/>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>▪ [GRAND] 為連機累進彩金。單場遊戲中，投注選項選擇 {2.00} 以上即可解鎖 [GRAND]。</t>
+          <t>▪ 當玩家獲得 {3} 個相同的 OP JACKPOT 特色符號，即可獲得該 OP JACKPOT 並結算總獎金。</t>
         </is>
       </c>
       <c r="E88" s="10" t="n"/>
       <c r="F88" s="11" t="n"/>
       <c r="G88" s="15" t="inlineStr">
         <is>
-          <t>▪ [GRAND] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [GRAND].</t>
+          <t>▪ IF THE PLAYER REVEALS {3} OF THE SAME JACKPOT SYMBOL, THE PLAYER WINS THAT JACKPOT AND IT IS ADDED TO THE TOTAL WIN.</t>
         </is>
       </c>
       <c r="H88" s="10" t="n"/>
@@ -2359,32 +2359,32 @@
       <c r="C89" s="18" t="n"/>
       <c r="D89" s="15" t="inlineStr">
         <is>
-          <t>▪ [MAJOR] 為連機累進彩金。單場遊戲中，投注選項選擇 {2.00} 以上即可解鎖 [MAJOR]。</t>
+          <t>▪ [GRAND] 為連機累進彩金。單場遊戲中，投注選項選擇 {2.00} 以上即可解鎖 [GRAND]。</t>
         </is>
       </c>
       <c r="E89" s="10" t="n"/>
       <c r="F89" s="11" t="n"/>
       <c r="G89" s="15" t="inlineStr">
         <is>
-          <t>▪ [MAJOR] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, THE PLAYER WILL UNLOCK [MAJOR].</t>
+          <t>▪ [GRAND] IS A LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, [GRAND] WILL BE UNLOCKED.</t>
         </is>
       </c>
       <c r="H89" s="10" t="n"/>
       <c r="I89" s="11" t="n"/>
     </row>
-    <row r="90" ht="31.5" customHeight="1">
+    <row r="90" ht="63" customHeight="1">
       <c r="B90" s="18" t="n"/>
       <c r="C90" s="18" t="n"/>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>▪ [MINOR] 為紅利彩金，依照投注選項改變。</t>
+          <t>▪ [MAJOR] 為連機累進彩金。單場遊戲中，投注選項選擇 {2.00} 以上即可解鎖 [MAJOR]。</t>
         </is>
       </c>
       <c r="E90" s="10" t="n"/>
       <c r="F90" s="11" t="n"/>
       <c r="G90" s="15" t="inlineStr">
         <is>
-          <t>▪ [MINOR] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
+          <t>▪ [MAJOR] IS A LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, [MAJOR] WILL BE UNLOCKED.</t>
         </is>
       </c>
       <c r="H90" s="10" t="n"/>
@@ -2395,139 +2395,139 @@
       <c r="C91" s="18" t="n"/>
       <c r="D91" s="15" t="inlineStr">
         <is>
-          <t>▪ [MINI] 為紅利彩金，依照投注選項改變。</t>
+          <t>▪ [MINOR] 為紅利彩金，依照投注選項改變。</t>
         </is>
       </c>
       <c r="E91" s="10" t="n"/>
       <c r="F91" s="11" t="n"/>
       <c r="G91" s="15" t="inlineStr">
         <is>
-          <t>▪ [MINI] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
+          <t>▪ [MINOR] WILL CHANGE IF THE PLAYER SELECTS A DIFFERENT BET OPTION.</t>
         </is>
       </c>
       <c r="H91" s="10" t="n"/>
       <c r="I91" s="11" t="n"/>
     </row>
     <row r="92" ht="31.5" customHeight="1">
-      <c r="B92" s="16" t="n"/>
-      <c r="C92" s="16" t="n"/>
+      <c r="B92" s="18" t="n"/>
+      <c r="C92" s="18" t="n"/>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>▪ 玩家投注越高，觸發 OP JACKPOT 特色的機會越高。</t>
+          <t>▪ [MINI] 為紅利彩金，依照投注選項改變。</t>
         </is>
       </c>
       <c r="E92" s="10" t="n"/>
       <c r="F92" s="11" t="n"/>
       <c r="G92" s="15" t="inlineStr">
         <is>
-          <t>▪ THE HIGHER BET, THE HIGHER CHANCES TO TRIGGER OP JACKPOT FEATURE.</t>
+          <t>▪ [MINI] WILL CHANGE IF THE PLAYER SELECTS A DIFFERENT BET OPTION.</t>
         </is>
       </c>
       <c r="H92" s="10" t="n"/>
       <c r="I92" s="11" t="n"/>
     </row>
-    <row r="93"/>
-    <row r="94" ht="15.75" customHeight="1">
-      <c r="B94" s="9" t="inlineStr">
+    <row r="93" ht="47.25" customHeight="1">
+      <c r="B93" s="16" t="n"/>
+      <c r="C93" s="16" t="n"/>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>▪ 玩家投注越高，觸發 OP JACKPOT 特色的機會越高。</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="n"/>
+      <c r="F93" s="11" t="n"/>
+      <c r="G93" s="15" t="inlineStr">
+        <is>
+          <t>▪ THE HIGHER THE BET, THE HIGHER THE CHANCE TO TRIGGER THE OP JACKPOT FEATURE.</t>
+        </is>
+      </c>
+      <c r="H93" s="10" t="n"/>
+      <c r="I93" s="11" t="n"/>
+    </row>
+    <row r="94"/>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="B95" s="9" t="inlineStr">
         <is>
           <t>WAY GAME</t>
         </is>
       </c>
-      <c r="C94" s="10" t="n"/>
-      <c r="D94" s="10" t="n"/>
-      <c r="E94" s="10" t="n"/>
-      <c r="F94" s="10" t="n"/>
-      <c r="G94" s="10" t="n"/>
-      <c r="H94" s="10" t="n"/>
-      <c r="I94" s="11" t="n"/>
-    </row>
-    <row r="95" ht="15.75" customHeight="1">
-      <c r="B95" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C95" s="12" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D95" s="13" t="inlineStr">
-        <is>
-          <t>繁中</t>
-        </is>
-      </c>
+      <c r="C95" s="10" t="n"/>
+      <c r="D95" s="10" t="n"/>
       <c r="E95" s="10" t="n"/>
-      <c r="F95" s="11" t="n"/>
-      <c r="G95" s="13" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="F95" s="10" t="n"/>
+      <c r="G95" s="10" t="n"/>
       <c r="H95" s="10" t="n"/>
       <c r="I95" s="11" t="n"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="B96" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C96" s="14" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
-      <c r="D96" s="15" t="inlineStr">
-        <is>
-          <t>最多路數</t>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D96" s="13" t="inlineStr">
+        <is>
+          <t>繁中</t>
         </is>
       </c>
       <c r="E96" s="10" t="n"/>
       <c r="F96" s="11" t="n"/>
-      <c r="G96" s="15" t="inlineStr">
-        <is>
-          <t>MAXIMUM WAYS</t>
+      <c r="G96" s="13" t="inlineStr">
+        <is>
+          <t>英文</t>
         </is>
       </c>
       <c r="H96" s="10" t="n"/>
       <c r="I96" s="11" t="n"/>
     </row>
-    <row r="97" ht="63" customHeight="1">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="B97" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97" s="14" t="inlineStr">
         <is>
-          <t>規則說明</t>
+          <t>主要標題</t>
         </is>
       </c>
       <c r="D97" s="15" t="inlineStr">
         <is>
-          <t>▪ 本遊戲為 {5} 輪 × {4} 列盤面，相同符號須出現在由左至右連續相鄰的轉輪上方可獲獎。</t>
+          <t>最多路數</t>
         </is>
       </c>
       <c r="E97" s="10" t="n"/>
       <c r="F97" s="11" t="n"/>
       <c r="G97" s="15" t="inlineStr">
         <is>
-          <t>▪ THE GAME USES {5} REELS × {4} ROWS. MATCHING SYMBOLS MUST APPEAR ON CONSECUTIVE ADJACENT REELS FROM LEFT TO RIGHT TO WIN.</t>
+          <t>MAXIMUM WAYS</t>
         </is>
       </c>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="11" t="n"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
-      <c r="B98" s="18" t="n"/>
-      <c r="C98" s="18" t="n"/>
+    <row r="98" ht="63" customHeight="1">
+      <c r="B98" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>▪ 遊戲設定 = 最多 {1,024} 路。</t>
+          <t>▪ 本遊戲為 {5} 輪 × {4} 列盤面，相同符號須出現在由左至右連續相鄰的轉輪上方可獲獎。</t>
         </is>
       </c>
       <c r="E98" s="10" t="n"/>
       <c r="F98" s="11" t="n"/>
       <c r="G98" s="15" t="inlineStr">
         <is>
-          <t>▪ GAME SETTING = {1,024} MAXIMUM WAYS.</t>
+          <t>▪ THE GAME USES {5} REELS × {4} ROWS. MATCHING SYMBOLS MUST APPEAR ON CONSECUTIVE ADJACENT REELS FROM LEFT TO RIGHT TO WIN.</t>
         </is>
       </c>
       <c r="H98" s="10" t="n"/>
@@ -2538,14 +2538,14 @@
       <c r="C99" s="18" t="n"/>
       <c r="D99" s="15" t="inlineStr">
         <is>
-          <t>[走線圖- 1,024 MAX WAYS]</t>
+          <t>▪ 遊戲設定 = 最多 {1,024} 路。</t>
         </is>
       </c>
       <c r="E99" s="10" t="n"/>
       <c r="F99" s="11" t="n"/>
       <c r="G99" s="15" t="inlineStr">
         <is>
-          <t>[走線圖- 1,024 MAX WAYS]</t>
+          <t>▪ GAME SETTING = {1,024} MAXIMUM WAYS.</t>
         </is>
       </c>
       <c r="H99" s="10" t="n"/>
@@ -2556,97 +2556,91 @@
       <c r="C100" s="18" t="n"/>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
+          <t>[走線圖- 1,024 MAX WAYS]</t>
         </is>
       </c>
       <c r="E100" s="10" t="n"/>
       <c r="F100" s="11" t="n"/>
       <c r="G100" s="15" t="inlineStr">
         <is>
-          <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
+          <t>[走線圖- 1,024 MAX WAYS]</t>
         </is>
       </c>
       <c r="H100" s="10" t="n"/>
       <c r="I100" s="11" t="n"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="B101" s="16" t="n"/>
-      <c r="C101" s="16" t="n"/>
+      <c r="B101" s="18" t="n"/>
+      <c r="C101" s="18" t="n"/>
       <c r="D101" s="15" t="inlineStr">
         <is>
-          <t>[走線圖-NO WIN]</t>
+          <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
         </is>
       </c>
       <c r="E101" s="10" t="n"/>
       <c r="F101" s="11" t="n"/>
       <c r="G101" s="15" t="inlineStr">
         <is>
-          <t>[走線圖-NO WIN]</t>
+          <t>[走線圖-3 OF A KIND PAYS 2 WAYS]</t>
         </is>
       </c>
       <c r="H101" s="10" t="n"/>
       <c r="I101" s="11" t="n"/>
     </row>
-    <row r="102"/>
-    <row r="103" ht="15.75" customHeight="1">
-      <c r="B103" s="9" t="inlineStr">
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="B102" s="16" t="n"/>
+      <c r="C102" s="16" t="n"/>
+      <c r="D102" s="15" t="inlineStr">
+        <is>
+          <t>[走線圖-NO WIN]</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="n"/>
+      <c r="F102" s="11" t="n"/>
+      <c r="G102" s="15" t="inlineStr">
+        <is>
+          <t>[走線圖-NO WIN]</t>
+        </is>
+      </c>
+      <c r="H102" s="10" t="n"/>
+      <c r="I102" s="11" t="n"/>
+    </row>
+    <row r="103"/>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="B104" s="9" t="inlineStr">
         <is>
           <t>GAME RULE</t>
         </is>
       </c>
-      <c r="C103" s="10" t="n"/>
-      <c r="D103" s="10" t="n"/>
-      <c r="E103" s="10" t="n"/>
-      <c r="F103" s="10" t="n"/>
-      <c r="G103" s="10" t="n"/>
-      <c r="H103" s="10" t="n"/>
-      <c r="I103" s="11" t="n"/>
-    </row>
-    <row r="104" ht="15.75" customHeight="1">
-      <c r="B104" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C104" s="12" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D104" s="13" t="inlineStr">
-        <is>
-          <t>繁中</t>
-        </is>
-      </c>
+      <c r="C104" s="10" t="n"/>
+      <c r="D104" s="10" t="n"/>
       <c r="E104" s="10" t="n"/>
-      <c r="F104" s="11" t="n"/>
-      <c r="G104" s="13" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="F104" s="10" t="n"/>
+      <c r="G104" s="10" t="n"/>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="11" t="n"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="B105" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C105" s="14" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
-      <c r="D105" s="15" t="inlineStr">
-        <is>
-          <t>遊戲規則</t>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D105" s="13" t="inlineStr">
+        <is>
+          <t>繁中</t>
         </is>
       </c>
       <c r="E105" s="10" t="n"/>
       <c r="F105" s="11" t="n"/>
-      <c r="G105" s="15" t="inlineStr">
-        <is>
-          <t>GAME RULES</t>
+      <c r="G105" s="13" t="inlineStr">
+        <is>
+          <t>英文</t>
         </is>
       </c>
       <c r="H105" s="10" t="n"/>
@@ -2654,106 +2648,127 @@
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="B106" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>規則說明</t>
+          <t>主要標題</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>▪ 選擇您想要玩的投注選項。</t>
+          <t>遊戲規則</t>
         </is>
       </c>
       <c r="E106" s="10" t="n"/>
       <c r="F106" s="11" t="n"/>
       <c r="G106" s="15" t="inlineStr">
         <is>
-          <t>▪ SELECT BET OPTION YOU WISH TO PLAY.</t>
+          <t>GAME RULES</t>
         </is>
       </c>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="11" t="n"/>
     </row>
     <row r="107" ht="31.5" customHeight="1">
-      <c r="B107" s="18" t="n"/>
-      <c r="C107" s="18" t="n"/>
+      <c r="B107" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C107" s="14" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D107" s="15" t="inlineStr">
         <is>
-          <t>▪ 所有中獎金額均乘以投注選項，除非是累積獎。</t>
+          <t>▪ 選擇您想要玩的投注選項。</t>
         </is>
       </c>
       <c r="E107" s="10" t="n"/>
       <c r="F107" s="11" t="n"/>
       <c r="G107" s="15" t="inlineStr">
         <is>
-          <t>▪ ALL WINS ARE MULTIPLIED BY BET OPTION EXCEPT PROGRESSIVES BONUSES.</t>
+          <t>▪ SELECT THE BET OPTION YOU WISH TO PLAY.</t>
         </is>
       </c>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="11" t="n"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" ht="31.5" customHeight="1">
       <c r="B108" s="18" t="n"/>
       <c r="C108" s="18" t="n"/>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>▪ 遊戲出現故障時，所有賠付與遊戲結果均視為無效。</t>
+          <t>▪ 所有中獎金額均乘以投注選項，除非是累積獎。</t>
         </is>
       </c>
       <c r="E108" s="10" t="n"/>
       <c r="F108" s="11" t="n"/>
       <c r="G108" s="15" t="inlineStr">
         <is>
-          <t>▪ MALFUNCTION VOIDS ALL PAYS AND PLAYS.</t>
+          <t>▪ ALL WINS ARE MULTIPLIED BY THE BET OPTION EXCEPT PROGRESSIVE BONUSES.</t>
         </is>
       </c>
       <c r="H108" s="10" t="n"/>
       <c r="I108" s="11" t="n"/>
     </row>
-    <row r="109" ht="63" customHeight="1">
-      <c r="B109" s="16" t="n"/>
-      <c r="C109" s="16" t="n"/>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="B109" s="18" t="n"/>
+      <c r="C109" s="18" t="n"/>
       <c r="D109" s="15" t="inlineStr">
         <is>
-          <t>▪ 若玩家在免費遊戲期間中斷連線，系統將自動完成該局結算，並將中獎金額加入餘額。</t>
+          <t>▪ 遊戲出現故障時，所有賠付與遊戲結果均視為無效。</t>
         </is>
       </c>
       <c r="E109" s="10" t="n"/>
       <c r="F109" s="11" t="n"/>
       <c r="G109" s="15" t="inlineStr">
         <is>
-          <t>▪ IF THE PLAYER LOSES CONNECTION DURING THE FREE GAME FEATURE, THE SYSTEM WILL COMPLETE THE RESULT AUTOMATICALLY AND ADD ANY WINNINGS TO THE BALANCE.</t>
+          <t>▪ MALFUNCTION VOIDS ALL PAYS AND PLAYS.</t>
         </is>
       </c>
       <c r="H109" s="10" t="n"/>
       <c r="I109" s="11" t="n"/>
     </row>
-    <row r="110" ht="63" customHeight="1"/>
+    <row r="110" ht="63" customHeight="1">
+      <c r="B110" s="16" t="n"/>
+      <c r="C110" s="16" t="n"/>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t>▪ 若玩家在免費遊戲期間中斷連線，系統將自動完成該局結算，並將中獎金額加入餘額。</t>
+        </is>
+      </c>
+      <c r="E110" s="10" t="n"/>
+      <c r="F110" s="11" t="n"/>
+      <c r="G110" s="15" t="inlineStr">
+        <is>
+          <t>▪ IF THE PLAYER LOSES CONNECTION DURING THE FREE GAME FEATURE, THE SYSTEM WILL COMPLETE THE RESULT AUTOMATICALLY AND ADD ANY WINNINGS TO THE BALANCE.</t>
+        </is>
+      </c>
+      <c r="H110" s="10" t="n"/>
+      <c r="I110" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="185">
+  <mergeCells count="187">
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="G38:I38"/>
     <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="C61:C63"/>
     <mergeCell ref="G13:I13"/>
     <mergeCell ref="G62:I62"/>
-    <mergeCell ref="B61:B62"/>
     <mergeCell ref="D66:F66"/>
     <mergeCell ref="G87:I87"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="D53:F53"/>
     <mergeCell ref="D47:F47"/>
-    <mergeCell ref="G95:I95"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="G89:I89"/>
-    <mergeCell ref="G104:I104"/>
     <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D102:F102"/>
     <mergeCell ref="G65:I65"/>
     <mergeCell ref="G79:I79"/>
     <mergeCell ref="D12:F12"/>
-    <mergeCell ref="B78:B79"/>
     <mergeCell ref="G73:I73"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="G88:I88"/>
@@ -2765,54 +2780,60 @@
     <mergeCell ref="G63:I63"/>
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="D29:F29"/>
+    <mergeCell ref="B82:I82"/>
     <mergeCell ref="G90:I90"/>
+    <mergeCell ref="B72:B74"/>
     <mergeCell ref="G9:I9"/>
     <mergeCell ref="G52:I52"/>
-    <mergeCell ref="B68:I68"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="G107:I107"/>
+    <mergeCell ref="D80:F80"/>
     <mergeCell ref="C15:C25"/>
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="D96:F96"/>
+    <mergeCell ref="B76:I76"/>
     <mergeCell ref="D105:F105"/>
     <mergeCell ref="G101:I101"/>
     <mergeCell ref="G28:I28"/>
-    <mergeCell ref="B75:I75"/>
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="G37:I37"/>
     <mergeCell ref="D107:F107"/>
-    <mergeCell ref="G69:I69"/>
     <mergeCell ref="C36:C40"/>
     <mergeCell ref="G78:I78"/>
-    <mergeCell ref="B106:B109"/>
     <mergeCell ref="D91:F91"/>
     <mergeCell ref="G92:I92"/>
     <mergeCell ref="G30:I30"/>
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="D106:F106"/>
+    <mergeCell ref="G80:I80"/>
+    <mergeCell ref="D93:F93"/>
     <mergeCell ref="G55:I55"/>
     <mergeCell ref="G64:I64"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="B107:B110"/>
     <mergeCell ref="B15:B25"/>
     <mergeCell ref="D83:F83"/>
     <mergeCell ref="D55:F55"/>
     <mergeCell ref="G54:I54"/>
     <mergeCell ref="C54:C56"/>
-    <mergeCell ref="C106:C109"/>
-    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D110:F110"/>
     <mergeCell ref="D85:F85"/>
+    <mergeCell ref="G106:I106"/>
     <mergeCell ref="D54:F54"/>
-    <mergeCell ref="G106:I106"/>
     <mergeCell ref="D60:F60"/>
     <mergeCell ref="G56:I56"/>
     <mergeCell ref="G96:I96"/>
-    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="C98:C102"/>
     <mergeCell ref="D100:F100"/>
     <mergeCell ref="G105:I105"/>
     <mergeCell ref="G43:I43"/>
     <mergeCell ref="D109:F109"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="G71:I71"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B79:B80"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="G98:I98"/>
     <mergeCell ref="D31:F31"/>
@@ -2822,25 +2843,25 @@
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="D108:F108"/>
     <mergeCell ref="D86:F86"/>
-    <mergeCell ref="C71:C73"/>
-    <mergeCell ref="G82:I82"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="D104:F104"/>
     <mergeCell ref="G10:I10"/>
     <mergeCell ref="G66:I66"/>
+    <mergeCell ref="B65:B67"/>
     <mergeCell ref="G53:I53"/>
+    <mergeCell ref="G93:I93"/>
     <mergeCell ref="D97:F97"/>
     <mergeCell ref="G34:I34"/>
-    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="C72:C74"/>
+    <mergeCell ref="G74:I74"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="D78:F78"/>
     <mergeCell ref="G83:I83"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="D87:F87"/>
     <mergeCell ref="G108:I108"/>
-    <mergeCell ref="B84:B92"/>
     <mergeCell ref="D71:F71"/>
     <mergeCell ref="G45:I45"/>
+    <mergeCell ref="G110:I110"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="G29:I29"/>
@@ -2848,16 +2869,14 @@
     <mergeCell ref="D73:F73"/>
     <mergeCell ref="G109:I109"/>
     <mergeCell ref="G47:I47"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="B97:B101"/>
     <mergeCell ref="G44:I44"/>
     <mergeCell ref="G84:I84"/>
-    <mergeCell ref="B103:I103"/>
+    <mergeCell ref="B69:I69"/>
     <mergeCell ref="G31:I31"/>
     <mergeCell ref="G46:I46"/>
+    <mergeCell ref="G102:I102"/>
     <mergeCell ref="D35:F35"/>
     <mergeCell ref="G40:I40"/>
-    <mergeCell ref="C78:C79"/>
     <mergeCell ref="D44:F44"/>
     <mergeCell ref="D59:F59"/>
     <mergeCell ref="G12:I12"/>
@@ -2865,57 +2884,57 @@
     <mergeCell ref="G86:I86"/>
     <mergeCell ref="C45:C49"/>
     <mergeCell ref="D34:F34"/>
-    <mergeCell ref="C97:C101"/>
     <mergeCell ref="D99:F99"/>
     <mergeCell ref="G70:I70"/>
     <mergeCell ref="D84:F84"/>
+    <mergeCell ref="B95:I95"/>
     <mergeCell ref="D36:F36"/>
+    <mergeCell ref="B104:I104"/>
     <mergeCell ref="G97:I97"/>
     <mergeCell ref="D45:F45"/>
     <mergeCell ref="D101:F101"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="D77:F77"/>
-    <mergeCell ref="C84:C92"/>
+    <mergeCell ref="C107:C110"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D61:F61"/>
-    <mergeCell ref="B81:I81"/>
+    <mergeCell ref="C85:C93"/>
     <mergeCell ref="D70:F70"/>
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="G49:I49"/>
     <mergeCell ref="B54:B56"/>
     <mergeCell ref="B58:I58"/>
     <mergeCell ref="D72:F72"/>
-    <mergeCell ref="B64:B66"/>
     <mergeCell ref="D62:F62"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="D56:F56"/>
     <mergeCell ref="G35:I35"/>
     <mergeCell ref="B10:B11"/>
-    <mergeCell ref="G76:I76"/>
     <mergeCell ref="G91:I91"/>
+    <mergeCell ref="B85:B93"/>
     <mergeCell ref="D64:F64"/>
     <mergeCell ref="D38:F38"/>
     <mergeCell ref="G85:I85"/>
-    <mergeCell ref="C61:C62"/>
     <mergeCell ref="D89:F89"/>
     <mergeCell ref="D98:F98"/>
     <mergeCell ref="G99:I99"/>
     <mergeCell ref="G60:I60"/>
     <mergeCell ref="D79:F79"/>
     <mergeCell ref="D88:F88"/>
-    <mergeCell ref="B71:B73"/>
     <mergeCell ref="G59:I59"/>
     <mergeCell ref="D63:F63"/>
     <mergeCell ref="G77:I77"/>
     <mergeCell ref="G11:I11"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D90:F90"/>
+    <mergeCell ref="C65:C67"/>
+    <mergeCell ref="G67:I67"/>
     <mergeCell ref="D65:F65"/>
     <mergeCell ref="G61:I61"/>
     <mergeCell ref="G39:I39"/>
     <mergeCell ref="G48:I48"/>
-    <mergeCell ref="B94:I94"/>
+    <mergeCell ref="B98:B102"/>
     <mergeCell ref="D52:F52"/>
     <mergeCell ref="D49:F49"/>
   </mergeCells>

--- a/Slots/H045_超級鑽石/文件/101015_Help.xlsx
+++ b/Slots/H045_超級鑽石/文件/101015_Help.xlsx
@@ -2520,14 +2520,14 @@
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>▪ 本遊戲為 {5} 輪 × {4} 列盤面，相同符號須出現在由左至右連續相鄰的轉輪上方可獲獎。</t>
+          <t>▪ 本遊戲為 {5} 輪 × {4} 列盤面，相同符號須出現在由最左至右連續相鄰的轉輪上方可獲獎。</t>
         </is>
       </c>
       <c r="E98" s="10" t="n"/>
       <c r="F98" s="11" t="n"/>
       <c r="G98" s="15" t="inlineStr">
         <is>
-          <t>▪ THE GAME USES {5} REELS × {4} ROWS. MATCHING SYMBOLS MUST APPEAR ON CONSECUTIVE ADJACENT REELS FROM LEFT TO RIGHT TO WIN.</t>
+          <t>▪ THE GAME USES {5} REELS × {4} ROWS. MATCHING SYMBOLS MUST APPEAR ON CONSECUTIVE ADJACENT REELS FROM LEFTMOST TO RIGHT TO WIN.</t>
         </is>
       </c>
       <c r="H98" s="10" t="n"/>
